--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46269</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>46269</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44593</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26270-2024</t>
+          <t>A 33003-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1151,14 +1151,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45468</v>
+        <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,14 +1170,19 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1186,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1195,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1211,35 +1216,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
@@ -1263,7 +1268,7 @@
         <v>46244</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1356,7 +1361,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 34275-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1385,13 +1390,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1431,42 +1431,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 34277-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1483,7 +1483,7 @@
         <v>46253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1540,38 +1540,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34277-2026</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46253</v>
+        <v>45468</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1601,23 +1601,23 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -1625,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1641,35 +1641,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
         <v>45719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44866</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 65329-2021</t>
+          <t>A 45980-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44515</v>
+        <v>44846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2484,7 +2484,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45980-2022</t>
+          <t>A 65329-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44846</v>
+        <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2574,7 +2574,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63257-2021</t>
+          <t>A 7786-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3005,14 +3005,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44508</v>
+        <v>44608</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7786-2022</t>
+          <t>A 63257-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3078,14 +3078,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44608</v>
+        <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3158,7 +3158,7 @@
         <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44456</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44456</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44606</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>44781</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>44714</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44477</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>44638</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44615</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>44616</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45186</v>
+        <v>44922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4090,7 +4090,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45215</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44810</v>
+        <v>45069</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4190,6 +4190,11 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>HJO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -4236,7 +4241,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45209</v>
+        <v>45582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4266,7 +4271,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4309,7 +4314,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4323,10 +4328,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44782</v>
+        <v>45198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4339,7 +4344,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4382,7 +4387,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4392,14 +4397,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45300</v>
+        <v>45198</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4455,7 +4460,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4469,10 +4474,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45468</v>
+        <v>45167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4485,7 +4490,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4528,7 +4533,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4542,10 +4547,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44853</v>
+        <v>45167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4558,7 +4563,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4601,7 +4606,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4615,10 +4620,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44939</v>
+        <v>45573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4631,7 +4636,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>11.6</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4674,7 +4679,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4684,14 +4689,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44945</v>
+        <v>45300</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4704,7 +4709,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4747,7 +4752,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4761,10 +4766,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44922</v>
+        <v>45351</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4777,7 +4782,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4820,7 +4825,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4834,10 +4839,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44939</v>
+        <v>45797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4850,7 +4855,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4893,7 +4898,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4907,10 +4912,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44935</v>
+        <v>45643</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4923,7 +4928,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4966,7 +4971,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45390</v>
+        <v>45805</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4996,7 +5001,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5039,7 +5044,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5049,14 +5054,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45197</v>
+        <v>45805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5069,7 +5074,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5112,7 +5117,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44615</v>
+        <v>45685</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5142,7 +5147,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5185,7 +5190,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5199,10 +5204,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45198</v>
+        <v>46019</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5215,7 +5220,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5258,7 +5263,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5272,10 +5277,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45826</v>
+        <v>44935</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5288,7 +5293,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5331,7 +5336,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5341,14 +5346,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45254</v>
+        <v>45186</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5361,7 +5366,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5404,7 +5409,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5418,10 +5423,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45069</v>
+        <v>44981</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5433,13 +5438,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45699</v>
+        <v>45142</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45854</v>
+        <v>46042</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5584,13 +5584,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5633,7 +5628,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5647,10 +5642,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45735</v>
+        <v>44945</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5663,7 +5658,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5706,7 +5701,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45573</v>
+        <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5779,7 +5774,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45923</v>
+        <v>45254</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5852,7 +5847,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5866,10 +5861,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45923</v>
+        <v>44782</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5882,7 +5877,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5925,7 +5920,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5939,10 +5934,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45643</v>
+        <v>45923</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5955,7 +5950,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5998,7 +5993,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44981</v>
+        <v>45923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6028,7 +6023,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6071,7 +6066,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6085,10 +6080,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45112</v>
+        <v>46056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6100,13 +6095,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6149,7 +6139,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6159,14 +6149,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45167</v>
+        <v>46056</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6179,7 +6169,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6222,7 +6212,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6236,10 +6226,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45602</v>
+        <v>45215</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6252,7 +6242,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6295,7 +6285,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6309,10 +6299,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45142</v>
+        <v>45643</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6325,7 +6315,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6368,7 +6358,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6382,10 +6372,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45938</v>
+        <v>45854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6397,8 +6387,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6441,7 +6436,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6455,10 +6450,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45596</v>
+        <v>45735</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6471,7 +6466,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6514,7 +6509,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6528,10 +6523,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45943</v>
+        <v>45615</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6544,7 +6539,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6587,7 +6582,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6601,10 +6596,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46086</v>
+        <v>45938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6617,7 +6612,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6660,7 +6655,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6677,7 +6672,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6690,7 +6685,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6733,7 +6728,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6747,10 +6742,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45950</v>
+        <v>45943</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6763,7 +6758,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6806,7 +6801,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6820,10 +6815,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45198</v>
+        <v>45000</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6836,7 +6831,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6879,7 +6874,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6889,14 +6884,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46104</v>
+        <v>46086</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6909,7 +6904,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6952,7 +6947,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6962,14 +6957,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45484</v>
+        <v>45950</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6982,7 +6977,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7025,7 +7020,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7039,10 +7034,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45993</v>
+        <v>45642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7055,7 +7050,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7098,7 +7093,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7112,10 +7107,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45028</v>
+        <v>45369</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7128,7 +7123,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7171,7 +7166,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7185,10 +7180,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45167</v>
+        <v>44508</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7201,7 +7196,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7244,7 +7239,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7258,10 +7253,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45167</v>
+        <v>45009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7274,7 +7269,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7317,7 +7312,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7327,14 +7322,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45265</v>
+        <v>46104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7346,13 +7341,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7395,7 +7385,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7409,10 +7399,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45369</v>
+        <v>45010</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7425,7 +7415,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7468,7 +7458,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7482,10 +7472,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46019</v>
+        <v>45621</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7498,7 +7488,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7541,7 +7531,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7555,10 +7545,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45113</v>
+        <v>45596</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7571,7 +7561,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7631,7 +7621,7 @@
         <v>45911</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7687,7 +7677,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7701,10 +7691,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45257</v>
+        <v>45993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7717,7 +7707,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7760,7 +7750,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7774,10 +7764,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45799</v>
+        <v>45113</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7790,7 +7780,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7833,7 +7823,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7847,10 +7837,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44957</v>
+        <v>45390</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7863,7 +7853,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7906,7 +7896,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7920,10 +7910,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46042</v>
+        <v>45265</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7935,8 +7925,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7979,7 +7974,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7993,10 +7988,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45161</v>
+        <v>45799</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,7 +8004,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8052,7 +8047,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8066,10 +8061,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46056</v>
+        <v>44560</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8082,7 +8077,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8125,7 +8120,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8139,10 +8134,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45000</v>
+        <v>45257</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8155,7 +8150,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>7.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8198,7 +8193,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8208,14 +8203,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46056</v>
+        <v>44963</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8228,7 +8223,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8271,7 +8266,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8285,10 +8280,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45615</v>
+        <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8344,7 +8339,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8358,10 +8353,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45557</v>
+        <v>44894</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8374,7 +8369,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>11.5</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8417,7 +8412,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8431,10 +8426,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45349</v>
+        <v>45882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8447,7 +8442,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8490,7 +8485,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8504,10 +8499,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45882</v>
+        <v>46161</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8520,7 +8515,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8563,7 +8558,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8577,10 +8572,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45229</v>
+        <v>45946</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8593,7 +8588,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8636,7 +8631,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8650,10 +8645,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8666,7 +8661,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8709,7 +8704,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8723,10 +8718,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45665</v>
+        <v>46244</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8738,8 +8733,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8782,7 +8782,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45946</v>
+        <v>45485</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8855,7 +8855,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45642</v>
+        <v>46244</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8884,8 +8884,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8928,7 +8933,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8942,10 +8947,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45615</v>
+        <v>46244</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8957,8 +8962,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9001,7 +9011,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9015,10 +9025,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45198</v>
+        <v>46244</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9030,8 +9040,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9074,7 +9089,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9088,10 +9103,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45390</v>
+        <v>46244</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9103,8 +9118,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9147,7 +9167,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9161,10 +9181,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45643</v>
+        <v>46205</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9177,7 +9197,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9220,7 +9240,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9234,10 +9254,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46181</v>
+        <v>45112</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9249,8 +9269,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9293,7 +9318,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9307,10 +9332,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45237</v>
+        <v>46205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9323,7 +9348,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9366,7 +9391,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9380,10 +9405,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44894</v>
+        <v>46205</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9396,7 +9421,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9439,7 +9464,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9453,10 +9478,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44697</v>
+        <v>46252</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9469,7 +9494,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9512,7 +9537,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9526,10 +9551,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44963</v>
+        <v>45146</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9542,7 +9567,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9585,7 +9610,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9599,10 +9624,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46244</v>
+        <v>44616</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9614,13 +9639,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9663,7 +9683,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9677,10 +9697,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46244</v>
+        <v>46262</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9692,13 +9712,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9741,7 +9756,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9755,10 +9770,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44745</v>
+        <v>44614</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9770,8 +9785,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9814,7 +9834,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9828,10 +9848,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46244</v>
+        <v>44980</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9843,13 +9863,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9892,7 +9907,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9906,10 +9921,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44508</v>
+        <v>46269</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9921,8 +9936,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9965,7 +9985,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9979,10 +9999,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46244</v>
+        <v>45557</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9994,13 +10014,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10043,7 +10058,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10057,10 +10072,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46244</v>
+        <v>45615</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10072,13 +10087,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10121,7 +10131,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10135,10 +10145,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44951</v>
+        <v>45198</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10151,7 +10161,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10194,7 +10204,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10208,10 +10218,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44963</v>
+        <v>45229</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10224,7 +10234,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10267,7 +10277,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10281,10 +10291,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46205</v>
+        <v>44957</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10297,7 +10307,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10340,7 +10350,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10354,10 +10364,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46205</v>
+        <v>45349</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10370,7 +10380,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10413,7 +10423,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10427,10 +10437,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45010</v>
+        <v>44963</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10443,7 +10453,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10486,7 +10496,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10500,10 +10510,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46205</v>
+        <v>45699</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10516,7 +10526,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10559,7 +10569,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10573,10 +10583,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44616</v>
+        <v>45468</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10589,7 +10599,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10632,7 +10642,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10646,10 +10656,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44537</v>
+        <v>44853</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10662,7 +10672,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10705,7 +10715,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10719,10 +10729,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45621</v>
+        <v>44606</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10735,7 +10745,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10778,7 +10788,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10792,10 +10802,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46252</v>
+        <v>45665</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10808,7 +10818,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10851,7 +10861,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10865,10 +10875,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44614</v>
+        <v>44745</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10880,13 +10890,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10929,7 +10934,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10943,10 +10948,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45009</v>
+        <v>45699</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10959,7 +10964,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11002,7 +11007,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11012,14 +11017,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45167</v>
+        <v>45091</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11031,8 +11036,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11075,7 +11085,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11089,10 +11099,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45146</v>
+        <v>44939</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11105,7 +11115,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11148,7 +11158,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11162,10 +11172,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44606</v>
+        <v>44939</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11178,7 +11188,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>11.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11221,7 +11231,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11235,10 +11245,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45091</v>
+        <v>44615</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11250,13 +11260,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>9.4</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11299,7 +11304,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11313,10 +11318,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45582</v>
+        <v>44697</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11329,7 +11334,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11372,7 +11377,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11386,10 +11391,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46262</v>
+        <v>45161</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11402,7 +11407,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11445,7 +11450,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11459,10 +11464,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44980</v>
+        <v>45602</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11475,7 +11480,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11518,7 +11523,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11532,10 +11537,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46269</v>
+        <v>44537</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11547,13 +11552,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11596,7 +11596,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11610,10 +11610,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45699</v>
+        <v>45167</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11669,7 +11669,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44560</v>
+        <v>45028</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45485</v>
+        <v>45167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11832,7 +11832,7 @@
         <v>45266</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11902,10 +11902,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45553</v>
+        <v>45209</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11961,7 +11961,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45470</v>
+        <v>45390</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11990,13 +11990,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>7.1</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12039,7 +12034,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12049,14 +12044,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45538</v>
+        <v>45197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12069,7 +12064,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12112,7 +12107,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12122,14 +12117,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45771</v>
+        <v>45484</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12142,7 +12137,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12185,7 +12180,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12195,14 +12190,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45351</v>
+        <v>44951</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12215,7 +12210,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12258,7 +12253,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12272,10 +12267,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45643</v>
+        <v>44810</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12288,7 +12283,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12331,7 +12326,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12345,10 +12340,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45797</v>
+        <v>45553</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12361,7 +12356,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12404,7 +12399,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12418,10 +12413,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45805</v>
+        <v>45771</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12434,7 +12429,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12477,7 +12472,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12491,10 +12486,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45805</v>
+        <v>45470</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12506,8 +12501,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12550,7 +12550,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12564,10 +12564,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45685</v>
+        <v>45538</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12640,7 +12640,7 @@
         <v>44607</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44735</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46269</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>46269</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44593</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1151,14 +1151,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46244</v>
+        <v>45468</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,29 +1170,24 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
@@ -1200,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1216,35 +1211,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1263,7 @@
         <v>46244</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1361,7 +1356,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 33003-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1375,10 +1370,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1390,8 +1385,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1431,248 +1431,248 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 34275-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 34277-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46253</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.8</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 26270-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45468</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44866</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7786-2022</t>
+          <t>A 63257-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3005,14 +3005,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44608</v>
+        <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63257-2021</t>
+          <t>A 7786-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3078,14 +3078,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44508</v>
+        <v>44608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3158,7 +3158,7 @@
         <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44456</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12726-2022</t>
+          <t>A 7231-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44641</v>
+        <v>44606</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47656-2022</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3370,14 +3370,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44854</v>
+        <v>45300</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50738-2021</t>
+          <t>A 12726-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44456</v>
+        <v>44641</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7231-2022</t>
+          <t>A 32219-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44606</v>
+        <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32219-2022</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44781</v>
+        <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3669,7 +3669,7 @@
         <v>44714</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56175-2021</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44477</v>
+        <v>44782</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12544-2022</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44638</v>
+        <v>45215</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9184-2022</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44615</v>
+        <v>45209</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9210-2022</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44616</v>
+        <v>45198</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44922</v>
+        <v>45390</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4090,7 +4090,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 56175-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>44477</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 12544-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45069</v>
+        <v>44638</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4192,13 +4192,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4241,7 +4236,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 9184-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4255,10 +4250,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45582</v>
+        <v>44615</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4271,7 +4266,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4314,7 +4309,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 47656-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4328,10 +4323,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45198</v>
+        <v>44854</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4387,7 +4382,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 50738-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4401,10 +4396,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45198</v>
+        <v>44456</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4417,7 +4412,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4460,7 +4455,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 9210-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4474,10 +4469,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45167</v>
+        <v>44616</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4490,7 +4485,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4533,7 +4528,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4543,14 +4538,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45167</v>
+        <v>45186</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4563,7 +4558,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4606,7 +4601,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4620,10 +4615,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45573</v>
+        <v>45468</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4636,7 +4631,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4679,7 +4674,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4689,14 +4684,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45300</v>
+        <v>45643</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4709,7 +4704,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4752,7 +4747,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4762,14 +4757,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45351</v>
+        <v>45237</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4782,7 +4777,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4825,7 +4820,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45797</v>
+        <v>44853</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4855,7 +4850,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4898,7 +4893,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4912,10 +4907,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45643</v>
+        <v>44894</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4928,7 +4923,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4971,7 +4966,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4985,10 +4980,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45805</v>
+        <v>46086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5001,7 +4996,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5044,7 +5039,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5058,10 +5053,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45805</v>
+        <v>44939</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5074,7 +5069,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5117,7 +5112,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5131,10 +5126,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45685</v>
+        <v>44945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5147,7 +5142,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5190,7 +5185,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5200,14 +5195,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46019</v>
+        <v>44922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5220,7 +5215,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5263,7 +5258,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5273,14 +5268,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44935</v>
+        <v>46104</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5293,7 +5288,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5336,7 +5331,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5346,14 +5341,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45186</v>
+        <v>44697</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5366,7 +5361,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5409,7 +5404,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5423,10 +5418,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44981</v>
+        <v>44939</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5439,7 +5434,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5482,7 +5477,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5496,10 +5491,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45142</v>
+        <v>44935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5512,7 +5507,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5555,7 +5550,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5569,10 +5564,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46042</v>
+        <v>45390</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5628,7 +5623,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5638,14 +5633,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44945</v>
+        <v>45197</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5658,7 +5653,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5701,7 +5696,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5715,10 +5710,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45826</v>
+        <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5731,7 +5726,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5774,7 +5769,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5788,10 +5783,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45254</v>
+        <v>45923</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5804,7 +5799,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5847,7 +5842,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5861,10 +5856,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44782</v>
+        <v>45923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5877,7 +5872,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5920,7 +5915,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45923</v>
+        <v>45198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5950,7 +5945,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5993,7 +5988,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6007,10 +6002,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45923</v>
+        <v>44963</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6023,7 +6018,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6066,7 +6061,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6080,10 +6075,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46056</v>
+        <v>45938</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6096,7 +6091,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6139,7 +6134,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6149,14 +6144,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46056</v>
+        <v>45943</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6169,7 +6164,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.3</v>
+        <v>4.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6212,7 +6207,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6226,10 +6221,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45215</v>
+        <v>45265</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6241,8 +6236,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45643</v>
+        <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45854</v>
+        <v>45069</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45735</v>
+        <v>45950</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45615</v>
+        <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45938</v>
+        <v>45113</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45943</v>
+        <v>45911</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45943</v>
+        <v>45257</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45000</v>
+        <v>45799</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46086</v>
+        <v>45573</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45950</v>
+        <v>45643</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45642</v>
+        <v>44745</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45369</v>
+        <v>44508</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44508</v>
+        <v>44981</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45009</v>
+        <v>45112</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7268,8 +7268,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7312,7 +7317,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7322,14 +7327,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46104</v>
+        <v>45167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7342,7 +7347,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7385,7 +7390,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7399,10 +7404,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45010</v>
+        <v>44951</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7415,7 +7420,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7458,7 +7463,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7472,10 +7477,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45621</v>
+        <v>45602</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7488,7 +7493,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7531,7 +7536,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7545,10 +7550,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45596</v>
+        <v>45142</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7561,7 +7566,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7604,7 +7609,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7618,10 +7623,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45911</v>
+        <v>45596</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7634,7 +7639,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7694,7 +7699,7 @@
         <v>45993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7750,7 +7755,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7764,10 +7769,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45113</v>
+        <v>44963</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7780,7 +7785,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7823,7 +7828,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7837,10 +7842,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45390</v>
+        <v>45198</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7853,7 +7858,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7896,7 +7901,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7906,14 +7911,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45265</v>
+        <v>45484</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7925,13 +7930,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45799</v>
+        <v>45010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44560</v>
+        <v>45882</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45257</v>
+        <v>46019</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8207,10 +8207,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44963</v>
+        <v>44616</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45237</v>
+        <v>46161</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8339,7 +8339,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44894</v>
+        <v>45946</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8412,7 +8412,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45882</v>
+        <v>44537</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8485,7 +8485,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46161</v>
+        <v>46042</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8572,10 +8572,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45946</v>
+        <v>45621</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8645,10 +8645,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46181</v>
+        <v>45028</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8704,7 +8704,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46244</v>
+        <v>45167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8733,13 +8733,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8782,7 +8777,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8796,10 +8791,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45485</v>
+        <v>45167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8812,7 +8807,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8855,7 +8850,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8869,10 +8864,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46244</v>
+        <v>46056</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8884,13 +8879,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8933,7 +8923,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8943,14 +8933,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46244</v>
+        <v>46056</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8962,13 +8952,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9011,7 +8996,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9025,10 +9010,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46244</v>
+        <v>46181</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9040,13 +9025,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9089,7 +9069,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9103,10 +9083,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46244</v>
+        <v>45369</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9118,13 +9098,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9167,7 +9142,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9181,10 +9156,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46205</v>
+        <v>44614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9196,8 +9171,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9240,7 +9220,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9254,10 +9234,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45112</v>
+        <v>44957</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9269,13 +9249,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9318,7 +9293,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9332,10 +9307,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46205</v>
+        <v>45161</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9323,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9391,7 +9366,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9405,10 +9380,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46205</v>
+        <v>45009</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9396,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9464,7 +9439,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9474,14 +9449,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46252</v>
+        <v>45167</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9494,7 +9469,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9554,7 +9529,7 @@
         <v>45146</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9610,7 +9585,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9624,10 +9599,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44616</v>
+        <v>44606</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9640,7 +9615,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9683,7 +9658,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9697,10 +9672,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46262</v>
+        <v>45000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9713,7 +9688,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9756,7 +9731,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9770,10 +9745,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44614</v>
+        <v>45091</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9787,11 +9762,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9834,7 +9809,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9848,10 +9823,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44980</v>
+        <v>46244</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9863,8 +9838,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9907,7 +9887,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9921,10 +9901,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46269</v>
+        <v>46244</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9942,7 +9922,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9985,7 +9965,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9999,10 +9979,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45557</v>
+        <v>46244</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10014,8 +9994,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>11.5</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10058,7 +10043,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10072,10 +10057,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45615</v>
+        <v>46244</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10087,8 +10072,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10131,7 +10121,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10145,10 +10135,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45198</v>
+        <v>46244</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10160,8 +10150,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10204,7 +10199,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10218,10 +10213,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45229</v>
+        <v>45615</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10234,7 +10229,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10277,7 +10272,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10291,10 +10286,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44957</v>
+        <v>45582</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10307,7 +10302,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10350,7 +10345,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10364,10 +10359,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45349</v>
+        <v>45557</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10380,7 +10375,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10423,7 +10418,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10437,10 +10432,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44963</v>
+        <v>46205</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10453,7 +10448,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10496,7 +10491,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10510,10 +10505,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45699</v>
+        <v>45349</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10526,7 +10521,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10569,7 +10564,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10583,10 +10578,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45468</v>
+        <v>46205</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10599,7 +10594,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10642,7 +10637,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10656,10 +10651,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44853</v>
+        <v>46205</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10672,7 +10667,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10715,7 +10710,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10729,10 +10724,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44606</v>
+        <v>46252</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10745,7 +10740,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10788,7 +10783,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10802,10 +10797,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45665</v>
+        <v>45229</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10818,7 +10813,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10861,7 +10856,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10875,10 +10870,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44745</v>
+        <v>44980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10891,7 +10886,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10934,7 +10929,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10948,10 +10943,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45699</v>
+        <v>45665</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10964,7 +10959,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11007,7 +11002,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11021,10 +11016,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45091</v>
+        <v>45642</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11036,13 +11031,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>9.4</v>
+        <v>2.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11085,7 +11075,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11099,10 +11089,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44939</v>
+        <v>45615</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11115,7 +11105,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11158,7 +11148,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11172,10 +11162,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44939</v>
+        <v>46262</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11188,7 +11178,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>11.6</v>
+        <v>4.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11231,7 +11221,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11245,10 +11235,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44615</v>
+        <v>45699</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11261,7 +11251,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11304,7 +11294,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11318,10 +11308,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44697</v>
+        <v>46269</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11331,6 +11321,11 @@
       <c r="G142" t="inlineStr">
         <is>
           <t>HJO</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -11377,7 +11372,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11391,10 +11386,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45161</v>
+        <v>44560</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11407,7 +11402,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11450,7 +11445,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11464,10 +11459,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45602</v>
+        <v>45485</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11480,7 +11475,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11523,7 +11518,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11537,10 +11532,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44537</v>
+        <v>45266</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11553,7 +11548,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11596,7 +11591,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11610,10 +11605,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45167</v>
+        <v>45553</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11626,7 +11621,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11669,7 +11664,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11683,10 +11678,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45028</v>
+        <v>45470</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11698,8 +11693,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>3.1</v>
+        <v>7.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45167</v>
+        <v>45538</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11815,7 +11815,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11829,10 +11829,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45266</v>
+        <v>45771</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11888,7 +11888,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11898,14 +11898,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45209</v>
+        <v>45351</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.4</v>
+        <v>7.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11961,7 +11961,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45390</v>
+        <v>45643</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12034,7 +12034,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12044,14 +12044,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45197</v>
+        <v>45797</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12107,7 +12107,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12117,14 +12117,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45484</v>
+        <v>45805</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12180,7 +12180,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44951</v>
+        <v>45805</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12253,7 +12253,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12267,10 +12267,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44810</v>
+        <v>45685</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12326,7 +12326,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12340,10 +12340,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45553</v>
+        <v>45826</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12399,7 +12399,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12413,10 +12413,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45771</v>
+        <v>45254</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12472,7 +12472,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12486,10 +12486,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45470</v>
+        <v>45854</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12503,11 +12503,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12550,7 +12550,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12564,10 +12564,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45538</v>
+        <v>45735</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12640,7 +12640,7 @@
         <v>44607</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44735</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46269</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>46269</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44593</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26270-2024</t>
+          <t>A 33003-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1151,14 +1151,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45468</v>
+        <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,14 +1170,19 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1186,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1195,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1211,35 +1216,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
@@ -1263,7 +1268,7 @@
         <v>46244</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1356,7 +1361,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 34275-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1385,13 +1390,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1431,42 +1431,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 34277-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1483,7 +1483,7 @@
         <v>46253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1540,38 +1540,38 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34277-2026</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46253</v>
+        <v>45468</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1601,23 +1601,23 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -1625,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1641,35 +1641,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
         <v>45719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44866</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7786-2022</t>
+          <t>A 32814-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3078,14 +3078,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44608</v>
+        <v>44784</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3141,7 +3141,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32814-2022</t>
+          <t>A 7786-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44784</v>
+        <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>44456</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7231-2022</t>
+          <t>A 12726-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44606</v>
+        <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 47656-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3370,14 +3370,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45300</v>
+        <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12726-2022</t>
+          <t>A 50738-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44641</v>
+        <v>44456</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32219-2022</t>
+          <t>A 7231-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44781</v>
+        <v>44606</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 32219-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44810</v>
+        <v>44781</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3669,7 +3669,7 @@
         <v>44714</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 56175-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44782</v>
+        <v>44477</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 12544-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45215</v>
+        <v>44638</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 9184-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45209</v>
+        <v>44615</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 9210-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45198</v>
+        <v>44616</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45390</v>
+        <v>44922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4090,7 +4090,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56175-2021</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44477</v>
+        <v>45069</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4119,8 +4119,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4163,7 +4168,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12544-2022</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4177,10 +4182,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44638</v>
+        <v>45643</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4193,7 +4198,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4236,7 +4241,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9184-2022</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44615</v>
+        <v>45582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4266,7 +4271,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4309,7 +4314,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47656-2022</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4323,10 +4328,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44854</v>
+        <v>45198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4382,7 +4387,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50738-2021</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4396,10 +4401,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44456</v>
+        <v>45198</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4412,7 +4417,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4455,7 +4460,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9210-2022</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4469,10 +4474,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44616</v>
+        <v>45573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4485,7 +4490,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4528,7 +4533,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4538,14 +4543,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45186</v>
+        <v>45167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4558,7 +4563,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4601,7 +4606,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4615,10 +4620,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45468</v>
+        <v>45167</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4631,7 +4636,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4674,7 +4679,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4684,14 +4689,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45643</v>
+        <v>45300</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4704,7 +4709,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4747,7 +4752,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4761,10 +4766,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45237</v>
+        <v>44935</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4777,7 +4782,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4820,7 +4825,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4830,14 +4835,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44853</v>
+        <v>45186</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4850,7 +4855,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4893,7 +4898,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4907,10 +4912,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44894</v>
+        <v>44981</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4923,7 +4928,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4966,7 +4971,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46086</v>
+        <v>45142</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4996,7 +5001,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5039,7 +5044,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5053,10 +5058,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44939</v>
+        <v>45805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5069,7 +5074,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>11.6</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5112,7 +5117,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44945</v>
+        <v>45805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5142,7 +5147,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5185,7 +5190,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5195,14 +5200,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44922</v>
+        <v>45685</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5215,7 +5220,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5258,7 +5263,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5268,14 +5273,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46104</v>
+        <v>44945</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5288,7 +5293,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5331,7 +5336,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5345,10 +5350,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44697</v>
+        <v>44782</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5361,7 +5366,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5404,7 +5409,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5418,10 +5423,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44939</v>
+        <v>45826</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5477,7 +5482,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5491,10 +5496,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44935</v>
+        <v>45254</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5507,7 +5512,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5550,7 +5555,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5564,10 +5569,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45390</v>
+        <v>45215</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5580,7 +5585,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5623,7 +5628,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5633,14 +5638,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45197</v>
+        <v>45643</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5653,7 +5658,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5696,7 +5701,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5710,10 +5715,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44615</v>
+        <v>45615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5726,7 +5731,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5769,7 +5774,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5786,7 +5791,7 @@
         <v>45923</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5799,7 +5804,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5842,7 +5847,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5859,7 +5864,7 @@
         <v>45923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5872,7 +5877,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5915,7 +5920,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5929,10 +5934,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45198</v>
+        <v>45000</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5945,7 +5950,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5988,7 +5993,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6002,10 +6007,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44963</v>
+        <v>45854</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6017,8 +6022,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6061,7 +6071,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6075,10 +6085,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45938</v>
+        <v>45642</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6091,7 +6101,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6134,7 +6144,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6148,10 +6158,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45943</v>
+        <v>45735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6164,7 +6174,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6207,7 +6217,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6221,10 +6231,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45265</v>
+        <v>45369</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6236,13 +6246,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6285,7 +6290,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6299,10 +6304,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45943</v>
+        <v>46042</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6315,7 +6320,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6358,7 +6363,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45069</v>
+        <v>44508</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6387,13 +6392,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45950</v>
+        <v>45938</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45699</v>
+        <v>45943</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45113</v>
+        <v>45943</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45911</v>
+        <v>45009</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45257</v>
+        <v>45950</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45799</v>
+        <v>46056</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45573</v>
+        <v>46056</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>6.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45643</v>
+        <v>45010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44745</v>
+        <v>45621</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44508</v>
+        <v>45596</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44981</v>
+        <v>45390</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45112</v>
+        <v>45993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7268,13 +7268,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7317,7 +7312,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7331,10 +7326,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45167</v>
+        <v>46086</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7347,7 +7342,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7390,7 +7385,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7404,10 +7399,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44951</v>
+        <v>44560</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7420,7 +7415,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7463,7 +7458,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7477,10 +7472,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45602</v>
+        <v>44963</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7493,7 +7488,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7536,7 +7531,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7550,10 +7545,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45142</v>
+        <v>45237</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7566,7 +7561,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7609,7 +7604,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7623,10 +7618,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45596</v>
+        <v>44894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7639,7 +7634,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7682,7 +7677,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7696,10 +7691,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45993</v>
+        <v>46019</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7712,7 +7707,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7755,7 +7750,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7765,14 +7760,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44963</v>
+        <v>46104</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7785,7 +7780,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7828,7 +7823,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7842,10 +7837,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45198</v>
+        <v>45485</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7858,7 +7853,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7901,7 +7896,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7911,14 +7906,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45484</v>
+        <v>45112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7928,6 +7923,11 @@
       <c r="G96" t="inlineStr">
         <is>
           <t>HJO</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -7974,7 +7974,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45010</v>
+        <v>45911</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45882</v>
+        <v>45146</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46019</v>
+        <v>44616</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8207,10 +8207,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44616</v>
+        <v>44614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8222,8 +8222,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8266,7 +8271,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8280,10 +8285,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46161</v>
+        <v>45113</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8296,7 +8301,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8339,7 +8344,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8353,10 +8358,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45946</v>
+        <v>44980</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8369,7 +8374,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8412,7 +8417,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8426,10 +8431,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44537</v>
+        <v>45265</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8441,8 +8446,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8485,7 +8495,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8499,10 +8509,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46042</v>
+        <v>45799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8515,7 +8525,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8558,7 +8568,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8572,10 +8582,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45621</v>
+        <v>45557</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8588,7 +8598,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>11.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8631,7 +8641,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8645,10 +8655,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45028</v>
+        <v>45257</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8661,7 +8671,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8704,7 +8714,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8718,10 +8728,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45167</v>
+        <v>45615</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8777,7 +8787,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8791,10 +8801,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45167</v>
+        <v>45882</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8807,7 +8817,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8850,7 +8860,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8864,10 +8874,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46056</v>
+        <v>45198</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8880,7 +8890,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8923,7 +8933,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8933,14 +8943,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46056</v>
+        <v>45229</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8953,7 +8963,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8996,7 +9006,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9010,10 +9020,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46181</v>
+        <v>46161</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9026,7 +9036,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9069,7 +9079,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9083,10 +9093,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45369</v>
+        <v>44957</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9099,7 +9109,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9142,7 +9152,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9156,10 +9166,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44614</v>
+        <v>45349</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9171,13 +9181,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9220,7 +9225,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9234,10 +9239,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44957</v>
+        <v>45946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9250,7 +9255,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9293,7 +9298,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9307,10 +9312,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45161</v>
+        <v>44963</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9323,7 +9328,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9366,7 +9371,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9380,10 +9385,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45009</v>
+        <v>45699</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9396,7 +9401,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9439,7 +9444,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9449,14 +9454,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45167</v>
+        <v>45468</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9469,7 +9474,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9512,7 +9517,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9526,10 +9531,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45146</v>
+        <v>44853</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9542,7 +9547,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9602,7 +9607,7 @@
         <v>44606</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9658,7 +9663,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9672,10 +9677,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45000</v>
+        <v>45665</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9688,7 +9693,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9731,7 +9736,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9745,10 +9750,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45091</v>
+        <v>46181</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9760,13 +9765,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9809,7 +9809,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46244</v>
+        <v>44745</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9838,13 +9838,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9887,7 +9882,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9901,10 +9896,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46244</v>
+        <v>45699</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9916,13 +9911,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9965,7 +9955,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9979,10 +9969,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46244</v>
+        <v>45091</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10000,7 +9990,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>9.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10043,7 +10033,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10057,10 +10047,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46244</v>
+        <v>44939</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10072,13 +10062,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10121,7 +10106,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10135,10 +10120,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46244</v>
+        <v>44939</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10150,13 +10135,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>11.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10199,7 +10179,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10213,10 +10193,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45615</v>
+        <v>44615</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10209,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10272,7 +10252,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10286,10 +10266,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45582</v>
+        <v>46244</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10301,8 +10281,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10345,7 +10330,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10359,10 +10344,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45557</v>
+        <v>46244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10374,8 +10359,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10418,7 +10408,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10432,10 +10422,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10447,8 +10437,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10491,7 +10486,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10505,10 +10500,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45349</v>
+        <v>46244</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10520,8 +10515,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10564,7 +10564,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10593,8 +10593,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10637,7 +10642,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10651,10 +10656,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46205</v>
+        <v>44697</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10710,7 +10715,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10724,10 +10729,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46252</v>
+        <v>46205</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10740,7 +10745,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10783,7 +10788,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10797,10 +10802,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45229</v>
+        <v>45161</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10813,7 +10818,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10856,7 +10861,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10870,10 +10875,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44980</v>
+        <v>45602</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10886,7 +10891,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10929,7 +10934,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10943,10 +10948,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45665</v>
+        <v>44537</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10959,7 +10964,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11002,7 +11007,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11016,10 +11021,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45642</v>
+        <v>45167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11032,7 +11037,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11075,7 +11080,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11089,10 +11094,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45615</v>
+        <v>46205</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11105,7 +11110,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11148,7 +11153,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11162,10 +11167,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46262</v>
+        <v>46205</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11178,7 +11183,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11221,7 +11226,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11235,10 +11240,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45699</v>
+        <v>46252</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11251,7 +11256,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11294,7 +11299,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11308,10 +11313,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46269</v>
+        <v>45028</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11323,13 +11328,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11382,14 +11382,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44560</v>
+        <v>45167</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11459,10 +11459,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45485</v>
+        <v>45266</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45266</v>
+        <v>45209</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45553</v>
+        <v>46262</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11664,7 +11664,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11678,10 +11678,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45470</v>
+        <v>45390</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11693,13 +11693,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>7.1</v>
+        <v>2.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11742,7 +11737,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11752,14 +11747,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45538</v>
+        <v>45197</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11772,7 +11767,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11815,7 +11810,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11825,14 +11820,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45771</v>
+        <v>45484</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11845,7 +11840,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11888,7 +11883,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11898,14 +11893,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45351</v>
+        <v>44951</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11918,7 +11913,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11961,7 +11956,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11975,10 +11970,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45643</v>
+        <v>46269</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11990,8 +11985,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12034,7 +12034,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12048,10 +12048,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45797</v>
+        <v>44810</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12107,7 +12107,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12121,10 +12121,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45805</v>
+        <v>45553</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12180,7 +12180,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45805</v>
+        <v>45771</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12253,7 +12253,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12267,10 +12267,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45685</v>
+        <v>45470</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12282,8 +12282,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12326,7 +12331,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12340,10 +12345,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45826</v>
+        <v>45538</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12356,7 +12361,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12399,7 +12404,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12409,14 +12414,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45254</v>
+        <v>45351</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12429,7 +12434,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12472,7 +12477,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12486,10 +12491,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45854</v>
+        <v>45797</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12501,13 +12506,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12550,7 +12550,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12564,10 +12564,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45735</v>
+        <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12640,7 +12640,7 @@
         <v>44607</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44735</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE161"/>
+  <dimension ref="A1:AE159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46269</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>46269</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44593</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1158,7 +1158,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1220,144 +1220,144 @@
         </is>
       </c>
       <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 33003-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>46253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>46253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45468</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44866</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32814-2022</t>
+          <t>A 7786-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3078,14 +3078,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44784</v>
+        <v>44608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3141,7 +3141,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7786-2022</t>
+          <t>A 32814-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44608</v>
+        <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3214,7 +3214,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 50783-2021</t>
+          <t>A 12726-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44456</v>
+        <v>44641</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3287,7 +3287,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12726-2022</t>
+          <t>A 47656-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44641</v>
+        <v>44854</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47656-2022</t>
+          <t>A 7231-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44854</v>
+        <v>44606</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50738-2021</t>
+          <t>A 32219-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44456</v>
+        <v>44781</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7231-2022</t>
+          <t>A 22586-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44606</v>
+        <v>44714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32219-2022</t>
+          <t>A 56175-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44781</v>
+        <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3652,7 +3652,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22586-2022</t>
+          <t>A 12544-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44714</v>
+        <v>44638</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56175-2021</t>
+          <t>A 9184-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44477</v>
+        <v>44615</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12544-2022</t>
+          <t>A 9210-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44638</v>
+        <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9184-2022</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3881,14 +3881,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44615</v>
+        <v>45186</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9210-2022</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3954,14 +3954,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44616</v>
+        <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44922</v>
+        <v>45215</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4090,7 +4090,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45069</v>
+        <v>44810</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4117,11 +4117,6 @@
       <c r="G44" t="inlineStr">
         <is>
           <t>HJO</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -4168,7 +4163,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4182,10 +4177,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45643</v>
+        <v>45209</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4198,7 +4193,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4241,7 +4236,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4255,10 +4250,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45582</v>
+        <v>44782</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4271,7 +4266,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4314,7 +4309,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4328,10 +4323,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45198</v>
+        <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4344,7 +4339,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4387,7 +4382,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4401,10 +4396,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45198</v>
+        <v>44853</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4417,7 +4412,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4460,7 +4455,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4474,10 +4469,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45573</v>
+        <v>44939</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4490,7 +4485,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>11.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4533,7 +4528,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4547,10 +4542,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45167</v>
+        <v>44945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4606,7 +4601,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4616,14 +4611,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45167</v>
+        <v>44922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4636,7 +4631,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4679,7 +4674,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4689,14 +4684,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45300</v>
+        <v>44939</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4709,7 +4704,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4769,7 +4764,7 @@
         <v>44935</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4825,7 +4820,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45186</v>
+        <v>45197</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4855,7 +4850,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4898,7 +4893,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4912,10 +4907,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44981</v>
+        <v>45390</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4928,7 +4923,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4971,7 +4966,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4985,10 +4980,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45142</v>
+        <v>44615</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5001,7 +4996,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5044,7 +5039,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5058,10 +5053,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45805</v>
+        <v>45198</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5074,7 +5069,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5117,7 +5112,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5131,10 +5126,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45805</v>
+        <v>45826</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5147,7 +5142,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5190,7 +5185,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5204,10 +5199,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45685</v>
+        <v>45254</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5220,7 +5215,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5263,7 +5258,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5277,10 +5272,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44945</v>
+        <v>45069</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5292,8 +5287,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44782</v>
+        <v>46086</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45826</v>
+        <v>45699</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45254</v>
+        <v>45854</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5511,8 +5511,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5555,7 +5560,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5565,14 +5570,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45215</v>
+        <v>46104</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5585,7 +5590,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5628,7 +5633,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5642,10 +5647,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45643</v>
+        <v>45573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5658,7 +5663,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5701,7 +5706,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45615</v>
+        <v>45735</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5731,7 +5736,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5774,7 +5779,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5788,10 +5793,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45923</v>
+        <v>45643</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5804,7 +5809,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5847,7 +5852,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5861,10 +5866,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45923</v>
+        <v>44981</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5877,7 +5882,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5920,7 +5925,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5934,10 +5939,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45000</v>
+        <v>45112</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,8 +5954,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5993,7 +6003,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6007,10 +6017,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45854</v>
+        <v>45167</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6022,13 +6032,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6071,7 +6076,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6085,10 +6090,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45642</v>
+        <v>45602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6101,7 +6106,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6144,7 +6149,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6158,10 +6163,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45735</v>
+        <v>45142</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6174,7 +6179,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6217,7 +6222,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6231,10 +6236,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45369</v>
+        <v>45596</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6247,7 +6252,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6290,7 +6295,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6304,10 +6309,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46042</v>
+        <v>45265</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6319,8 +6324,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6363,7 +6373,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6377,10 +6387,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44508</v>
+        <v>45198</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6393,7 +6403,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6436,7 +6446,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6446,14 +6456,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45938</v>
+        <v>45484</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6466,7 +6476,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6509,7 +6519,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6523,10 +6533,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45943</v>
+        <v>45113</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6539,7 +6549,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6582,7 +6592,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6596,10 +6606,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45943</v>
+        <v>45911</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6612,7 +6622,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6655,7 +6665,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6669,10 +6679,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45009</v>
+        <v>45257</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6685,7 +6695,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6728,7 +6738,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6742,10 +6752,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45950</v>
+        <v>45799</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6758,7 +6768,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6801,7 +6811,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6815,10 +6825,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46056</v>
+        <v>45923</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6831,7 +6841,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6874,7 +6884,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6884,14 +6894,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46056</v>
+        <v>45923</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6904,7 +6914,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6947,7 +6957,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6961,10 +6971,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45010</v>
+        <v>45028</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6977,7 +6987,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7020,7 +7030,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7034,10 +7044,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45621</v>
+        <v>45167</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7050,7 +7060,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7093,7 +7103,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7107,10 +7117,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45596</v>
+        <v>45167</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7123,7 +7133,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7166,7 +7176,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7180,10 +7190,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45390</v>
+        <v>45369</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7196,7 +7206,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7239,7 +7249,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7253,10 +7263,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45993</v>
+        <v>45882</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7269,7 +7279,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7312,7 +7322,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7326,10 +7336,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46086</v>
+        <v>45938</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7342,7 +7352,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7385,7 +7395,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7399,10 +7409,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44560</v>
+        <v>44957</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7415,7 +7425,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7458,7 +7468,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7472,10 +7482,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44963</v>
+        <v>45943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7488,7 +7498,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7531,7 +7541,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7545,10 +7555,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45237</v>
+        <v>46161</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7561,7 +7571,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7604,7 +7614,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7618,10 +7628,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44894</v>
+        <v>45161</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7634,7 +7644,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7677,7 +7687,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7691,10 +7701,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46019</v>
+        <v>45943</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7707,7 +7717,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7750,7 +7760,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7760,14 +7770,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46104</v>
+        <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7780,7 +7790,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7823,7 +7833,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7837,10 +7847,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45485</v>
+        <v>45000</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7853,7 +7863,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7896,7 +7906,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7910,10 +7920,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45112</v>
+        <v>45950</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7925,13 +7935,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7974,7 +7979,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7988,10 +7993,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45911</v>
+        <v>45615</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8004,7 +8009,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8047,7 +8052,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8061,10 +8066,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45146</v>
+        <v>46181</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8077,7 +8082,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8120,7 +8125,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8134,10 +8139,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44616</v>
+        <v>45557</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8150,7 +8155,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8193,7 +8198,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8207,10 +8212,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44614</v>
+        <v>45349</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8222,13 +8227,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8271,7 +8271,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45113</v>
+        <v>46244</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8300,8 +8300,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8344,7 +8349,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8358,10 +8363,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44980</v>
+        <v>46244</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8373,8 +8378,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8417,7 +8427,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8431,10 +8441,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45265</v>
+        <v>45229</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8446,13 +8456,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8495,7 +8500,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8509,10 +8514,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45799</v>
+        <v>46244</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8524,8 +8529,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8568,7 +8578,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8582,10 +8592,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45557</v>
+        <v>46244</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8597,8 +8607,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8641,7 +8656,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8655,10 +8670,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45257</v>
+        <v>46244</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8670,8 +8685,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8714,7 +8734,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8728,10 +8748,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45615</v>
+        <v>46205</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8744,7 +8764,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8787,7 +8807,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8801,10 +8821,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45882</v>
+        <v>45665</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8817,7 +8837,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8860,7 +8880,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8874,10 +8894,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45198</v>
+        <v>46205</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8890,7 +8910,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8933,7 +8953,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8947,10 +8967,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45229</v>
+        <v>46205</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8963,7 +8983,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9006,7 +9026,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9020,10 +9040,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46161</v>
+        <v>45642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9036,7 +9056,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9079,7 +9099,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9093,10 +9113,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44957</v>
+        <v>45615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9152,7 +9172,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9166,10 +9186,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45349</v>
+        <v>45198</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9182,7 +9202,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9225,7 +9245,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9239,10 +9259,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45946</v>
+        <v>46252</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9255,7 +9275,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9298,7 +9318,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9312,10 +9332,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44963</v>
+        <v>45390</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9328,7 +9348,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9371,7 +9391,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9385,10 +9405,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45699</v>
+        <v>45643</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9401,7 +9421,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9444,7 +9464,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9458,10 +9478,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45468</v>
+        <v>45993</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9474,7 +9494,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9517,7 +9537,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9531,10 +9551,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44853</v>
+        <v>45237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9547,7 +9567,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9590,7 +9610,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9604,10 +9624,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44606</v>
+        <v>44894</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9620,7 +9640,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9663,7 +9683,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9677,10 +9697,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45665</v>
+        <v>46262</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9693,7 +9713,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9736,7 +9756,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9750,10 +9770,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46181</v>
+        <v>44697</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9766,7 +9786,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9809,7 +9829,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9823,10 +9843,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44745</v>
+        <v>46269</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9838,8 +9858,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9882,7 +9907,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9896,10 +9921,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45699</v>
+        <v>46019</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9912,7 +9937,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9955,7 +9980,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9969,10 +9994,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45091</v>
+        <v>44963</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9984,13 +10009,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10033,7 +10053,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10047,10 +10067,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44939</v>
+        <v>44745</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10063,7 +10083,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10106,7 +10126,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10120,10 +10140,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44939</v>
+        <v>44508</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10136,7 +10156,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10179,7 +10199,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10193,10 +10213,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44615</v>
+        <v>44951</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10209,7 +10229,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10252,7 +10272,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10266,10 +10286,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46244</v>
+        <v>44963</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10281,13 +10301,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10330,7 +10345,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10344,10 +10359,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46244</v>
+        <v>45010</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10359,13 +10374,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10408,7 +10418,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10422,10 +10432,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46244</v>
+        <v>44616</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10437,13 +10447,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10486,7 +10491,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10500,10 +10505,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46244</v>
+        <v>44537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10515,13 +10520,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10564,7 +10564,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46244</v>
+        <v>45621</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10593,13 +10593,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10642,7 +10637,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10656,10 +10651,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44697</v>
+        <v>46042</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10672,7 +10667,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10715,7 +10710,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10729,10 +10724,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46205</v>
+        <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10744,8 +10739,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10788,7 +10788,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10802,10 +10802,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45161</v>
+        <v>45009</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10861,7 +10861,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10875,10 +10875,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45602</v>
+        <v>46056</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10944,14 +10944,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44537</v>
+        <v>46056</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11007,7 +11007,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11017,14 +11017,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
         <v>45167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46205</v>
+        <v>45146</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11153,7 +11153,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46205</v>
+        <v>44606</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11226,7 +11226,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11240,10 +11240,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46252</v>
+        <v>45091</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11255,8 +11255,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11299,7 +11304,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11313,10 +11318,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45028</v>
+        <v>45582</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11329,7 +11334,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11372,7 +11377,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11382,14 +11387,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45167</v>
+        <v>44980</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11402,7 +11407,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11445,7 +11450,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11459,10 +11464,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45266</v>
+        <v>45699</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11475,7 +11480,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11518,7 +11523,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11532,10 +11537,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45209</v>
+        <v>44560</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11548,7 +11553,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.4</v>
+        <v>0.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11591,7 +11596,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11605,10 +11610,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46262</v>
+        <v>45485</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11621,7 +11626,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11664,7 +11669,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11678,10 +11683,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45390</v>
+        <v>45266</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11737,7 +11742,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11747,14 +11752,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45197</v>
+        <v>45553</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11767,7 +11772,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11810,7 +11815,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11820,14 +11825,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45484</v>
+        <v>45470</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11839,8 +11844,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11883,7 +11893,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11897,10 +11907,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44951</v>
+        <v>45538</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11913,7 +11923,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11956,7 +11966,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11970,10 +11980,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46269</v>
+        <v>45771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11985,13 +11995,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12034,7 +12039,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12044,14 +12049,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44810</v>
+        <v>45351</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12064,7 +12069,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12107,7 +12112,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12121,10 +12126,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45553</v>
+        <v>45643</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12137,7 +12142,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12180,7 +12185,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12194,10 +12199,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45771</v>
+        <v>45797</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12210,7 +12215,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12253,7 +12258,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12267,10 +12272,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45470</v>
+        <v>45805</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12282,13 +12287,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12331,7 +12331,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45538</v>
+        <v>45805</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12414,14 +12414,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45351</v>
+        <v>45685</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12477,24 +12477,24 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>S 967-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45797</v>
+        <v>44607</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12506,8 +12506,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>151.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12547,27 +12552,27 @@
       </c>
       <c r="V158" s="2" t="inlineStr"/>
     </row>
-    <row r="159" ht="15" customHeight="1">
+    <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>S 3584-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45643</v>
+        <v>44735</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12580,7 +12585,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.1</v>
+        <v>28.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12619,157 +12624,6 @@
         <v>0</v>
       </c>
       <c r="V159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160" ht="15" customHeight="1">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>S 967-2022</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D160" s="1" t="n">
-        <v>44607</v>
-      </c>
-      <c r="E160" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
-        <v>151.6</v>
-      </c>
-      <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" t="n">
-        <v>0</v>
-      </c>
-      <c r="U160" t="n">
-        <v>0</v>
-      </c>
-      <c r="V160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>S 3584-2022</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D161" s="1" t="n">
-        <v>44735</v>
-      </c>
-      <c r="E161" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I161" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" t="n">
-        <v>0</v>
-      </c>
-      <c r="V161" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46269</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>46269</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44593</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32951-2026</t>
+          <t>A 33003-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1158,7 +1158,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1220,148 +1220,148 @@
         </is>
       </c>
       <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32951-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 33003-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46253</v>
+        <v>45468</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1391,23 +1391,23 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1415,10 +1415,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1431,248 +1431,248 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 34275-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 34277-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46253</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.8</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 26270-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45468</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44866</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>44608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44641</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44854</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44606</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44781</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>44638</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44615</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45186</v>
+        <v>44922</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3954,14 +3954,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45300</v>
+        <v>45069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3973,8 +3973,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4017,7 +4022,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4031,10 +4036,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45215</v>
+        <v>45643</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4047,7 +4052,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4090,7 +4095,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44810</v>
+        <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4120,7 +4125,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4163,7 +4168,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4177,10 +4182,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45209</v>
+        <v>45198</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4193,7 +4198,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4236,7 +4241,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44782</v>
+        <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4266,7 +4271,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4309,7 +4314,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4323,10 +4328,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45468</v>
+        <v>45573</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4339,7 +4344,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4382,7 +4387,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4396,10 +4401,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44853</v>
+        <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4412,7 +4417,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4455,7 +4460,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4469,10 +4474,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44939</v>
+        <v>45167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4485,7 +4490,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>11.6</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4528,7 +4533,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4538,14 +4543,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44945</v>
+        <v>45300</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4558,7 +4563,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4601,7 +4606,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4611,14 +4616,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44922</v>
+        <v>44935</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4631,7 +4636,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4674,7 +4679,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4688,10 +4693,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44939</v>
+        <v>44981</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4704,7 +4709,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4747,7 +4752,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4757,14 +4762,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44935</v>
+        <v>45186</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4777,7 +4782,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4820,7 +4825,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4830,14 +4835,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45197</v>
+        <v>45142</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4850,7 +4855,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4893,7 +4898,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4907,10 +4912,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45390</v>
+        <v>44782</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4923,7 +4928,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4966,7 +4971,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44615</v>
+        <v>44945</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4996,7 +5001,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5039,7 +5044,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5053,10 +5058,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45198</v>
+        <v>45643</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5069,7 +5074,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5112,7 +5117,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45826</v>
+        <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5142,7 +5147,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5185,7 +5190,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5199,10 +5204,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45254</v>
+        <v>45615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5215,7 +5220,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5258,7 +5263,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5272,10 +5277,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45069</v>
+        <v>45000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5287,13 +5292,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46086</v>
+        <v>45642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45699</v>
+        <v>45369</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45854</v>
+        <v>44508</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5511,13 +5511,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5560,7 +5555,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5570,14 +5565,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46104</v>
+        <v>45009</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5590,7 +5585,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5633,7 +5628,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5647,10 +5642,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45573</v>
+        <v>45621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5663,7 +5658,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5706,7 +5701,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45735</v>
+        <v>45010</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5736,7 +5731,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5779,7 +5774,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45643</v>
+        <v>45596</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5852,7 +5847,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5866,10 +5861,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44981</v>
+        <v>45113</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5882,7 +5877,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5925,7 +5920,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5939,10 +5934,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45112</v>
+        <v>45390</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5954,13 +5949,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6003,7 +5993,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6017,10 +6007,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45167</v>
+        <v>45265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6032,8 +6022,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6076,7 +6071,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6090,10 +6085,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45602</v>
+        <v>44560</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6106,7 +6101,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6149,7 +6144,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6163,10 +6158,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45142</v>
+        <v>45799</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6179,7 +6174,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6222,7 +6217,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6236,10 +6231,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45596</v>
+        <v>44963</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6252,7 +6247,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6295,7 +6290,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6309,10 +6304,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45265</v>
+        <v>45257</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6324,13 +6319,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6373,7 +6363,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6387,10 +6377,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45198</v>
+        <v>45237</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6403,7 +6393,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.800000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6446,7 +6436,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6456,14 +6446,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45484</v>
+        <v>44894</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6519,7 +6509,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6533,10 +6523,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45113</v>
+        <v>45923</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6549,7 +6539,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6592,7 +6582,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6606,10 +6596,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6622,7 +6612,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6665,7 +6655,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6679,10 +6669,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45257</v>
+        <v>45938</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6695,7 +6685,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.7</v>
+        <v>4.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6738,7 +6728,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6752,10 +6742,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45799</v>
+        <v>45943</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6768,7 +6758,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6811,7 +6801,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6825,10 +6815,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45923</v>
+        <v>45943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6841,7 +6831,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6884,7 +6874,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6898,10 +6888,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45923</v>
+        <v>45950</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6914,7 +6904,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6957,7 +6947,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6971,10 +6961,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45028</v>
+        <v>45485</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6987,7 +6977,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7030,7 +7020,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7044,10 +7034,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45167</v>
+        <v>45112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7059,8 +7049,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7103,7 +7098,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7117,10 +7112,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45167</v>
+        <v>45146</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7133,7 +7128,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7176,7 +7171,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7190,10 +7185,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45369</v>
+        <v>45882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7206,7 +7201,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7249,7 +7244,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7263,10 +7258,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45882</v>
+        <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7279,7 +7274,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7322,7 +7317,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7336,10 +7331,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45938</v>
+        <v>44614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7351,8 +7346,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7395,7 +7395,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44957</v>
+        <v>44980</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7468,7 +7468,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45943</v>
+        <v>45557</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7541,7 +7541,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46161</v>
+        <v>45993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7614,7 +7614,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45161</v>
+        <v>46161</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7687,7 +7687,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45943</v>
+        <v>45615</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
         <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45000</v>
+        <v>46019</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45950</v>
+        <v>45198</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7979,7 +7979,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45615</v>
+        <v>45229</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8052,7 +8052,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8066,10 +8066,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46181</v>
+        <v>46042</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8125,7 +8125,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45557</v>
+        <v>44957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
         <v>45349</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46244</v>
+        <v>46056</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8300,13 +8300,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8349,7 +8344,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8363,10 +8358,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46244</v>
+        <v>44963</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8378,13 +8373,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8427,7 +8417,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8437,14 +8427,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45229</v>
+        <v>46056</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8457,7 +8447,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8500,7 +8490,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8514,10 +8504,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46244</v>
+        <v>45699</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8529,13 +8519,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8578,7 +8563,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8592,10 +8577,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46244</v>
+        <v>45468</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8607,13 +8592,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8656,7 +8636,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8670,10 +8650,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46244</v>
+        <v>44853</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8685,13 +8665,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8734,7 +8709,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8748,10 +8723,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46205</v>
+        <v>46181</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8764,7 +8739,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8807,7 +8782,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8821,10 +8796,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45665</v>
+        <v>44606</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8837,7 +8812,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8880,7 +8855,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8894,10 +8869,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46205</v>
+        <v>45665</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8910,7 +8885,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8953,7 +8928,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8967,10 +8942,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46205</v>
+        <v>44745</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8983,7 +8958,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9026,7 +9001,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9040,10 +9015,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45642</v>
+        <v>46086</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9056,7 +9031,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9099,7 +9074,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9113,10 +9088,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45615</v>
+        <v>45699</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9129,7 +9104,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9172,7 +9147,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9186,10 +9161,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45198</v>
+        <v>45091</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9201,8 +9176,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>9.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9245,7 +9225,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9255,14 +9235,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46252</v>
+        <v>46104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9275,7 +9255,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9318,7 +9298,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9332,10 +9312,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45390</v>
+        <v>44939</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9348,7 +9328,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9391,7 +9371,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9405,10 +9385,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45643</v>
+        <v>44939</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9421,7 +9401,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.9</v>
+        <v>11.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9464,7 +9444,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9478,10 +9458,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45993</v>
+        <v>44615</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9494,7 +9474,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9537,7 +9517,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9551,10 +9531,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45237</v>
+        <v>46244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9566,8 +9546,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9610,7 +9595,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9624,10 +9609,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44894</v>
+        <v>46244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9639,8 +9624,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9683,7 +9673,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9697,10 +9687,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9712,8 +9702,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9756,7 +9751,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9770,10 +9765,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44697</v>
+        <v>46244</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9785,8 +9780,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46269</v>
+        <v>44697</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9856,11 +9856,6 @@
       <c r="G122" t="inlineStr">
         <is>
           <t>HJO</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -9907,7 +9902,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9921,10 +9916,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46019</v>
+        <v>46244</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9936,8 +9931,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9980,7 +9980,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9994,10 +9994,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44963</v>
+        <v>45161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10053,7 +10053,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44745</v>
+        <v>45602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10126,7 +10126,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10140,10 +10140,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44508</v>
+        <v>44537</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10199,7 +10199,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10213,10 +10213,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44951</v>
+        <v>45167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10272,7 +10272,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10286,10 +10286,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44963</v>
+        <v>45911</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10359,10 +10359,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45010</v>
+        <v>45028</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10418,7 +10418,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10428,14 +10428,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44616</v>
+        <v>45167</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10491,7 +10491,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44537</v>
+        <v>45266</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10564,7 +10564,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45621</v>
+        <v>46205</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10637,7 +10637,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10651,10 +10651,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46042</v>
+        <v>46205</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10710,7 +10710,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44614</v>
+        <v>46205</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10739,13 +10739,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10788,7 +10783,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10802,10 +10797,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45009</v>
+        <v>45209</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10818,7 +10813,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10861,7 +10856,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10875,10 +10870,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46056</v>
+        <v>46252</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10891,7 +10886,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10934,7 +10929,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10944,14 +10939,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46056</v>
+        <v>45390</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10964,7 +10959,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11007,7 +11002,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11021,10 +11016,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45167</v>
+        <v>45197</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11037,7 +11032,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11080,7 +11075,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11090,14 +11085,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45146</v>
+        <v>45484</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11110,7 +11105,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11153,7 +11148,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11167,10 +11162,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44606</v>
+        <v>44951</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11183,7 +11178,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11226,7 +11221,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11240,10 +11235,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45091</v>
+        <v>44810</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11255,13 +11250,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11304,7 +11294,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11318,10 +11308,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45582</v>
+        <v>46262</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11334,7 +11324,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11377,7 +11367,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11391,10 +11381,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44980</v>
+        <v>46269</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11406,8 +11396,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11450,7 +11445,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11464,10 +11459,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45699</v>
+        <v>45553</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11480,7 +11475,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11523,7 +11518,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11537,10 +11532,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44560</v>
+        <v>45771</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11553,7 +11548,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11596,7 +11591,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11610,10 +11605,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45485</v>
+        <v>45470</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11625,8 +11620,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>7.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11669,7 +11669,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45266</v>
+        <v>45538</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45553</v>
+        <v>45351</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11815,7 +11815,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11829,10 +11829,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45470</v>
+        <v>45797</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11844,13 +11844,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11893,7 +11888,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11907,10 +11902,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45538</v>
+        <v>45643</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11923,7 +11918,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11966,7 +11961,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11980,10 +11975,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45771</v>
+        <v>45805</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11996,7 +11991,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12039,7 +12034,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12049,14 +12044,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45351</v>
+        <v>45805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12069,7 +12064,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12112,7 +12107,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12126,10 +12121,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45643</v>
+        <v>45685</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12142,7 +12137,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12185,7 +12180,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12199,10 +12194,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45797</v>
+        <v>45826</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12215,7 +12210,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12258,7 +12253,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12272,10 +12267,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45805</v>
+        <v>45254</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12288,7 +12283,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12331,7 +12326,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12345,10 +12340,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45805</v>
+        <v>45854</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12360,8 +12355,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12418,10 +12418,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45685</v>
+        <v>45735</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
         <v>44607</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44735</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46269</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>46269</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44593</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>46244</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45468</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>46253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44866</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>44608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44641</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44854</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44606</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44781</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>44638</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44615</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44922</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45643</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>45198</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45573</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45300</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44935</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44981</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45186</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45142</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44782</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44945</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45643</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45369</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44508</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45009</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>45621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45010</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45596</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45113</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45390</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44560</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45799</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44963</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45257</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>45237</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44894</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45923</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45938</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45943</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45950</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>45485</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45146</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44980</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45557</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>46161</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45615</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>46019</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45198</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45229</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>46042</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45349</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>46056</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44963</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>46056</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45699</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45468</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44853</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>46181</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44606</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45665</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44745</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46086</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>45699</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>45091</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>46104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44939</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44939</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44615</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>46244</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>46244</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>46244</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44697</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>46244</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>45161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>45602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44537</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45911</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45028</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45167</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45266</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>46205</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>46205</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>46205</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45209</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46252</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45390</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45197</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45484</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44951</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44810</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>46262</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>46269</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45553</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45771</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45470</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45538</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45351</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45797</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45643</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45805</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45685</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45826</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45254</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45854</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45735</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>44607</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44735</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE159"/>
+  <dimension ref="A1:AE160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46269</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>46269</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44593</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 34275-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,13 +1170,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1216,42 +1211,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32951-2026</t>
+          <t>A 34277-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1265,10 +1260,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,13 +1275,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1326,35 +1316,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
@@ -1378,7 +1368,7 @@
         <v>45468</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1466,7 +1456,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 33003-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1480,10 +1470,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1495,8 +1485,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1536,42 +1531,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34277-2026</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1585,10 +1580,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1600,8 +1595,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1641,35 +1641,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
         <v/>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
         <v>45719</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44799</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>44692</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44866</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>44608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44641</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44854</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44606</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44781</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>44638</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44615</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44922</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45643</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>45198</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45573</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45300</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44935</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44981</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4762,14 +4762,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45186</v>
+        <v>45142</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4835,14 +4835,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45142</v>
+        <v>45186</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44782</v>
+        <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44945</v>
+        <v>44782</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
         <v>45643</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45369</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44508</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45009</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45621</v>
+        <v>45010</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45010</v>
+        <v>45911</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45596</v>
+        <v>45621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5847,7 +5847,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45113</v>
+        <v>45596</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5920,7 +5920,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45390</v>
+        <v>45113</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6010,7 +6010,7 @@
         <v>45265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44560</v>
+        <v>45799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45799</v>
+        <v>45923</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44963</v>
+        <v>45923</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45257</v>
+        <v>45390</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45237</v>
+        <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44894</v>
+        <v>44560</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45923</v>
+        <v>45938</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45923</v>
+        <v>44963</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45938</v>
+        <v>45882</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45943</v>
+        <v>45237</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6818,7 +6818,7 @@
         <v>45943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45950</v>
+        <v>45943</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45485</v>
+        <v>44894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45112</v>
+        <v>45950</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7049,13 +7049,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7098,7 +7093,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7112,10 +7107,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45146</v>
+        <v>46161</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7128,7 +7123,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7171,7 +7166,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7185,10 +7180,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45882</v>
+        <v>45946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7201,7 +7196,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7244,7 +7239,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7258,10 +7253,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44616</v>
+        <v>45993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7274,7 +7269,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7317,7 +7312,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7331,10 +7326,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44614</v>
+        <v>45485</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7346,13 +7341,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7395,7 +7385,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7409,10 +7399,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44980</v>
+        <v>45112</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7424,8 +7414,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7468,7 +7463,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7482,10 +7477,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45557</v>
+        <v>45146</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7498,7 +7493,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>11.5</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7541,7 +7536,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7555,10 +7550,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45993</v>
+        <v>44616</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7571,7 +7566,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7614,7 +7609,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7628,10 +7623,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46161</v>
+        <v>46019</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7644,7 +7639,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7687,7 +7682,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7701,10 +7696,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45615</v>
+        <v>44614</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7716,8 +7711,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45946</v>
+        <v>44980</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7833,7 +7833,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46019</v>
+        <v>46181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7906,7 +7906,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45198</v>
+        <v>45557</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7979,7 +7979,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45229</v>
+        <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8052,7 +8052,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8066,10 +8066,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46042</v>
+        <v>46056</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8125,7 +8125,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8135,14 +8135,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44957</v>
+        <v>46056</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8198,7 +8198,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45349</v>
+        <v>45615</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8271,7 +8271,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46056</v>
+        <v>45198</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8358,10 +8358,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44963</v>
+        <v>45229</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8417,7 +8417,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8427,14 +8427,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46056</v>
+        <v>46086</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8490,7 +8490,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8500,14 +8500,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45699</v>
+        <v>46104</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8563,7 +8563,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45468</v>
+        <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8636,7 +8636,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44853</v>
+        <v>45349</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8709,7 +8709,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46181</v>
+        <v>46205</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8782,7 +8782,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44606</v>
+        <v>44963</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8855,7 +8855,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45665</v>
+        <v>45699</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8928,7 +8928,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44745</v>
+        <v>45468</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46086</v>
+        <v>44853</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9088,10 +9088,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45699</v>
+        <v>44606</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45091</v>
+        <v>45665</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9176,13 +9176,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>9.4</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9225,7 +9220,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9235,14 +9230,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46104</v>
+        <v>46205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9255,7 +9250,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9298,7 +9293,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9312,10 +9307,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44939</v>
+        <v>46205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9328,7 +9323,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9371,7 +9366,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9385,10 +9380,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44939</v>
+        <v>44745</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9401,7 +9396,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>11.6</v>
+        <v>2.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9444,7 +9439,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9458,10 +9453,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44615</v>
+        <v>46252</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9474,7 +9469,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9517,7 +9512,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9531,10 +9526,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46244</v>
+        <v>45699</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9546,13 +9541,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9595,7 +9585,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9609,10 +9599,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46244</v>
+        <v>45091</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9630,7 +9620,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9673,7 +9663,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9687,10 +9677,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46244</v>
+        <v>44939</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9702,13 +9692,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9751,7 +9736,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9765,10 +9750,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46244</v>
+        <v>44939</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9780,13 +9765,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9829,7 +9809,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9843,10 +9823,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44697</v>
+        <v>44615</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9859,7 +9839,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9902,7 +9882,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9916,10 +9896,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46244</v>
+        <v>44697</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9931,13 +9911,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9997,7 +9972,7 @@
         <v>45161</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10070,7 +10045,7 @@
         <v>45602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10143,7 +10118,7 @@
         <v>44537</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10216,7 +10191,7 @@
         <v>45167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10272,7 +10247,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10286,10 +10261,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45911</v>
+        <v>46269</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10301,8 +10276,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10362,7 +10342,7 @@
         <v>45028</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10435,7 +10415,7 @@
         <v>45167</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10508,7 +10488,7 @@
         <v>45266</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10564,7 +10544,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10578,10 +10558,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46205</v>
+        <v>45209</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10594,7 +10574,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10637,7 +10617,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10651,10 +10631,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46205</v>
+        <v>45390</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10667,7 +10647,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10710,7 +10690,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10720,14 +10700,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46205</v>
+        <v>45197</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10740,7 +10720,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10783,7 +10763,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10793,14 +10773,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45209</v>
+        <v>45484</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10813,7 +10793,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10856,7 +10836,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10870,10 +10850,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46252</v>
+        <v>46262</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10886,7 +10866,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10929,7 +10909,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10943,10 +10923,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45390</v>
+        <v>44951</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10959,7 +10939,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11002,7 +10982,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11012,14 +10992,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45197</v>
+        <v>46244</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11031,8 +11011,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11075,7 +11060,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11085,14 +11070,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45484</v>
+        <v>46244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11104,8 +11089,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11148,7 +11138,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11162,10 +11152,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44951</v>
+        <v>46244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11177,8 +11167,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11238,7 +11233,7 @@
         <v>44810</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11294,7 +11289,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11308,10 +11303,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11323,8 +11318,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11367,7 +11367,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11381,10 +11381,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46269</v>
+        <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11459,10 +11459,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45553</v>
+        <v>46286</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11474,8 +11474,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>6.5</v>
+        <v>12.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11518,7 +11523,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11532,10 +11537,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45771</v>
+        <v>45553</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11548,7 +11553,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11591,7 +11596,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11605,10 +11610,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45470</v>
+        <v>45771</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11620,13 +11625,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>7.1</v>
+        <v>0.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11669,7 +11669,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11683,10 +11683,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45538</v>
+        <v>45470</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11698,8 +11698,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11742,7 +11747,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11752,14 +11757,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45351</v>
+        <v>45538</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11772,7 +11777,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11815,7 +11820,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11825,14 +11830,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45797</v>
+        <v>45351</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11845,7 +11850,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>7.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11888,7 +11893,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11902,10 +11907,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45643</v>
+        <v>45797</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11918,7 +11923,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11961,7 +11966,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11975,10 +11980,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45805</v>
+        <v>45643</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11991,7 +11996,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12034,7 +12039,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12051,7 +12056,7 @@
         <v>45805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12064,7 +12069,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12107,7 +12112,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12121,10 +12126,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45685</v>
+        <v>45805</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12137,7 +12142,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12180,7 +12185,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12194,10 +12199,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45826</v>
+        <v>45685</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12210,7 +12215,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12253,7 +12258,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12267,10 +12272,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45254</v>
+        <v>45826</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12283,7 +12288,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12326,7 +12331,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12340,10 +12345,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45854</v>
+        <v>45254</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12355,13 +12360,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12418,10 +12418,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45735</v>
+        <v>45854</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12433,8 +12433,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12477,153 +12482,226 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
+          <t>A 13177-2025</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E158" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159" ht="15" customHeight="1">
+      <c r="A159" t="inlineStr">
+        <is>
           <t>S 967-2022</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D158" s="1" t="n">
+      <c r="D159" s="1" t="n">
         <v>44607</v>
       </c>
-      <c r="E158" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
+      <c r="E159" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I158" t="n">
+      <c r="I159" t="n">
         <v>151.6</v>
       </c>
-      <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
-        <v>0</v>
-      </c>
-      <c r="M158" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>S 3584-2022</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D159" s="1" t="n">
+      <c r="D160" s="1" t="n">
         <v>44735</v>
       </c>
-      <c r="E159" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
+      <c r="E160" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
         <v>28.7</v>
       </c>
-      <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="n">
-        <v>0</v>
-      </c>
-      <c r="T159" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" t="n">
-        <v>0</v>
-      </c>
-      <c r="V159" s="2" t="inlineStr"/>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE160"/>
+  <dimension ref="A1:AE164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36434-2026</t>
+          <t>A 39364-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46269</v>
+        <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>10.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -749,504 +749,512 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Fransig jordstjärna
+Grovticka
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 39364-2026 artfynd.xlsx", "A 39364-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 39364-2026 karta.png", "A 39364-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 39364-2026 georefererad karta.tif", "A 39364-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 39364-2026 FSC-klagomål.docx", "A 39364-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 39364-2026 FSC-klagomål mail.docx", "A 39364-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 39364-2026 tillsynsbegäran.docx", "A 39364-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 39364-2026 tillsynsbegäran mail.docx", "A 39364-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 36434-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Ägretthäger
 Fransig jordstjärna</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 36434-2026 artfynd.xlsx", "A 36434-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 36434-2026 karta.png", "A 36434-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 36434-2026 georefererad karta.tif", "A 36434-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 36434-2026 FSC-klagomål.docx", "A 36434-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 36434-2026 FSC-klagomål mail.docx", "A 36434-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 36434-2026 tillsynsbegäran.docx", "A 36434-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 36434-2026 tillsynsbegäran mail.docx", "A 36434-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/fåglar/A 36434-2026 prioriterade fågelarter.docx", "A 36434-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>A 48359-2025</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>45933</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="E5" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3.5</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>2</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>2</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dunmossa
 Blåmossa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 48359-2025 artfynd.xlsx", "A 48359-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 48359-2025 karta.png", "A 48359-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 48359-2025 georefererad karta.tif", "A 48359-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 48359-2025 FSC-klagomål.docx", "A 48359-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 48359-2025 FSC-klagomål mail.docx", "A 48359-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 48359-2025 tillsynsbegäran.docx", "A 48359-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 48359-2025 tillsynsbegäran mail.docx", "A 48359-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 36441-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>6.8</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>2</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Talltita</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 36441-2026 artfynd.xlsx", "A 36441-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 36441-2026 karta.png", "A 36441-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 36441-2026 georefererad karta.tif", "A 36441-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 36441-2026 FSC-klagomål.docx", "A 36441-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 36441-2026 FSC-klagomål mail.docx", "A 36441-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 36441-2026 tillsynsbegäran.docx", "A 36441-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 36441-2026 tillsynsbegäran mail.docx", "A 36441-2026")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/fåglar/A 36441-2026 prioriterade fågelarter.docx", "A 36441-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 4966-2022</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>44593</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.6</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 4966-2022 artfynd.xlsx", "A 4966-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 4966-2022 karta.png", "A 4966-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 4966-2022 georefererad karta.tif", "A 4966-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 4966-2022 FSC-klagomål.docx", "A 4966-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 4966-2022 FSC-klagomål mail.docx", "A 4966-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 4966-2022 tillsynsbegäran.docx", "A 4966-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 4966-2022 tillsynsbegäran mail.docx", "A 4966-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 34275-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34277-2026</t>
+          <t>A 10014-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1260,10 +1268,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46253</v>
+        <v>45719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1276,20 +1284,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1300,51 +1308,55 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
         <v/>
       </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+        <v/>
+      </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
         <v/>
       </c>
     </row>
@@ -1368,7 +1380,7 @@
         <v>45468</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1456,7 +1468,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,7 +1485,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1491,7 +1503,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1535,148 +1547,148 @@
         </is>
       </c>
       <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 33003-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 10014-2025</t>
+          <t>A 34275-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1690,10 +1702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45719</v>
+        <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1706,19 +1718,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1730,79 +1742,75 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
-        <v/>
-      </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S 4605-2024</t>
+          <t>A 34277-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45601</v>
+        <v>46253</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1814,19 +1822,14 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1860,115 +1863,152 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S 4605-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45601</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/S 4605-2024 artfynd.xlsx", "S 4605-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/S 4605-2024 karta.png", "S 4605-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/S 4605-2024 georefererad karta.tif", "S 4605-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/S 4605-2024 FSC-klagomål.docx", "S 4605-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/S 4605-2024 FSC-klagomål mail.docx", "S 4605-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/S 4605-2024 tillsynsbegäran.docx", "S 4605-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/S 4605-2024 tillsynsbegäran mail.docx", "S 4605-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 35602-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44799</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr"/>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25205-2022</t>
+          <t>A 35602-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1978,14 +2018,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44729</v>
+        <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1997,13 +2037,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2046,7 +2081,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 67995-2021</t>
+          <t>A 25205-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2056,14 +2091,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44525</v>
+        <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2075,8 +2110,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2119,7 +2159,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 9209-2022</t>
+          <t>A 67995-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2133,10 +2173,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44616</v>
+        <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2149,7 +2189,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2192,7 +2232,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19341-2022</t>
+          <t>A 9209-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2202,14 +2242,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44692</v>
+        <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2222,7 +2262,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2265,7 +2305,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50559-2022</t>
+          <t>A 19341-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2275,14 +2315,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44866</v>
+        <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2295,7 +2335,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2338,7 +2378,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10337-2022</t>
+          <t>A 50559-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2352,10 +2392,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44623</v>
+        <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2368,7 +2408,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2411,7 +2451,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45980-2022</t>
+          <t>A 10337-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2421,14 +2461,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44846</v>
+        <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2441,7 +2481,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.1</v>
+        <v>8.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2484,7 +2524,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 65329-2021</t>
+          <t>A 45980-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2494,14 +2534,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44515</v>
+        <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2514,7 +2554,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2557,7 +2597,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55091-2021</t>
+          <t>A 65329-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2571,10 +2611,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44474</v>
+        <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2587,7 +2627,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2630,7 +2670,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46998-2022</t>
+          <t>A 55091-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2644,10 +2684,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44852</v>
+        <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2660,7 +2700,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2703,7 +2743,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35216-2022</t>
+          <t>A 46998-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2717,10 +2757,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44797</v>
+        <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2733,7 +2773,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2776,7 +2816,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28512-2022</t>
+          <t>A 35216-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2790,10 +2830,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44748</v>
+        <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2806,7 +2846,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2849,7 +2889,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58495-2021</t>
+          <t>A 28512-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2863,10 +2903,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44488</v>
+        <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2879,7 +2919,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2922,7 +2962,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32158-2022</t>
+          <t>A 58495-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2936,10 +2976,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44781</v>
+        <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2952,7 +2992,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2995,7 +3035,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63257-2021</t>
+          <t>A 32158-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3009,10 +3049,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44508</v>
+        <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3025,7 +3065,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3068,7 +3108,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7786-2022</t>
+          <t>A 63257-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3078,14 +3118,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44608</v>
+        <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3098,7 +3138,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3141,7 +3181,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32814-2022</t>
+          <t>A 7786-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3151,14 +3191,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44784</v>
+        <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3171,7 +3211,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3214,7 +3254,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12726-2022</t>
+          <t>A 32814-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3228,10 +3268,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44641</v>
+        <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3244,7 +3284,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3287,7 +3327,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47656-2022</t>
+          <t>A 12726-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3301,10 +3341,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44854</v>
+        <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3317,7 +3357,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3360,7 +3400,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7231-2022</t>
+          <t>A 56175-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3374,10 +3414,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44606</v>
+        <v>44477</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3390,7 +3430,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3433,7 +3473,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32219-2022</t>
+          <t>A 12544-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3447,10 +3487,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44781</v>
+        <v>44638</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3463,7 +3503,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3506,7 +3546,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22586-2022</t>
+          <t>A 9184-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3520,10 +3560,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44714</v>
+        <v>44615</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3536,7 +3576,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3579,7 +3619,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56175-2021</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3593,10 +3633,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44477</v>
+        <v>45771</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3609,7 +3649,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3652,7 +3692,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12544-2022</t>
+          <t>A 47656-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3666,10 +3706,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44638</v>
+        <v>44854</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3682,7 +3722,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3725,7 +3765,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9184-2022</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3739,10 +3779,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44615</v>
+        <v>45198</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3755,7 +3795,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3815,7 +3855,7 @@
         <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3871,7 +3911,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 7231-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3881,14 +3921,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44922</v>
+        <v>44606</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3901,7 +3941,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3944,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 32219-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3958,10 +3998,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45069</v>
+        <v>44781</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3973,13 +4013,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4022,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4032,14 +4067,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45643</v>
+        <v>45186</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4052,7 +4087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4095,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 22586-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4109,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45582</v>
+        <v>44714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4125,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4168,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4178,14 +4213,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45198</v>
+        <v>45484</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4198,7 +4233,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4241,7 +4276,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4251,14 +4286,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45198</v>
+        <v>45300</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4314,7 +4349,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4328,10 +4363,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45573</v>
+        <v>44810</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4387,7 +4422,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4401,10 +4436,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45167</v>
+        <v>44782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4417,7 +4452,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4460,7 +4495,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4474,10 +4509,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45167</v>
+        <v>45215</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4490,7 +4525,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4533,7 +4568,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4543,14 +4578,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45300</v>
+        <v>45209</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4563,7 +4598,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4606,7 +4641,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4616,14 +4651,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44935</v>
+        <v>45351</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4636,7 +4671,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4679,7 +4714,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4693,10 +4728,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44981</v>
+        <v>45643</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4709,7 +4744,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4752,7 +4787,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4766,10 +4801,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45142</v>
+        <v>45028</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4782,7 +4817,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4825,7 +4860,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4835,14 +4870,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45186</v>
+        <v>45468</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4855,7 +4890,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4898,7 +4933,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4912,10 +4947,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44945</v>
+        <v>45167</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4971,7 +5006,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4985,10 +5020,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44782</v>
+        <v>45167</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5001,7 +5036,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5044,7 +5079,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5058,10 +5093,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45643</v>
+        <v>45797</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5074,7 +5109,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5117,7 +5152,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5131,10 +5166,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45215</v>
+        <v>45369</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5147,7 +5182,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5190,7 +5225,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5204,10 +5239,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45615</v>
+        <v>44853</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5220,7 +5255,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5263,7 +5298,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5277,10 +5312,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45000</v>
+        <v>44957</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5293,7 +5328,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5336,7 +5371,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5350,10 +5385,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45642</v>
+        <v>44939</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5366,7 +5401,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>11.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5409,7 +5444,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5423,10 +5458,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45369</v>
+        <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5439,7 +5474,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5482,7 +5517,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5496,10 +5531,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44508</v>
+        <v>44945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5512,7 +5547,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5555,7 +5590,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5569,10 +5604,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45009</v>
+        <v>45000</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5585,7 +5620,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5628,7 +5663,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5638,14 +5673,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45010</v>
+        <v>44922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5658,7 +5693,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5701,7 +5736,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5715,10 +5750,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5731,7 +5766,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5774,7 +5809,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5788,10 +5823,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45621</v>
+        <v>45805</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5804,7 +5839,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5847,7 +5882,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5861,10 +5896,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45596</v>
+        <v>45805</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5877,7 +5912,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5920,7 +5955,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5934,10 +5969,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45113</v>
+        <v>45923</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5950,7 +5985,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5993,7 +6028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6007,10 +6042,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45265</v>
+        <v>45685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6022,13 +6057,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6071,7 +6101,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6085,10 +6115,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45799</v>
+        <v>44939</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6101,7 +6131,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6144,7 +6174,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6158,10 +6188,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45923</v>
+        <v>45615</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6174,7 +6204,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6217,7 +6247,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6231,10 +6261,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45923</v>
+        <v>44935</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6247,7 +6277,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6290,7 +6320,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6307,7 +6337,7 @@
         <v>45390</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6320,7 +6350,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6363,7 +6393,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6377,10 +6407,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45257</v>
+        <v>45557</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6393,7 +6423,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6436,7 +6466,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6450,10 +6480,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44560</v>
+        <v>45349</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6466,7 +6496,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6526,7 +6556,7 @@
         <v>45938</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6582,7 +6612,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6592,14 +6622,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44963</v>
+        <v>45197</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6612,7 +6642,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6655,7 +6685,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6669,10 +6699,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45882</v>
+        <v>44615</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6685,7 +6715,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6728,7 +6758,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6742,10 +6772,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45237</v>
+        <v>45943</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6758,7 +6788,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6801,7 +6831,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6818,7 +6848,7 @@
         <v>45943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6831,7 +6861,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6874,7 +6904,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6888,10 +6918,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45943</v>
+        <v>45198</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6904,7 +6934,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6947,7 +6977,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6961,10 +6991,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44894</v>
+        <v>45950</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6977,7 +7007,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7020,7 +7050,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7034,10 +7064,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45950</v>
+        <v>45069</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7049,8 +7079,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7093,7 +7128,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7107,10 +7142,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46161</v>
+        <v>45699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7123,7 +7158,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7166,7 +7201,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7180,10 +7215,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45946</v>
+        <v>45229</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7196,7 +7231,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7239,7 +7274,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7253,10 +7288,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45993</v>
+        <v>45665</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7269,7 +7304,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7312,7 +7347,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7326,10 +7361,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45485</v>
+        <v>45573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7342,7 +7377,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7385,7 +7420,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7399,10 +7434,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45112</v>
+        <v>45642</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7414,13 +7449,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7463,7 +7493,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7477,10 +7507,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45146</v>
+        <v>45615</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7493,7 +7523,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7536,7 +7566,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7550,10 +7580,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44616</v>
+        <v>45643</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7566,7 +7596,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7609,7 +7639,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7623,10 +7653,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46019</v>
+        <v>45198</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7639,7 +7669,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7682,7 +7712,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7696,10 +7726,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44614</v>
+        <v>45826</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7711,13 +7741,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7760,7 +7785,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7774,10 +7799,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44980</v>
+        <v>44981</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7790,7 +7815,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7833,7 +7858,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7847,10 +7872,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46181</v>
+        <v>45390</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7863,7 +7888,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7906,7 +7931,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7920,10 +7945,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45557</v>
+        <v>45112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7935,8 +7960,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>11.5</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7979,7 +8009,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7993,10 +8023,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46042</v>
+        <v>45167</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8009,7 +8039,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8052,7 +8082,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8066,10 +8096,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46056</v>
+        <v>45602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8082,7 +8112,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8125,7 +8155,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8135,14 +8165,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46056</v>
+        <v>45142</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8155,7 +8185,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8198,7 +8228,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8212,10 +8242,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45615</v>
+        <v>45596</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8271,7 +8301,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8285,10 +8315,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45198</v>
+        <v>45993</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8301,7 +8331,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8344,7 +8374,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8358,10 +8388,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45229</v>
+        <v>45254</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8374,7 +8404,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8417,7 +8447,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8431,10 +8461,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46086</v>
+        <v>45643</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8447,7 +8477,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8490,7 +8520,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8500,14 +8530,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46104</v>
+        <v>45237</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8520,7 +8550,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8563,7 +8593,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8577,10 +8607,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44957</v>
+        <v>46042</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8593,7 +8623,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8636,7 +8666,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8650,10 +8680,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45349</v>
+        <v>44894</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8666,7 +8696,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8709,7 +8739,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8723,10 +8753,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46205</v>
+        <v>46019</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8739,7 +8769,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8782,7 +8812,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8796,10 +8826,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44963</v>
+        <v>44697</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8812,7 +8842,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8855,7 +8885,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8869,10 +8899,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45699</v>
+        <v>46056</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8885,7 +8915,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8928,7 +8958,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8942,10 +8972,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45468</v>
+        <v>46286</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8957,8 +8987,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>12.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9001,7 +9036,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9011,14 +9046,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44853</v>
+        <v>46056</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9031,7 +9066,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9074,7 +9109,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9088,10 +9123,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44606</v>
+        <v>46262</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9104,7 +9139,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9147,7 +9182,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9161,10 +9196,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45665</v>
+        <v>44963</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9177,7 +9212,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9220,7 +9255,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9234,10 +9269,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9249,8 +9284,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9293,7 +9333,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9307,10 +9347,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9322,8 +9362,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9366,7 +9411,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9380,10 +9425,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44745</v>
+        <v>46244</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9395,8 +9440,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9439,7 +9489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9453,10 +9503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46252</v>
+        <v>46288</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9468,8 +9518,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9512,7 +9567,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9522,14 +9577,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45699</v>
+        <v>46288</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9542,7 +9597,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9585,7 +9640,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9599,10 +9654,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45091</v>
+        <v>46288</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9614,13 +9669,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9663,7 +9713,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9677,10 +9727,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44939</v>
+        <v>44745</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9693,7 +9743,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9736,7 +9786,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9750,10 +9800,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44939</v>
+        <v>44508</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9766,7 +9816,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9809,7 +9859,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9823,10 +9873,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44615</v>
+        <v>46244</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9838,8 +9888,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9882,7 +9937,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9896,10 +9951,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44697</v>
+        <v>46244</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9911,8 +9966,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9955,7 +10015,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9969,10 +10029,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45161</v>
+        <v>46086</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9985,7 +10045,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10028,7 +10088,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10042,10 +10102,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45602</v>
+        <v>44951</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10058,7 +10118,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10101,7 +10161,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10115,10 +10175,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44537</v>
+        <v>44963</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10131,7 +10191,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10174,7 +10234,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10188,10 +10248,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45167</v>
+        <v>45010</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10204,7 +10264,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10247,7 +10307,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10261,10 +10321,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46269</v>
+        <v>45854</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10278,11 +10338,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10325,7 +10385,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10335,14 +10395,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45028</v>
+        <v>46104</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10355,7 +10415,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10398,7 +10458,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10408,14 +10468,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45167</v>
+        <v>44616</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10428,7 +10488,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10471,7 +10531,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10485,10 +10545,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45266</v>
+        <v>44537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10501,7 +10561,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10544,7 +10604,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10558,10 +10618,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45209</v>
+        <v>45621</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10574,7 +10634,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10617,7 +10677,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10631,10 +10691,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45390</v>
+        <v>45735</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10647,7 +10707,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10690,7 +10750,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10700,14 +10760,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45197</v>
+        <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10719,8 +10779,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10763,7 +10828,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10773,14 +10838,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45484</v>
+        <v>45009</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10793,7 +10858,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10836,7 +10901,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10846,14 +10911,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46262</v>
+        <v>45167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10866,7 +10931,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10909,7 +10974,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10923,10 +10988,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44951</v>
+        <v>45146</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10939,7 +11004,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10982,7 +11047,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10996,10 +11061,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46244</v>
+        <v>44606</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11011,13 +11076,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11060,7 +11120,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11074,10 +11134,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46244</v>
+        <v>45091</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11095,7 +11155,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11138,7 +11198,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11152,10 +11212,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46244</v>
+        <v>45265</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11169,11 +11229,11 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11216,7 +11276,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11230,10 +11290,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44810</v>
+        <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11246,7 +11306,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11289,7 +11349,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11303,10 +11363,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46244</v>
+        <v>45113</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11318,13 +11378,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11367,7 +11422,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11381,10 +11436,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46244</v>
+        <v>45911</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11396,13 +11451,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11445,7 +11495,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11459,10 +11509,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46286</v>
+        <v>44980</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11474,13 +11524,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>12.7</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11523,7 +11568,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11537,10 +11582,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45553</v>
+        <v>45257</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11553,7 +11598,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11596,7 +11641,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11610,10 +11655,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45771</v>
+        <v>45799</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11626,7 +11671,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11669,7 +11714,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11683,10 +11728,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45470</v>
+        <v>45699</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11698,13 +11743,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11747,7 +11787,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11761,10 +11801,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45538</v>
+        <v>44560</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11777,7 +11817,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11820,7 +11860,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11830,14 +11870,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45351</v>
+        <v>45485</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11850,7 +11890,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>7.3</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11893,7 +11933,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11907,10 +11947,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45797</v>
+        <v>45266</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11923,7 +11963,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11966,7 +12006,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11980,10 +12020,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45643</v>
+        <v>45553</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11996,7 +12036,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12039,7 +12079,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12053,10 +12093,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45805</v>
+        <v>45470</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12068,8 +12108,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12112,7 +12157,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12126,10 +12171,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45805</v>
+        <v>45538</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12142,7 +12187,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12185,7 +12230,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12199,10 +12244,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45685</v>
+        <v>45882</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12215,7 +12260,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12258,7 +12303,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12272,10 +12317,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45826</v>
+        <v>46161</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12331,7 +12376,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12345,10 +12390,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45254</v>
+        <v>45946</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12361,7 +12406,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12404,7 +12449,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12418,10 +12463,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45854</v>
+        <v>46181</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12433,13 +12478,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12482,7 +12522,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12496,10 +12536,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45735</v>
+        <v>46205</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12512,7 +12552,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12555,153 +12595,450 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
+          <t>A 29905-2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160" ht="15" customHeight="1">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>A 29953-2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E160" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161" ht="15" customHeight="1">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>A 33950-2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E161" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162" ht="15" customHeight="1">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>A 36436-2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E162" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163" ht="15" customHeight="1">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>S 967-2022</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D159" s="1" t="n">
+      <c r="D163" s="1" t="n">
         <v>44607</v>
       </c>
-      <c r="E159" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
+      <c r="E163" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I159" t="n">
+      <c r="I163" t="n">
         <v>151.6</v>
       </c>
-      <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="n">
-        <v>0</v>
-      </c>
-      <c r="T159" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" t="n">
-        <v>0</v>
-      </c>
-      <c r="V159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>S 3584-2022</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D160" s="1" t="n">
+      <c r="D164" s="1" t="n">
         <v>44735</v>
       </c>
-      <c r="E160" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
+      <c r="E164" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
         <v>28.7</v>
       </c>
-      <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" t="n">
-        <v>0</v>
-      </c>
-      <c r="U160" t="n">
-        <v>0</v>
-      </c>
-      <c r="V160" s="2" t="inlineStr"/>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 10014-2025</t>
+          <t>A 34275-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45719</v>
+        <v>46253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1308,62 +1308,58 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
-        <v/>
-      </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26270-2024</t>
+          <t>A 34277-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1373,14 +1369,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45468</v>
+        <v>46253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,13 +1389,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1408,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1417,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1433,148 +1429,143 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 26270-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45468</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1595,7 +1586,7 @@
         <v>46244</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1688,7 +1679,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1702,10 +1693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1717,8 +1708,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1758,42 +1754,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34277-2026</t>
+          <t>A 10014-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46253</v>
+        <v>45719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,20 +1819,20 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -1847,51 +1843,55 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
         <v/>
       </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+        <v/>
+      </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
         <v/>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56175-2021</t>
+          <t>A 47656-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44477</v>
+        <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12544-2022</t>
+          <t>A 7231-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44638</v>
+        <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9184-2022</t>
+          <t>A 32219-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44615</v>
+        <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 22586-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45771</v>
+        <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47656-2022</t>
+          <t>A 56175-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44854</v>
+        <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3765,7 +3765,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 12544-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45198</v>
+        <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3838,7 +3838,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9210-2022</t>
+          <t>A 9184-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44616</v>
+        <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7231-2022</t>
+          <t>A 9210-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44606</v>
+        <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32219-2022</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3994,14 +3994,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44781</v>
+        <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4067,14 +4067,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45186</v>
+        <v>45069</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4086,8 +4086,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4135,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22586-2022</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4149,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44714</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4213,14 +4218,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45484</v>
+        <v>45582</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4233,7 +4238,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4276,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4286,14 +4291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45300</v>
+        <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4306,7 +4311,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4349,7 +4354,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4363,10 +4368,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44810</v>
+        <v>45198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4379,7 +4384,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4422,7 +4427,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44782</v>
+        <v>45573</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4452,7 +4457,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4495,7 +4500,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4509,10 +4514,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45215</v>
+        <v>45167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4525,7 +4530,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4568,7 +4573,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4582,10 +4587,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45209</v>
+        <v>45167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4598,7 +4603,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4641,7 +4646,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4655,10 +4660,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45351</v>
+        <v>45300</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4671,7 +4676,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4714,7 +4719,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4728,10 +4733,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45643</v>
+        <v>44935</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4744,7 +4749,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4787,7 +4792,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4801,10 +4806,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45028</v>
+        <v>44981</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4817,7 +4822,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4860,7 +4865,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45468</v>
+        <v>45142</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4890,7 +4895,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4933,7 +4938,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4943,14 +4948,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45167</v>
+        <v>45186</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4963,7 +4968,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5006,7 +5011,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5020,10 +5025,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45167</v>
+        <v>44945</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5036,7 +5041,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5093,10 +5098,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45797</v>
+        <v>44782</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5109,7 +5114,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5152,7 +5157,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5166,10 +5171,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45369</v>
+        <v>45643</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44853</v>
+        <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5255,7 +5260,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5298,7 +5303,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5312,10 +5317,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44957</v>
+        <v>45615</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5371,7 +5376,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5385,10 +5390,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44939</v>
+        <v>45000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>11.6</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5444,7 +5449,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5458,10 +5463,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45161</v>
+        <v>45642</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5474,7 +5479,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5517,7 +5522,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44945</v>
+        <v>45369</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5547,7 +5552,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5590,7 +5595,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45000</v>
+        <v>44508</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5620,7 +5625,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5663,7 +5668,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,14 +5678,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44922</v>
+        <v>45009</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5693,7 +5698,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5736,7 +5741,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5750,10 +5755,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45923</v>
+        <v>45911</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5766,7 +5771,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5809,7 +5814,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5823,10 +5828,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45805</v>
+        <v>45010</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5839,7 +5844,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5882,7 +5887,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45805</v>
+        <v>45621</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5912,7 +5917,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5955,7 +5960,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5969,10 +5974,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45923</v>
+        <v>45596</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5985,7 +5990,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6028,7 +6033,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6042,10 +6047,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45685</v>
+        <v>45923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6058,7 +6063,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6101,7 +6106,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6115,10 +6120,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44939</v>
+        <v>45923</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6131,7 +6136,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6174,7 +6179,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6188,10 +6193,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45615</v>
+        <v>45390</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6204,7 +6209,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6247,7 +6252,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6261,10 +6266,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44935</v>
+        <v>45113</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6277,7 +6282,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6320,7 +6325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6334,10 +6339,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45390</v>
+        <v>44560</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6350,7 +6355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6393,7 +6398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6407,10 +6412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45557</v>
+        <v>44963</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6423,7 +6428,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6466,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6480,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45349</v>
+        <v>45265</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6495,8 +6500,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6539,7 +6549,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6553,10 +6563,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45938</v>
+        <v>45237</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6569,7 +6579,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6612,7 +6622,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6622,14 +6632,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45197</v>
+        <v>45938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6642,7 +6652,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6685,7 +6695,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6699,10 +6709,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44615</v>
+        <v>44894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6715,7 +6725,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6775,7 +6785,7 @@
         <v>45943</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6848,7 +6858,7 @@
         <v>45943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6904,7 +6914,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6918,10 +6928,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45198</v>
+        <v>45799</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6934,7 +6944,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6994,7 +7004,7 @@
         <v>45950</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7050,7 +7060,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7064,10 +7074,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45069</v>
+        <v>45257</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7079,13 +7089,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7128,7 +7133,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7142,10 +7147,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45699</v>
+        <v>45485</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7158,7 +7163,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7201,7 +7206,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7215,10 +7220,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45229</v>
+        <v>45112</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7230,8 +7235,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7274,7 +7284,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7288,10 +7298,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45665</v>
+        <v>45993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7304,7 +7314,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7347,7 +7357,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7361,10 +7371,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45573</v>
+        <v>45146</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7377,7 +7387,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7420,7 +7430,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7434,10 +7444,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45642</v>
+        <v>45882</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7450,7 +7460,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7493,7 +7503,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7507,10 +7517,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45615</v>
+        <v>44616</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7523,7 +7533,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7566,7 +7576,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7580,10 +7590,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45643</v>
+        <v>44614</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7595,8 +7605,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7639,7 +7654,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7653,10 +7668,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45198</v>
+        <v>44980</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7669,7 +7684,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7712,7 +7727,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7726,10 +7741,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45826</v>
+        <v>46019</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7742,7 +7757,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7785,7 +7800,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7799,10 +7814,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44981</v>
+        <v>45557</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7815,7 +7830,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>11.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7858,7 +7873,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7872,10 +7887,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45390</v>
+        <v>46161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7888,7 +7903,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7931,7 +7946,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7945,10 +7960,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45112</v>
+        <v>46042</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7960,13 +7975,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8009,7 +8019,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8023,10 +8033,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45167</v>
+        <v>45946</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8039,7 +8049,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8082,7 +8092,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8096,10 +8106,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45602</v>
+        <v>45615</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8112,7 +8122,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8155,7 +8165,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8169,10 +8179,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45142</v>
+        <v>46056</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8185,7 +8195,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8228,7 +8238,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8238,14 +8248,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45596</v>
+        <v>46056</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8258,7 +8268,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8301,7 +8311,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8315,10 +8325,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45993</v>
+        <v>45198</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8331,7 +8341,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8374,7 +8384,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8388,10 +8398,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45254</v>
+        <v>45229</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8404,7 +8414,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8447,7 +8457,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8461,10 +8471,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45643</v>
+        <v>46086</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8477,7 +8487,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8520,7 +8530,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8534,10 +8544,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45237</v>
+        <v>44957</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8550,7 +8560,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8593,7 +8603,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8607,10 +8617,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46042</v>
+        <v>45349</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8623,7 +8633,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8666,7 +8676,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8676,14 +8686,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44894</v>
+        <v>46104</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8696,7 +8706,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8739,7 +8749,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8753,10 +8763,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46019</v>
+        <v>46181</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8769,7 +8779,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8812,7 +8822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8826,10 +8836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44697</v>
+        <v>44963</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8842,7 +8852,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8885,7 +8895,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8899,10 +8909,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46056</v>
+        <v>45699</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8915,7 +8925,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8958,7 +8968,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8972,10 +8982,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46286</v>
+        <v>45468</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8987,13 +8997,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>12.7</v>
+        <v>3.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9036,7 +9041,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9046,14 +9051,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46056</v>
+        <v>44853</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9066,7 +9071,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9109,7 +9114,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9123,10 +9128,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46262</v>
+        <v>44606</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9139,7 +9144,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9182,7 +9187,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9196,10 +9201,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44963</v>
+        <v>45665</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9212,7 +9217,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9255,7 +9260,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9269,10 +9274,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46244</v>
+        <v>44745</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9284,13 +9289,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9333,7 +9333,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46244</v>
+        <v>45699</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9362,13 +9362,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9411,7 +9406,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9425,10 +9420,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46244</v>
+        <v>45091</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9446,7 +9441,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9489,7 +9484,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9503,10 +9498,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46288</v>
+        <v>46205</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9518,13 +9513,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>11.7</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9567,7 +9557,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9577,14 +9567,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46288</v>
+        <v>44939</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9597,7 +9587,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9640,7 +9630,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9654,10 +9644,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46288</v>
+        <v>44939</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9670,7 +9660,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9713,7 +9703,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9727,10 +9717,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44745</v>
+        <v>44615</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9743,7 +9733,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9786,7 +9776,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9800,10 +9790,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44508</v>
+        <v>46205</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9816,7 +9806,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9859,7 +9849,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9873,10 +9863,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9888,13 +9878,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9937,7 +9922,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9951,10 +9936,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9966,13 +9951,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10015,7 +9995,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10029,10 +10009,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46086</v>
+        <v>44697</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10045,7 +10025,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10088,7 +10068,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10102,10 +10082,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44951</v>
+        <v>45161</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10118,7 +10098,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10161,7 +10141,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10175,10 +10155,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44963</v>
+        <v>45602</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10191,7 +10171,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10234,7 +10214,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10248,10 +10228,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45010</v>
+        <v>44537</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10264,7 +10244,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10307,7 +10287,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10321,10 +10301,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45854</v>
+        <v>45167</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10336,13 +10316,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10385,7 +10360,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10395,14 +10370,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46104</v>
+        <v>45028</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10415,7 +10390,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10458,7 +10433,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10468,14 +10443,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44616</v>
+        <v>45167</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10488,7 +10463,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10531,7 +10506,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10545,10 +10520,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44537</v>
+        <v>45266</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10561,7 +10536,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10604,7 +10579,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10618,10 +10593,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45621</v>
+        <v>45209</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10634,7 +10609,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10677,7 +10652,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10691,10 +10666,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45735</v>
+        <v>46269</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10706,8 +10681,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10750,7 +10730,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10764,10 +10744,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44614</v>
+        <v>45390</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10779,13 +10759,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10828,7 +10803,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10838,14 +10813,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45009</v>
+        <v>45197</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10858,7 +10833,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10901,7 +10876,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10915,10 +10890,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45167</v>
+        <v>45484</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10931,7 +10906,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10974,7 +10949,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10988,10 +10963,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45146</v>
+        <v>44951</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11004,7 +10979,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11047,7 +11022,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11061,10 +11036,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44606</v>
+        <v>44810</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11077,7 +11052,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11120,7 +11095,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11134,10 +11109,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45091</v>
+        <v>45553</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11149,13 +11124,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>9.4</v>
+        <v>6.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11198,7 +11168,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11212,10 +11182,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45265</v>
+        <v>46262</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11227,13 +11197,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11276,7 +11241,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11290,10 +11255,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45582</v>
+        <v>45771</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11306,7 +11271,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11349,7 +11314,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11363,10 +11328,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45113</v>
+        <v>45470</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11378,8 +11343,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11422,7 +11392,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11436,10 +11406,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45911</v>
+        <v>45538</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11452,7 +11422,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11495,7 +11465,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11509,10 +11479,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44980</v>
+        <v>46244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11524,8 +11494,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11568,7 +11543,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11582,10 +11557,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45257</v>
+        <v>46244</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11597,8 +11572,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11641,7 +11621,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11655,10 +11635,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45799</v>
+        <v>46244</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11670,8 +11650,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11714,7 +11699,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11728,10 +11713,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45699</v>
+        <v>46244</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11743,8 +11728,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11787,7 +11777,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11801,10 +11791,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44560</v>
+        <v>46244</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11816,8 +11806,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11860,7 +11855,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11874,10 +11869,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45485</v>
+        <v>46286</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11889,8 +11884,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>12.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11933,7 +11933,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11943,14 +11943,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45266</v>
+        <v>45351</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12006,7 +12006,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12020,10 +12020,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45553</v>
+        <v>45797</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12079,7 +12079,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12093,10 +12093,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45470</v>
+        <v>46288</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12110,11 +12110,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.1</v>
+        <v>11.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12157,7 +12157,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12167,14 +12167,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45538</v>
+        <v>46288</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12244,10 +12244,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45882</v>
+        <v>45643</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12303,7 +12303,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46161</v>
+        <v>46288</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12390,10 +12390,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45946</v>
+        <v>45805</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12463,10 +12463,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46181</v>
+        <v>45805</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12522,7 +12522,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12536,10 +12536,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46205</v>
+        <v>45685</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12595,7 +12595,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12609,10 +12609,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46205</v>
+        <v>45826</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12668,7 +12668,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46205</v>
+        <v>45254</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12741,7 +12741,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12755,10 +12755,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46252</v>
+        <v>45854</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12770,8 +12770,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12814,7 +12819,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12828,10 +12833,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46269</v>
+        <v>45735</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12843,13 +12848,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>46253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>46253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45468</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1586,7 +1586,7 @@
         <v>46244</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1648,144 +1648,144 @@
         </is>
       </c>
       <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 33003-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44922</v>
+        <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45069</v>
+        <v>44810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4084,11 +4084,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>HJO</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4135,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4145,14 +4140,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>45186</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4165,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45582</v>
+        <v>44782</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4238,7 +4233,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4276,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4295,10 +4290,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45198</v>
+        <v>45215</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4311,7 +4306,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4354,7 +4349,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4368,10 +4363,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45198</v>
+        <v>45209</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4384,7 +4379,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4427,7 +4422,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4441,10 +4436,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45573</v>
+        <v>45468</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4457,7 +4452,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4500,7 +4495,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4514,10 +4509,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45167</v>
+        <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4530,7 +4525,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4573,7 +4568,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4583,14 +4578,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45167</v>
+        <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4603,7 +4598,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4646,7 +4641,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4656,14 +4651,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45300</v>
+        <v>46019</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4676,7 +4671,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4719,7 +4714,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4733,10 +4728,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44935</v>
+        <v>45643</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4749,7 +4744,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4792,7 +4787,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4806,10 +4801,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44981</v>
+        <v>44939</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4822,7 +4817,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>11.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4865,7 +4860,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4879,10 +4874,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45142</v>
+        <v>45797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4895,7 +4890,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4938,7 +4933,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4948,14 +4943,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45186</v>
+        <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4968,7 +4963,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5011,7 +5006,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5025,10 +5020,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44945</v>
+        <v>46042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5041,7 +5036,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5094,14 +5089,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44782</v>
+        <v>44922</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5114,7 +5109,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5157,7 +5152,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5171,10 +5166,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45643</v>
+        <v>44939</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5187,7 +5182,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5230,7 +5225,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45215</v>
+        <v>46056</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5260,7 +5255,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5303,7 +5298,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5317,10 +5312,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45615</v>
+        <v>44935</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5333,7 +5328,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5376,7 +5371,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5386,14 +5381,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45000</v>
+        <v>46056</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5406,7 +5401,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5449,7 +5444,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5463,10 +5458,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45642</v>
+        <v>45390</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5479,7 +5474,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5522,7 +5517,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5532,14 +5527,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45369</v>
+        <v>45197</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5552,7 +5547,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5595,7 +5590,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44508</v>
+        <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5625,7 +5620,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5668,7 +5663,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5682,10 +5677,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45009</v>
+        <v>45923</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5698,7 +5693,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5741,7 +5736,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5755,10 +5750,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5771,7 +5766,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5814,7 +5809,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5828,10 +5823,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45010</v>
+        <v>45805</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5844,7 +5839,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5887,7 +5882,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5901,10 +5896,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45621</v>
+        <v>45805</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5917,7 +5912,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5960,7 +5955,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5974,10 +5969,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45596</v>
+        <v>45198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5990,7 +5985,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6033,7 +6028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6047,10 +6042,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45923</v>
+        <v>45685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6063,7 +6058,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6106,7 +6101,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6120,10 +6115,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45923</v>
+        <v>46086</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6136,7 +6131,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6179,7 +6174,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6193,10 +6188,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45390</v>
+        <v>45938</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6209,7 +6204,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6252,7 +6247,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6266,10 +6261,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45113</v>
+        <v>45069</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6281,8 +6276,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44560</v>
+        <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44963</v>
+        <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45265</v>
+        <v>45699</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6500,13 +6500,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45237</v>
+        <v>45950</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6622,7 +6617,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6632,14 +6627,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45938</v>
+        <v>46104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44894</v>
+        <v>45573</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6725,7 +6720,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6768,7 +6763,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6782,10 +6777,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45943</v>
+        <v>45643</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6798,7 +6793,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6841,7 +6836,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45943</v>
+        <v>44981</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6871,7 +6866,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6914,7 +6909,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6928,10 +6923,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45799</v>
+        <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6943,8 +6938,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45950</v>
+        <v>45167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45257</v>
+        <v>45602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45485</v>
+        <v>45142</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45112</v>
+        <v>45596</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7235,13 +7235,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7284,7 +7279,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7298,10 +7293,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45993</v>
+        <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7313,8 +7308,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7357,7 +7357,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45146</v>
+        <v>45993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45882</v>
+        <v>45198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44616</v>
+        <v>45113</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44614</v>
+        <v>45911</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7605,13 +7605,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7654,7 +7649,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7668,10 +7663,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44980</v>
+        <v>45257</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7684,7 +7679,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7727,7 +7722,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7741,10 +7736,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46019</v>
+        <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7757,7 +7752,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7800,7 +7795,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7810,14 +7805,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45557</v>
+        <v>45484</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7830,7 +7825,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>11.5</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7873,7 +7868,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7887,10 +7882,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46161</v>
+        <v>45826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7946,7 +7941,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7960,10 +7955,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46042</v>
+        <v>45254</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7976,7 +7971,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8019,7 +8014,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8033,10 +8028,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45946</v>
+        <v>45028</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8049,7 +8044,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8092,7 +8087,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8106,10 +8101,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45615</v>
+        <v>45167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8165,7 +8160,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8179,10 +8174,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46056</v>
+        <v>45167</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8195,7 +8190,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8238,7 +8233,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8248,14 +8243,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46056</v>
+        <v>45882</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8268,7 +8263,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8311,7 +8306,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8325,10 +8320,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45198</v>
+        <v>45369</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8341,7 +8336,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8384,7 +8379,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45229</v>
+        <v>46161</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8414,7 +8409,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8457,7 +8452,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8471,10 +8466,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46086</v>
+        <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8487,7 +8482,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8530,7 +8525,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8544,10 +8539,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44957</v>
+        <v>45854</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8559,8 +8554,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45349</v>
+        <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8686,14 +8686,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46104</v>
+        <v>45735</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8749,7 +8749,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46181</v>
+        <v>45161</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44963</v>
+        <v>45000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45699</v>
+        <v>46181</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8968,7 +8968,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45468</v>
+        <v>45615</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9041,7 +9041,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44853</v>
+        <v>45557</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>11.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9114,7 +9114,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9128,10 +9128,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44606</v>
+        <v>45349</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45665</v>
+        <v>46205</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9260,7 +9260,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44745</v>
+        <v>46205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9333,7 +9333,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45699</v>
+        <v>46205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9406,7 +9406,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45091</v>
+        <v>46252</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9435,13 +9435,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>9.4</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9484,7 +9479,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9498,10 +9493,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46205</v>
+        <v>45229</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9514,7 +9509,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9557,7 +9552,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9571,10 +9566,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44939</v>
+        <v>45665</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9587,7 +9582,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9630,7 +9625,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9644,10 +9639,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44939</v>
+        <v>45642</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9660,7 +9655,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9703,7 +9698,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9717,10 +9712,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44615</v>
+        <v>45615</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9733,7 +9728,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9776,7 +9771,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9790,10 +9785,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46205</v>
+        <v>45198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9806,7 +9801,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9849,7 +9844,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9863,10 +9858,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46205</v>
+        <v>45390</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9879,7 +9874,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9922,7 +9917,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46252</v>
+        <v>45643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9952,7 +9947,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9995,7 +9990,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10009,10 +10004,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44697</v>
+        <v>45237</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10025,7 +10020,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10068,7 +10063,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10082,10 +10077,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45161</v>
+        <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10097,8 +10092,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10141,7 +10141,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45602</v>
+        <v>44894</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10214,7 +10214,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44537</v>
+        <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45167</v>
+        <v>46286</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10316,8 +10316,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>12.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10360,7 +10365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10374,10 +10379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45028</v>
+        <v>44963</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10390,7 +10395,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10433,7 +10438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10443,14 +10448,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45167</v>
+        <v>46262</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10463,7 +10468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10506,7 +10511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10520,10 +10525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45266</v>
+        <v>44745</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10541,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10579,7 +10584,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10593,10 +10598,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45209</v>
+        <v>46244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10608,8 +10613,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>5.4</v>
+        <v>8.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10652,7 +10662,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10666,10 +10676,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46269</v>
+        <v>46244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10687,7 +10697,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10730,7 +10740,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10744,10 +10754,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45390</v>
+        <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10760,7 +10770,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10803,7 +10813,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10813,14 +10823,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45197</v>
+        <v>46244</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10832,8 +10842,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10876,7 +10891,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10886,14 +10901,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45484</v>
+        <v>46288</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10905,8 +10920,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>11.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10949,7 +10969,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10959,14 +10979,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44951</v>
+        <v>46288</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10979,7 +10999,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11022,7 +11042,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11036,10 +11056,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44810</v>
+        <v>46288</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11052,7 +11072,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11095,7 +11115,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11109,10 +11129,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45553</v>
+        <v>44951</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11125,7 +11145,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>6.5</v>
+        <v>1.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11168,7 +11188,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11182,10 +11202,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11197,8 +11217,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11241,7 +11266,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11255,10 +11280,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45771</v>
+        <v>46244</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11270,8 +11295,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11314,7 +11344,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11328,10 +11358,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45470</v>
+        <v>44963</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11343,13 +11373,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11392,7 +11417,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11406,10 +11431,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45538</v>
+        <v>45010</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11422,7 +11447,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11465,7 +11490,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11479,10 +11504,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46244</v>
+        <v>44616</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11494,13 +11519,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11543,7 +11563,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11557,10 +11577,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46244</v>
+        <v>44537</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11572,13 +11592,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11621,7 +11636,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11635,10 +11650,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46244</v>
+        <v>45621</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11650,13 +11665,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11699,7 +11709,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11713,10 +11723,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46244</v>
+        <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11730,11 +11740,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11777,7 +11787,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11791,10 +11801,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46244</v>
+        <v>45009</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11806,13 +11816,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11855,7 +11860,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11865,14 +11870,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46286</v>
+        <v>45167</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11884,13 +11889,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>12.7</v>
+        <v>5.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11933,7 +11933,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11943,14 +11943,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45351</v>
+        <v>45146</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12006,7 +12006,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12020,10 +12020,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45797</v>
+        <v>44606</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12079,7 +12079,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12093,10 +12093,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46288</v>
+        <v>45091</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>11.7</v>
+        <v>9.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12157,7 +12157,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12167,14 +12167,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46288</v>
+        <v>45582</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12244,10 +12244,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45643</v>
+        <v>44980</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12303,7 +12303,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46288</v>
+        <v>45699</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12390,10 +12390,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45805</v>
+        <v>44560</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12463,10 +12463,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45805</v>
+        <v>45485</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12522,7 +12522,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12536,10 +12536,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45685</v>
+        <v>45266</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12595,7 +12595,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12609,10 +12609,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45826</v>
+        <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12668,7 +12668,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45254</v>
+        <v>45470</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12697,8 +12697,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12741,7 +12746,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12755,10 +12760,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45854</v>
+        <v>45538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12770,13 +12775,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12833,10 +12833,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45735</v>
+        <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>46253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>46253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45468</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>46244</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>45186</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>44782</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45215</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>45209</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45468</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>46019</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45643</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44939</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>46042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>44922</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44939</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>46056</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44935</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>46056</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45390</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45197</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>45923</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>45923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45805</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>45805</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>46086</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45938</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45069</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45699</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45950</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>46104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45573</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45643</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44981</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45142</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45596</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45113</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45911</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45257</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45484</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45254</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>45028</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45167</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45882</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45369</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>46161</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45854</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45735</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>45161</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>46181</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45615</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45557</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45349</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>46205</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>46205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>46205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>46252</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>45229</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45665</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45642</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45615</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45390</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45237</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44894</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>46286</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44963</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46262</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44745</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>46244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>46244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>46244</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>46288</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46288</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46288</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44951</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>46244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>46244</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44963</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>45010</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44616</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44537</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>45621</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45009</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45167</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45146</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44606</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45091</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>45582</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44980</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45699</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44560</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45485</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45266</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45470</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>46253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>46253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45468</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>46244</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>45186</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>44782</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45215</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>45209</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45468</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>46019</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45643</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44939</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>46042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>44922</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44939</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>46056</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44935</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>46056</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45390</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45197</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>45923</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>45923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45805</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>45805</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>46086</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45938</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45069</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45699</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45950</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>46104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45573</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45643</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44981</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45142</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45596</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45113</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45911</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45257</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45484</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45254</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>45028</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45167</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45882</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45369</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>46161</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45854</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45735</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>45161</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>46181</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45615</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45557</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45349</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>46205</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>46205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>46205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>46252</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>45229</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45665</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45642</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45615</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45390</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45237</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44894</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>46286</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44963</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46262</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44745</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>46244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>46244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>46244</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>46288</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46288</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46288</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44951</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>46244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>46244</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44963</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>45010</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44616</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44537</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>45621</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45009</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45167</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45146</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44606</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45091</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>45582</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44980</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45699</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44560</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45485</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45266</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45470</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 10014-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46253</v>
+        <v>45719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1284,20 +1284,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1308,374 +1308,373 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 34275-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 34277-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>46253</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.8</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 26270-2024</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45468</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>5.6</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1696,7 +1695,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1789,7 +1788,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10014-2025</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45719</v>
+        <v>46244</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,20 +1817,25 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1843,55 +1847,51 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
-        <v/>
-      </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
         <v/>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45300</v>
+        <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44810</v>
+        <v>45069</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4084,6 +4084,11 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>HJO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4130,7 +4135,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4140,14 +4145,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45186</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44782</v>
+        <v>45582</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4233,7 +4238,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4276,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4290,10 +4295,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45215</v>
+        <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4306,7 +4311,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4349,7 +4354,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4363,10 +4368,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45209</v>
+        <v>45198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4379,7 +4384,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4422,7 +4427,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45468</v>
+        <v>45538</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4452,7 +4457,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4495,7 +4500,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4509,10 +4514,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44853</v>
+        <v>45573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4525,7 +4530,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4585,7 +4590,7 @@
         <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4641,7 +4646,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4655,10 +4660,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46019</v>
+        <v>45167</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4671,7 +4676,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4714,7 +4719,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4728,10 +4733,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45643</v>
+        <v>45167</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4744,7 +4749,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4787,7 +4792,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4801,10 +4806,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44939</v>
+        <v>45797</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4817,7 +4822,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4860,7 +4865,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45797</v>
+        <v>45643</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4890,7 +4895,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4933,7 +4938,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4943,14 +4948,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44945</v>
+        <v>45300</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4963,7 +4968,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5006,7 +5011,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5020,10 +5025,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46042</v>
+        <v>45805</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5036,7 +5041,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5089,14 +5094,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44922</v>
+        <v>45805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5109,7 +5114,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5152,7 +5157,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5166,10 +5171,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44939</v>
+        <v>45685</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46056</v>
+        <v>44935</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5255,7 +5260,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5298,7 +5303,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5308,14 +5313,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44935</v>
+        <v>45186</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5328,7 +5333,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5371,7 +5376,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5381,14 +5386,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46056</v>
+        <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5444,7 +5449,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5458,10 +5463,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45390</v>
+        <v>45142</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5474,7 +5479,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5517,7 +5522,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5527,14 +5532,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45197</v>
+        <v>44945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5547,7 +5552,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5590,7 +5595,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44615</v>
+        <v>45923</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5620,7 +5625,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5680,7 +5685,7 @@
         <v>45923</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5736,7 +5741,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5750,10 +5755,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45923</v>
+        <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5766,7 +5771,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5809,7 +5814,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5823,10 +5828,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45805</v>
+        <v>44782</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5839,7 +5844,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5882,7 +5887,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45805</v>
+        <v>45254</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5912,7 +5917,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5955,7 +5960,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5969,10 +5974,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45198</v>
+        <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5985,7 +5990,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6028,7 +6033,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6042,10 +6047,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45685</v>
+        <v>45938</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6058,7 +6063,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6101,7 +6106,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6115,10 +6120,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46086</v>
+        <v>45943</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6131,7 +6136,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6174,7 +6179,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6188,10 +6193,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45938</v>
+        <v>45943</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6204,7 +6209,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6247,7 +6252,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6261,10 +6266,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45069</v>
+        <v>45215</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6276,13 +6281,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45943</v>
+        <v>45643</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45943</v>
+        <v>45950</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45699</v>
+        <v>45854</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6500,8 +6500,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45950</v>
+        <v>45615</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6627,14 +6632,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46104</v>
+        <v>45735</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6647,7 +6652,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6704,10 +6709,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45573</v>
+        <v>45000</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6763,7 +6768,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6793,7 +6798,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6836,7 +6841,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6850,10 +6855,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44981</v>
+        <v>45369</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6866,7 +6871,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6909,7 +6914,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6923,10 +6928,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45112</v>
+        <v>44508</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6938,13 +6943,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45167</v>
+        <v>46042</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45602</v>
+        <v>45009</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45142</v>
+        <v>45010</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45596</v>
+        <v>45993</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45265</v>
+        <v>45621</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7308,13 +7308,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7357,7 +7352,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7371,10 +7366,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45993</v>
+        <v>45596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7387,7 +7382,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7430,7 +7425,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7444,10 +7439,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45198</v>
+        <v>46056</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7460,7 +7455,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7503,7 +7498,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7513,14 +7508,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45113</v>
+        <v>46056</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7533,7 +7528,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7576,7 +7571,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7590,10 +7585,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45911</v>
+        <v>45390</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7606,7 +7601,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7649,7 +7644,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7663,10 +7658,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45257</v>
+        <v>46086</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7679,7 +7674,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7722,7 +7717,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7736,10 +7731,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45799</v>
+        <v>44560</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7752,7 +7747,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7795,7 +7790,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7805,14 +7800,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45484</v>
+        <v>44963</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7825,7 +7820,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7868,7 +7863,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7882,10 +7877,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45826</v>
+        <v>45237</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7898,7 +7893,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7941,7 +7936,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7955,10 +7950,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45254</v>
+        <v>44894</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7971,7 +7966,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8014,7 +8009,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8024,14 +8019,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45028</v>
+        <v>46104</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8044,7 +8039,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8087,7 +8082,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8101,10 +8096,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45167</v>
+        <v>45485</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8117,7 +8112,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8160,7 +8155,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8174,10 +8169,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45167</v>
+        <v>45911</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8190,7 +8185,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8233,7 +8228,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8247,10 +8242,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45882</v>
+        <v>45112</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8262,8 +8257,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8306,7 +8306,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8320,10 +8320,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45369</v>
+        <v>45146</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8379,7 +8379,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8393,10 +8393,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46161</v>
+        <v>44616</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45946</v>
+        <v>45113</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8525,7 +8525,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45854</v>
+        <v>44614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8556,11 +8556,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44957</v>
+        <v>45265</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8632,8 +8632,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8676,7 +8681,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8690,10 +8695,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45735</v>
+        <v>45799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8706,7 +8711,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8749,7 +8754,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8763,10 +8768,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45161</v>
+        <v>44980</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8779,7 +8784,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8822,7 +8827,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45000</v>
+        <v>45257</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8852,7 +8857,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>7.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8895,7 +8900,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8909,10 +8914,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46181</v>
+        <v>45557</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8925,7 +8930,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8985,7 +8990,7 @@
         <v>45615</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9041,7 +9046,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9055,10 +9060,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45557</v>
+        <v>45882</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9071,7 +9076,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>11.5</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9114,7 +9119,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9128,10 +9133,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45349</v>
+        <v>45198</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9144,7 +9149,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9187,7 +9192,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9201,10 +9206,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46205</v>
+        <v>45229</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9217,7 +9222,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9260,7 +9265,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9274,10 +9279,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46205</v>
+        <v>46161</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9290,7 +9295,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9333,7 +9338,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9347,10 +9352,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46205</v>
+        <v>45946</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9363,7 +9368,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9406,7 +9411,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9420,10 +9425,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46252</v>
+        <v>44957</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9436,7 +9441,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9479,7 +9484,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9493,10 +9498,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45229</v>
+        <v>45349</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9509,7 +9514,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9552,7 +9557,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9566,10 +9571,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45665</v>
+        <v>44963</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9582,7 +9587,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9625,7 +9630,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9639,10 +9644,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45642</v>
+        <v>45699</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9655,7 +9660,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9698,7 +9703,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9712,10 +9717,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45615</v>
+        <v>45468</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9728,7 +9733,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9771,7 +9776,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9785,10 +9790,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45198</v>
+        <v>44853</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9801,7 +9806,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9844,7 +9849,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9858,10 +9863,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45390</v>
+        <v>44606</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9874,7 +9879,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9917,7 +9922,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9931,10 +9936,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45643</v>
+        <v>46181</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9947,7 +9952,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9990,7 +9995,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10004,10 +10009,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45237</v>
+        <v>45665</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10020,7 +10025,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10063,7 +10068,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10077,10 +10082,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46269</v>
+        <v>44745</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10092,13 +10097,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10141,7 +10141,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44894</v>
+        <v>45699</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10214,7 +10214,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44697</v>
+        <v>45091</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10243,8 +10243,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10287,7 +10292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10301,10 +10306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46286</v>
+        <v>44939</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10316,13 +10321,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>12.7</v>
+        <v>2.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10365,7 +10365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10379,10 +10379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44963</v>
+        <v>44939</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10438,7 +10438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46262</v>
+        <v>44615</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10511,7 +10511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10525,10 +10525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44745</v>
+        <v>46205</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10584,7 +10584,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46244</v>
+        <v>44697</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10613,13 +10613,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10662,7 +10657,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10676,10 +10671,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46244</v>
+        <v>45161</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10691,13 +10686,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10740,7 +10730,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10754,10 +10744,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44508</v>
+        <v>45602</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10770,7 +10760,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10813,7 +10803,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10827,10 +10817,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10842,13 +10832,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10891,7 +10876,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10905,10 +10890,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46288</v>
+        <v>46205</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10920,13 +10905,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>11.7</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10969,7 +10949,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10979,14 +10959,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46288</v>
+        <v>44537</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10999,7 +10979,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11042,7 +11022,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11056,10 +11036,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46288</v>
+        <v>45167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11072,7 +11052,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11115,7 +11095,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11129,10 +11109,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44951</v>
+        <v>46252</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11145,7 +11125,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11188,7 +11168,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11202,10 +11182,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46244</v>
+        <v>45028</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11217,13 +11197,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11266,7 +11241,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11276,14 +11251,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46244</v>
+        <v>45167</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11295,13 +11270,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11344,7 +11314,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11358,10 +11328,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44963</v>
+        <v>45266</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11374,7 +11344,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11417,7 +11387,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11431,10 +11401,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45010</v>
+        <v>45209</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11490,7 +11460,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11504,10 +11474,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44616</v>
+        <v>45390</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11520,7 +11490,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11563,7 +11533,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11573,14 +11543,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44537</v>
+        <v>45197</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11593,7 +11563,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11636,7 +11606,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11646,14 +11616,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45621</v>
+        <v>45484</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11666,7 +11636,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11709,7 +11679,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11723,10 +11693,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44614</v>
+        <v>46269</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11740,11 +11710,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11787,7 +11757,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11801,10 +11771,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45009</v>
+        <v>44951</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11817,7 +11787,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11860,7 +11830,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11870,14 +11840,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45167</v>
+        <v>44810</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11890,7 +11860,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11933,7 +11903,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11947,10 +11917,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45146</v>
+        <v>45553</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11963,7 +11933,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12006,7 +11976,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12020,10 +11990,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44606</v>
+        <v>45771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12036,7 +12006,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12079,7 +12049,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12093,10 +12063,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45091</v>
+        <v>45470</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12110,11 +12080,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12157,7 +12127,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12171,10 +12141,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45582</v>
+        <v>46262</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12187,7 +12157,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12230,7 +12200,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12244,10 +12214,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44980</v>
+        <v>46244</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12259,8 +12229,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12303,7 +12278,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12317,10 +12292,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45699</v>
+        <v>46244</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12332,8 +12307,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12376,7 +12356,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12390,10 +12370,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44560</v>
+        <v>46244</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12405,8 +12385,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12449,7 +12434,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12463,10 +12448,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45485</v>
+        <v>46244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12478,8 +12463,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12522,7 +12512,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12536,10 +12526,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45266</v>
+        <v>46244</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12551,8 +12541,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12595,7 +12590,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12609,10 +12604,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45553</v>
+        <v>46286</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12624,8 +12619,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>6.5</v>
+        <v>12.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12668,7 +12668,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45470</v>
+        <v>46288</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12699,11 +12699,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>7.1</v>
+        <v>11.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12746,7 +12746,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12756,14 +12756,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45538</v>
+        <v>46288</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12833,10 +12833,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45771</v>
+        <v>46288</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1373,14 +1373,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46253</v>
+        <v>45468</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1393,23 +1393,23 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1417,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1433,252 +1433,252 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 34275-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 34277-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46253</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.8</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 26270-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45468</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1695,7 +1695,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1757,144 +1757,144 @@
         </is>
       </c>
       <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 33003-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44922</v>
+        <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45069</v>
+        <v>44810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4084,11 +4084,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>HJO</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4135,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4149,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>45215</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4165,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45582</v>
+        <v>44782</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4238,7 +4233,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4276,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4295,10 +4290,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45198</v>
+        <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4311,7 +4306,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4354,7 +4349,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4368,10 +4363,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45198</v>
+        <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4384,7 +4379,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4427,7 +4422,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4437,14 +4432,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45538</v>
+        <v>45186</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4457,7 +4452,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4500,7 +4495,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4514,10 +4509,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45573</v>
+        <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4530,7 +4525,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4590,7 +4585,7 @@
         <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4646,7 +4641,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4660,10 +4655,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45167</v>
+        <v>46019</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4676,7 +4671,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4719,7 +4714,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4733,10 +4728,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45167</v>
+        <v>45643</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4749,7 +4744,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4809,7 +4804,7 @@
         <v>45797</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4865,7 +4860,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4879,10 +4874,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45643</v>
+        <v>44939</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4895,7 +4890,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>11.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4938,7 +4933,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4948,14 +4943,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45300</v>
+        <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4968,7 +4963,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5011,7 +5006,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5028,7 +5023,7 @@
         <v>45805</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5041,7 +5036,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5101,7 +5096,7 @@
         <v>45805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5114,7 +5109,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5174,7 +5169,7 @@
         <v>45685</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5230,7 +5225,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5240,14 +5235,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44935</v>
+        <v>44922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5260,7 +5255,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5303,7 +5298,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5313,14 +5308,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45186</v>
+        <v>44939</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5333,7 +5328,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5376,7 +5371,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5390,10 +5385,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44981</v>
+        <v>44935</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5406,7 +5401,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5449,7 +5444,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5463,10 +5458,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45142</v>
+        <v>45390</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5479,7 +5474,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5522,7 +5517,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5536,10 +5531,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44945</v>
+        <v>45826</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5552,7 +5547,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5595,7 +5590,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45923</v>
+        <v>46042</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5625,7 +5620,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5668,7 +5663,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5678,14 +5673,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45923</v>
+        <v>45197</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5698,7 +5693,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5741,7 +5736,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5755,10 +5750,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45826</v>
+        <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5771,7 +5766,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5814,7 +5809,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5828,10 +5823,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44782</v>
+        <v>45254</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5844,7 +5839,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5887,7 +5882,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5901,10 +5896,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45254</v>
+        <v>45923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5917,7 +5912,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5960,7 +5955,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5974,10 +5969,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46019</v>
+        <v>45923</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5990,7 +5985,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6033,7 +6028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6047,10 +6042,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45938</v>
+        <v>45198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6063,7 +6058,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6106,7 +6101,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6120,10 +6115,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45943</v>
+        <v>45938</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6136,7 +6131,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6179,7 +6174,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6193,10 +6188,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45943</v>
+        <v>45854</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6208,8 +6203,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45215</v>
+        <v>45069</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6281,8 +6281,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45643</v>
+        <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6412,10 +6417,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45950</v>
+        <v>45735</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45854</v>
+        <v>45943</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6500,13 +6505,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45615</v>
+        <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6622,7 +6622,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45735</v>
+        <v>45950</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6695,7 +6695,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45000</v>
+        <v>46056</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6768,7 +6768,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6778,14 +6778,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45642</v>
+        <v>46056</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45369</v>
+        <v>45573</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44508</v>
+        <v>45643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46042</v>
+        <v>44981</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45009</v>
+        <v>45112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7089,8 +7089,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7133,7 +7138,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7147,10 +7152,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45010</v>
+        <v>45167</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7163,7 +7168,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7206,7 +7211,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7220,10 +7225,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45993</v>
+        <v>45602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7236,7 +7241,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7279,7 +7284,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7293,10 +7298,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45621</v>
+        <v>45142</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7309,7 +7314,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7369,7 +7374,7 @@
         <v>45596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7425,7 +7430,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7439,10 +7444,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46056</v>
+        <v>45993</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7455,7 +7460,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7498,7 +7503,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7508,14 +7513,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46056</v>
+        <v>45198</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7528,7 +7533,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7571,7 +7576,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7585,10 +7590,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45390</v>
+        <v>46086</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7601,7 +7606,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7644,7 +7649,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7654,14 +7659,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46086</v>
+        <v>45484</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7674,7 +7679,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7717,7 +7722,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7727,14 +7732,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44560</v>
+        <v>46104</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7747,7 +7752,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7790,7 +7795,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7804,10 +7809,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44963</v>
+        <v>45028</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7820,7 +7825,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7863,7 +7868,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7877,10 +7882,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45237</v>
+        <v>45167</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7936,7 +7941,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7950,10 +7955,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44894</v>
+        <v>45167</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7966,7 +7971,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8009,7 +8014,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8019,14 +8024,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46104</v>
+        <v>45265</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8038,8 +8043,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8082,7 +8092,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8096,10 +8106,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45485</v>
+        <v>45369</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8112,7 +8122,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8155,7 +8165,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8169,10 +8179,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45911</v>
+        <v>44957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8185,7 +8195,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8228,7 +8238,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8242,10 +8252,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8257,13 +8267,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8306,7 +8311,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8320,10 +8325,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45146</v>
+        <v>45911</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8336,7 +8341,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8379,7 +8384,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8393,10 +8398,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44616</v>
+        <v>45161</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8409,7 +8414,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8452,7 +8457,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8466,10 +8471,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45113</v>
+        <v>45257</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8482,7 +8487,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8525,7 +8530,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8539,10 +8544,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44614</v>
+        <v>45799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8554,13 +8559,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45265</v>
+        <v>45000</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8632,13 +8632,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8681,7 +8676,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8695,10 +8690,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45799</v>
+        <v>45615</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8711,7 +8706,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8754,7 +8749,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8768,10 +8763,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44980</v>
+        <v>45557</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8784,7 +8779,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>11.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8827,7 +8822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8841,10 +8836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45257</v>
+        <v>45349</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8857,7 +8852,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8900,7 +8895,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8914,10 +8909,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45557</v>
+        <v>45882</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8930,7 +8925,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>11.5</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8973,7 +8968,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8987,10 +8982,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45615</v>
+        <v>45229</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9003,7 +8998,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9046,7 +9041,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9060,10 +9055,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45882</v>
+        <v>46161</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9076,7 +9071,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9119,7 +9114,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9133,10 +9128,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45198</v>
+        <v>45665</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9149,7 +9144,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9192,7 +9187,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9206,10 +9201,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45229</v>
+        <v>45946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9222,7 +9217,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9265,7 +9260,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9279,10 +9274,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46161</v>
+        <v>45642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9295,7 +9290,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9338,7 +9333,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9352,10 +9347,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45946</v>
+        <v>45615</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9368,7 +9363,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9411,7 +9406,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9425,10 +9420,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44957</v>
+        <v>45198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9441,7 +9436,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9484,7 +9479,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9498,10 +9493,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45349</v>
+        <v>45390</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9557,7 +9552,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9571,10 +9566,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44963</v>
+        <v>45643</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9587,7 +9582,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9630,7 +9625,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9644,10 +9639,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45699</v>
+        <v>46181</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9660,7 +9655,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9703,7 +9698,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9717,10 +9712,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45468</v>
+        <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9733,7 +9728,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9776,7 +9771,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9790,10 +9785,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44853</v>
+        <v>44894</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9806,7 +9801,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9849,7 +9844,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9863,10 +9858,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44606</v>
+        <v>44697</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9879,7 +9874,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9922,7 +9917,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46181</v>
+        <v>44963</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9995,7 +9990,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10009,10 +10004,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45665</v>
+        <v>46205</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10025,7 +10020,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10068,7 +10063,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10082,10 +10077,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44745</v>
+        <v>46205</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10098,7 +10093,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10141,7 +10136,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10155,10 +10150,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45699</v>
+        <v>46205</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10171,7 +10166,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10214,7 +10209,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10228,10 +10223,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45091</v>
+        <v>44745</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10243,13 +10238,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>9.4</v>
+        <v>2.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10292,7 +10282,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10306,10 +10296,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44939</v>
+        <v>44508</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10322,7 +10312,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10365,7 +10355,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10379,10 +10369,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44939</v>
+        <v>44951</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10395,7 +10385,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10438,7 +10428,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10452,10 +10442,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44615</v>
+        <v>44963</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10468,7 +10458,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10511,7 +10501,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10525,10 +10515,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46205</v>
+        <v>45010</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10541,7 +10531,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10584,7 +10574,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10598,10 +10588,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44697</v>
+        <v>44616</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10604,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10657,7 +10647,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10671,10 +10661,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45161</v>
+        <v>44537</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10687,7 +10677,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10730,7 +10720,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10744,10 +10734,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45602</v>
+        <v>45621</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10760,7 +10750,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10803,7 +10793,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10817,10 +10807,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46205</v>
+        <v>44614</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10832,8 +10822,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10876,7 +10871,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10890,10 +10885,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46205</v>
+        <v>45009</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10906,7 +10901,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10949,7 +10944,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10959,14 +10954,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44537</v>
+        <v>45167</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10979,7 +10974,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11022,7 +11017,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11036,10 +11031,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45167</v>
+        <v>45146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11052,7 +11047,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11095,7 +11090,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11109,10 +11104,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46252</v>
+        <v>44606</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11125,7 +11120,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11168,7 +11163,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11182,10 +11177,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45028</v>
+        <v>45091</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11197,8 +11192,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11241,7 +11241,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11251,14 +11251,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45167</v>
+        <v>46269</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11270,8 +11270,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11314,7 +11319,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11328,10 +11333,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45266</v>
+        <v>45582</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11344,7 +11349,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11387,7 +11392,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11401,10 +11406,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45209</v>
+        <v>44980</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11417,7 +11422,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11460,7 +11465,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11474,10 +11479,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45390</v>
+        <v>45699</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11490,7 +11495,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11533,7 +11538,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11543,14 +11548,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45197</v>
+        <v>46286</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11562,8 +11567,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>12.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11606,7 +11616,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11616,14 +11626,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45484</v>
+        <v>44560</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11636,7 +11646,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11679,7 +11689,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11693,10 +11703,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46269</v>
+        <v>45485</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11708,13 +11718,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11757,7 +11762,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11771,10 +11776,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44951</v>
+        <v>46262</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11787,7 +11792,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11830,7 +11835,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11844,10 +11849,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44810</v>
+        <v>46244</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11859,8 +11864,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11903,7 +11913,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11917,10 +11927,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45553</v>
+        <v>46244</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11932,8 +11942,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11976,7 +11991,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11990,10 +12005,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45771</v>
+        <v>46244</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12005,8 +12020,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12049,7 +12069,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12063,10 +12083,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45470</v>
+        <v>46288</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12080,11 +12100,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.1</v>
+        <v>11.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12127,7 +12147,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12137,14 +12157,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46262</v>
+        <v>46288</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12157,7 +12177,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12200,7 +12220,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12214,10 +12234,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46244</v>
+        <v>46288</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12229,13 +12249,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12278,7 +12293,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12292,10 +12307,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46244</v>
+        <v>45266</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12307,13 +12322,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12373,7 +12383,7 @@
         <v>46244</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12434,7 +12444,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12451,7 +12461,7 @@
         <v>46244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12469,7 +12479,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12512,7 +12522,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12526,10 +12536,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46244</v>
+        <v>45553</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12541,13 +12551,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12590,7 +12595,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12604,10 +12609,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46286</v>
+        <v>45470</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12621,11 +12626,11 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>12.7</v>
+        <v>7.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12668,7 +12673,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12682,10 +12687,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46288</v>
+        <v>45538</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12697,13 +12702,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>11.7</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12746,7 +12746,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12756,14 +12756,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46288</v>
+        <v>45771</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12833,10 +12833,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46288</v>
+        <v>46252</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 10014-2025</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1264,14 +1264,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45719</v>
+        <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1284,22 +1284,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1317,158 +1317,158 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 10014-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45719</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26270-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45468</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 33003-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1497,8 +1497,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1538,363 +1543,358 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 32951-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 34275-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 34277-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>46253</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.8</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 33003-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 65329-2021</t>
+          <t>A 46998-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44515</v>
+        <v>44852</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55091-2021</t>
+          <t>A 65329-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44474</v>
+        <v>44515</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46998-2022</t>
+          <t>A 32158-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44852</v>
+        <v>44781</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35216-2022</t>
+          <t>A 63257-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44797</v>
+        <v>44508</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28512-2022</t>
+          <t>A 7786-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44748</v>
+        <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2962,7 +2962,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58495-2021</t>
+          <t>A 28512-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44488</v>
+        <v>44748</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32158-2022</t>
+          <t>A 58495-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44781</v>
+        <v>44488</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63257-2021</t>
+          <t>A 32814-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44508</v>
+        <v>44784</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7786-2022</t>
+          <t>A 55091-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44608</v>
+        <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32814-2022</t>
+          <t>A 35216-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44784</v>
+        <v>44797</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12726-2022</t>
+          <t>A 47656-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44641</v>
+        <v>44854</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47656-2022</t>
+          <t>A 7231-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44854</v>
+        <v>44606</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7231-2022</t>
+          <t>A 9210-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44606</v>
+        <v>44616</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32219-2022</t>
+          <t>A 12726-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44781</v>
+        <v>44641</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22586-2022</t>
+          <t>A 56175-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44714</v>
+        <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56175-2021</t>
+          <t>A 32219-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44477</v>
+        <v>44781</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3765,7 +3765,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12544-2022</t>
+          <t>A 22586-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44638</v>
+        <v>44714</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3838,7 +3838,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9184-2022</t>
+          <t>A 12544-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44615</v>
+        <v>44638</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9210-2022</t>
+          <t>A 9184-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44616</v>
+        <v>44615</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3994,14 +3994,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45300</v>
+        <v>45000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4067,14 +4067,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44810</v>
+        <v>44922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45215</v>
+        <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44782</v>
+        <v>45369</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45209</v>
+        <v>44508</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45468</v>
+        <v>45209</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45186</v>
+        <v>45615</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44853</v>
+        <v>45069</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4524,8 +4524,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4568,7 +4573,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4578,14 +4583,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45351</v>
+        <v>45009</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4598,7 +4603,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4641,7 +4646,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4655,10 +4660,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46019</v>
+        <v>45643</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4671,7 +4676,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4714,7 +4719,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4728,10 +4733,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45643</v>
+        <v>45582</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4744,7 +4749,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4787,7 +4792,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4801,10 +4806,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45797</v>
+        <v>45390</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4817,7 +4822,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4860,7 +4865,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44939</v>
+        <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4890,7 +4895,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>11.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4933,7 +4938,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44945</v>
+        <v>45229</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4963,7 +4968,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5006,7 +5011,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5020,10 +5025,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45805</v>
+        <v>45010</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5036,7 +5041,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5089,14 +5094,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45805</v>
+        <v>45197</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5109,7 +5114,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5152,7 +5157,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5162,14 +5167,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45685</v>
+        <v>45484</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5235,14 +5240,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44922</v>
+        <v>45621</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5255,7 +5260,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5298,7 +5303,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5312,10 +5317,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44939</v>
+        <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5328,7 +5333,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5371,7 +5376,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5385,10 +5390,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44935</v>
+        <v>44951</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5444,7 +5449,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5458,10 +5463,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45390</v>
+        <v>44957</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5474,7 +5479,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5517,7 +5522,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45826</v>
+        <v>45349</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5547,7 +5552,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5590,7 +5595,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46042</v>
+        <v>44810</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5620,7 +5625,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5663,7 +5668,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,14 +5678,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45197</v>
+        <v>45198</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5693,7 +5698,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5736,7 +5741,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5750,10 +5755,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44615</v>
+        <v>45198</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5766,7 +5771,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5809,7 +5814,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5823,10 +5828,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45254</v>
+        <v>45390</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5839,7 +5844,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5882,7 +5887,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45923</v>
+        <v>45573</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5912,7 +5917,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5955,7 +5960,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5969,10 +5974,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45923</v>
+        <v>44963</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5985,7 +5990,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6028,7 +6033,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6042,10 +6047,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45198</v>
+        <v>44560</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6058,7 +6063,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6101,7 +6106,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6115,10 +6120,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45938</v>
+        <v>45699</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6131,7 +6136,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6174,7 +6179,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6188,10 +6193,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45854</v>
+        <v>45468</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6203,13 +6208,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45069</v>
+        <v>44853</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6281,13 +6281,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45943</v>
+        <v>45553</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45735</v>
+        <v>44963</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45943</v>
+        <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45699</v>
+        <v>45237</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6636,10 +6631,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45950</v>
+        <v>44894</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46056</v>
+        <v>45665</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6725,7 +6720,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6768,7 +6763,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6778,14 +6773,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46056</v>
+        <v>45771</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6798,7 +6793,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6841,7 +6836,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45573</v>
+        <v>45470</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6870,8 +6865,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45643</v>
+        <v>44745</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44981</v>
+        <v>45538</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7060,7 +7060,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45112</v>
+        <v>45699</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7089,13 +7089,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7138,7 +7133,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7155,7 +7150,7 @@
         <v>45167</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7211,7 +7206,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7225,10 +7220,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45602</v>
+        <v>45167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7241,7 +7236,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7284,7 +7279,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7294,14 +7289,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45142</v>
+        <v>45351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7314,7 +7309,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7357,7 +7352,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7367,14 +7362,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45596</v>
+        <v>45300</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7387,7 +7382,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7430,7 +7425,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7444,10 +7439,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45993</v>
+        <v>45797</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7460,7 +7455,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7503,7 +7498,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7517,10 +7512,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45198</v>
+        <v>45643</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7533,7 +7528,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7576,7 +7571,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7590,10 +7585,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46086</v>
+        <v>45091</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7605,8 +7600,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>9.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7649,7 +7649,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7659,14 +7659,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45484</v>
+        <v>44935</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7722,7 +7722,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7736,10 +7736,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46104</v>
+        <v>45186</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7795,7 +7795,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7809,10 +7809,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45028</v>
+        <v>44981</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7868,7 +7868,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45167</v>
+        <v>44939</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7941,7 +7941,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45167</v>
+        <v>44939</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>11.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45265</v>
+        <v>44615</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8043,13 +8043,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8092,7 +8087,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8106,10 +8101,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45369</v>
+        <v>45142</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8122,7 +8117,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8165,7 +8160,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8179,10 +8174,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44957</v>
+        <v>45805</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8195,7 +8190,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8238,7 +8233,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8252,10 +8247,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45113</v>
+        <v>45805</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8268,7 +8263,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8311,7 +8306,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8325,10 +8320,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45911</v>
+        <v>45685</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8341,7 +8336,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8384,7 +8379,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45161</v>
+        <v>44697</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8414,7 +8409,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8457,7 +8452,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8471,10 +8466,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45257</v>
+        <v>44945</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8487,7 +8482,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8530,7 +8525,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8544,10 +8539,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45799</v>
+        <v>45485</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8560,7 +8555,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8603,7 +8598,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8617,10 +8612,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45000</v>
+        <v>45161</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8633,7 +8628,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8676,7 +8671,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8690,10 +8685,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45615</v>
+        <v>45602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8706,7 +8701,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8749,7 +8744,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8763,10 +8758,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45557</v>
+        <v>45112</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8778,8 +8773,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>11.5</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45349</v>
+        <v>44537</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45882</v>
+        <v>45167</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8968,7 +8968,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45229</v>
+        <v>44782</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9041,7 +9041,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46161</v>
+        <v>45146</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9114,7 +9114,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9128,10 +9128,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45665</v>
+        <v>45826</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45946</v>
+        <v>45254</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9260,7 +9260,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45642</v>
+        <v>44616</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9333,7 +9333,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45615</v>
+        <v>45028</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9406,7 +9406,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9416,14 +9416,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45198</v>
+        <v>45167</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9479,7 +9479,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45390</v>
+        <v>45266</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9552,7 +9552,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45643</v>
+        <v>44614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9581,8 +9581,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9625,7 +9630,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9639,10 +9644,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46181</v>
+        <v>44980</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9655,7 +9660,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9698,7 +9703,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9712,10 +9717,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45237</v>
+        <v>45215</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9728,7 +9733,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9771,7 +9776,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9785,10 +9790,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44894</v>
+        <v>45854</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9800,8 +9805,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9844,7 +9854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9858,10 +9868,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44697</v>
+        <v>45735</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9874,7 +9884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9917,7 +9927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9931,10 +9941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44963</v>
+        <v>45643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9947,7 +9957,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9990,7 +10000,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10004,10 +10014,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46205</v>
+        <v>45557</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10020,7 +10030,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10063,7 +10073,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10077,10 +10087,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46205</v>
+        <v>45615</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10093,7 +10103,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10136,7 +10146,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10150,10 +10160,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46205</v>
+        <v>45938</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10166,7 +10176,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10209,7 +10219,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10223,10 +10233,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44745</v>
+        <v>45943</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10239,7 +10249,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10282,7 +10292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10296,10 +10306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44508</v>
+        <v>45943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10312,7 +10322,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10355,7 +10365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10369,10 +10379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44951</v>
+        <v>45950</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10385,7 +10395,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10428,7 +10438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10442,10 +10452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44963</v>
+        <v>45923</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10458,7 +10468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10501,7 +10511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10515,10 +10525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45010</v>
+        <v>45923</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10531,7 +10541,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10574,7 +10584,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10588,10 +10598,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44616</v>
+        <v>45993</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10604,7 +10614,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10647,7 +10657,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10661,10 +10671,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44537</v>
+        <v>46019</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10677,7 +10687,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10720,7 +10730,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10734,10 +10744,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45621</v>
+        <v>46042</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10750,7 +10760,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10793,7 +10803,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10807,10 +10817,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44614</v>
+        <v>46056</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10822,13 +10832,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10871,7 +10876,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10881,14 +10886,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45009</v>
+        <v>46056</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10901,7 +10906,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10944,7 +10949,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10954,14 +10959,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45167</v>
+        <v>46086</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10974,7 +10979,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11017,7 +11022,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11027,14 +11032,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45146</v>
+        <v>46104</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11047,7 +11052,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11090,7 +11095,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11104,10 +11109,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44606</v>
+        <v>45911</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11120,7 +11125,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11163,7 +11168,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11177,10 +11182,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45091</v>
+        <v>45113</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11192,13 +11197,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11241,7 +11241,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11255,10 +11255,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46269</v>
+        <v>45265</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11272,11 +11272,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11319,7 +11319,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45582</v>
+        <v>45799</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11392,7 +11392,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11406,10 +11406,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44980</v>
+        <v>45257</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11465,7 +11465,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45699</v>
+        <v>45882</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11538,7 +11538,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11552,10 +11552,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46286</v>
+        <v>46161</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11567,13 +11567,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>12.7</v>
+        <v>2.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11616,7 +11611,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11630,10 +11625,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44560</v>
+        <v>45946</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11646,7 +11641,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11689,7 +11684,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11703,10 +11698,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45485</v>
+        <v>46181</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11719,7 +11714,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11762,7 +11757,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11776,10 +11771,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46262</v>
+        <v>46205</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11792,7 +11787,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11835,7 +11830,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11849,10 +11844,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11864,13 +11859,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11913,7 +11903,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11927,10 +11917,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11942,13 +11932,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11991,7 +11976,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12005,10 +11990,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46244</v>
+        <v>46269</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12026,7 +12011,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12069,7 +12054,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12083,10 +12068,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46288</v>
+        <v>46262</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12098,13 +12083,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>11.7</v>
+        <v>4.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12147,7 +12127,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12157,14 +12137,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46288</v>
+        <v>46244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12176,8 +12156,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12220,7 +12205,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12234,10 +12219,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46288</v>
+        <v>46244</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12249,8 +12234,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12293,7 +12283,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12307,10 +12297,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45266</v>
+        <v>46244</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12322,8 +12312,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12366,7 +12361,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12383,7 +12378,7 @@
         <v>46244</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12401,7 +12396,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12444,7 +12439,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12461,7 +12456,7 @@
         <v>46244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12479,7 +12474,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12522,7 +12517,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12536,10 +12531,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45553</v>
+        <v>46286</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12551,8 +12546,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>6.5</v>
+        <v>12.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12595,7 +12595,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12609,10 +12609,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45470</v>
+        <v>46288</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12626,11 +12626,11 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.1</v>
+        <v>11.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12673,7 +12673,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12683,14 +12683,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45538</v>
+        <v>46288</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12746,7 +12746,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12760,10 +12760,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45771</v>
+        <v>46288</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12836,7 +12836,7 @@
         <v>46252</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26270-2024</t>
+          <t>A 10014-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1264,14 +1264,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45468</v>
+        <v>45719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1296,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1317,158 +1317,158 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 26270-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45468</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 10014-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45719</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1485,7 +1485,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1547,144 +1547,144 @@
         </is>
       </c>
       <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 33003-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>46253</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46998-2022</t>
+          <t>A 65329-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44852</v>
+        <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 65329-2021</t>
+          <t>A 55091-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44515</v>
+        <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32158-2022</t>
+          <t>A 46998-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44781</v>
+        <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63257-2021</t>
+          <t>A 35216-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44508</v>
+        <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7786-2022</t>
+          <t>A 28512-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44608</v>
+        <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2962,7 +2962,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28512-2022</t>
+          <t>A 58495-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44748</v>
+        <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58495-2021</t>
+          <t>A 32158-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44488</v>
+        <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32814-2022</t>
+          <t>A 63257-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44784</v>
+        <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55091-2021</t>
+          <t>A 7786-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44474</v>
+        <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35216-2022</t>
+          <t>A 32814-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44797</v>
+        <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47656-2022</t>
+          <t>A 12726-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44854</v>
+        <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7231-2022</t>
+          <t>A 47656-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44606</v>
+        <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9210-2022</t>
+          <t>A 7231-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44616</v>
+        <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12726-2022</t>
+          <t>A 32219-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44641</v>
+        <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56175-2021</t>
+          <t>A 22586-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44477</v>
+        <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32219-2022</t>
+          <t>A 56175-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44781</v>
+        <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3765,7 +3765,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22586-2022</t>
+          <t>A 12544-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44714</v>
+        <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3838,7 +3838,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12544-2022</t>
+          <t>A 9184-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44638</v>
+        <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9184-2022</t>
+          <t>A 9210-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3994,14 +3994,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45000</v>
+        <v>45186</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44922</v>
+        <v>45300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>45215</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45369</v>
+        <v>44810</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44508</v>
+        <v>45209</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45209</v>
+        <v>44782</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45615</v>
+        <v>45468</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45069</v>
+        <v>46019</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4524,13 +4524,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4573,7 +4568,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4587,10 +4582,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45009</v>
+        <v>44853</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4603,7 +4598,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4646,7 +4641,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4656,14 +4651,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45643</v>
+        <v>45351</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4676,7 +4671,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4719,7 +4714,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4733,10 +4728,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45582</v>
+        <v>45643</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4749,7 +4744,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4792,7 +4787,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4806,10 +4801,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45390</v>
+        <v>46042</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4865,7 +4860,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4879,10 +4874,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45198</v>
+        <v>44939</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4895,7 +4890,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.800000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4938,7 +4933,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4952,10 +4947,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45229</v>
+        <v>44945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4968,7 +4963,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5011,7 +5006,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5025,10 +5020,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45010</v>
+        <v>46056</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5041,7 +5036,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5098,10 +5093,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45197</v>
+        <v>46056</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5114,7 +5109,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5157,7 +5152,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5167,14 +5162,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45484</v>
+        <v>45797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5187,7 +5182,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5230,7 +5225,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5240,14 +5235,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45621</v>
+        <v>44922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5260,7 +5255,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5303,7 +5298,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5317,10 +5312,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45596</v>
+        <v>44939</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5333,7 +5328,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5376,7 +5371,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5390,10 +5385,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44951</v>
+        <v>44935</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5449,7 +5444,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5463,10 +5458,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44957</v>
+        <v>45923</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5479,7 +5474,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5522,7 +5517,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5536,10 +5531,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45349</v>
+        <v>45923</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5552,7 +5547,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5595,7 +5590,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44810</v>
+        <v>45390</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5625,7 +5620,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5668,7 +5663,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5682,10 +5677,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45198</v>
+        <v>45805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5698,7 +5693,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5741,7 +5736,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5755,10 +5750,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45198</v>
+        <v>45805</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5771,7 +5766,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5814,7 +5809,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5824,14 +5819,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45390</v>
+        <v>45197</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5844,7 +5839,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5887,7 +5882,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5901,10 +5896,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45573</v>
+        <v>44615</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5917,7 +5912,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5960,7 +5955,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5974,10 +5969,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44963</v>
+        <v>45685</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5990,7 +5985,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6033,7 +6028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6047,10 +6042,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44560</v>
+        <v>46086</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6063,7 +6058,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6106,7 +6101,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6120,10 +6115,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45699</v>
+        <v>45938</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6136,7 +6131,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6179,7 +6174,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6193,10 +6188,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45468</v>
+        <v>45198</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6209,7 +6204,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6252,7 +6247,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6266,10 +6261,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44853</v>
+        <v>45943</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6282,7 +6277,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6325,7 +6320,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6339,10 +6334,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45553</v>
+        <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6355,7 +6350,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6398,7 +6393,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6412,10 +6407,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44963</v>
+        <v>45950</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6428,7 +6423,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6471,7 +6466,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6485,10 +6480,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44606</v>
+        <v>45069</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6500,8 +6495,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6544,7 +6544,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6554,14 +6554,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45237</v>
+        <v>46104</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6617,7 +6617,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44894</v>
+        <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45665</v>
+        <v>45573</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6763,7 +6763,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45771</v>
+        <v>45643</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45470</v>
+        <v>45265</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6867,11 +6867,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44745</v>
+        <v>44981</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45538</v>
+        <v>45112</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7016,8 +7016,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7060,7 +7065,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7074,10 +7079,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45699</v>
+        <v>45167</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7090,7 +7095,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7133,7 +7138,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7147,10 +7152,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45167</v>
+        <v>45602</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7163,7 +7168,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7206,7 +7211,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7220,10 +7225,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45167</v>
+        <v>45142</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7236,7 +7241,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7279,7 +7284,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7289,14 +7294,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45351</v>
+        <v>45596</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7309,7 +7314,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7352,7 +7357,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7362,14 +7367,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45300</v>
+        <v>45993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7382,7 +7387,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7425,7 +7430,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7439,10 +7444,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45797</v>
+        <v>45113</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7455,7 +7460,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7498,7 +7503,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7512,10 +7517,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45643</v>
+        <v>45911</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7528,7 +7533,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7571,7 +7576,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7585,10 +7590,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45091</v>
+        <v>45826</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7600,13 +7605,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7649,7 +7649,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44935</v>
+        <v>45257</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7722,7 +7722,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7732,14 +7732,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45186</v>
+        <v>45198</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7795,7 +7795,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7809,10 +7809,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44981</v>
+        <v>45799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7868,7 +7868,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44939</v>
+        <v>45254</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7941,7 +7941,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7951,14 +7951,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44939</v>
+        <v>45484</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>11.6</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44615</v>
+        <v>45854</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8043,8 +8043,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8087,7 +8092,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8101,10 +8106,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45142</v>
+        <v>45735</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8117,7 +8122,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8160,7 +8165,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8174,10 +8179,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45805</v>
+        <v>45028</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8190,7 +8195,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8233,7 +8238,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8247,10 +8252,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45805</v>
+        <v>45167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8263,7 +8268,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8306,7 +8311,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8320,10 +8325,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45685</v>
+        <v>45167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8336,7 +8341,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8379,7 +8384,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8393,10 +8398,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44697</v>
+        <v>45369</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8409,7 +8414,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8452,7 +8457,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8466,10 +8471,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44945</v>
+        <v>45882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8482,7 +8487,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8525,7 +8530,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8539,10 +8544,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45485</v>
+        <v>44957</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8555,7 +8560,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8598,7 +8603,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8612,10 +8617,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45161</v>
+        <v>46161</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8628,7 +8633,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8671,7 +8676,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8685,10 +8690,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45602</v>
+        <v>45161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8701,7 +8706,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8744,7 +8749,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8758,10 +8763,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45112</v>
+        <v>45946</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8773,13 +8778,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44537</v>
+        <v>45000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45167</v>
+        <v>45615</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44782</v>
+        <v>45557</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>11.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9041,7 +9041,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45146</v>
+        <v>45349</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9114,7 +9114,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9128,10 +9128,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45826</v>
+        <v>46181</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45254</v>
+        <v>45229</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9260,7 +9260,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44616</v>
+        <v>45665</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9333,7 +9333,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45028</v>
+        <v>46205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9406,7 +9406,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9416,14 +9416,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45167</v>
+        <v>45642</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9479,7 +9479,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45266</v>
+        <v>46205</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9552,7 +9552,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44614</v>
+        <v>45615</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9581,13 +9581,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9630,7 +9625,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9644,10 +9639,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44980</v>
+        <v>46205</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9660,7 +9655,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9703,7 +9698,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9717,10 +9712,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45215</v>
+        <v>45198</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9733,7 +9728,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9776,7 +9771,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9790,10 +9785,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45854</v>
+        <v>45390</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9805,13 +9800,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9854,7 +9844,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9868,10 +9858,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45735</v>
+        <v>45643</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9884,7 +9874,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9927,7 +9917,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9941,10 +9931,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45643</v>
+        <v>45237</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9957,7 +9947,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10000,7 +9990,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10014,10 +10004,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45557</v>
+        <v>44894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10030,7 +10020,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>11.5</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10073,7 +10063,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10087,10 +10077,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45615</v>
+        <v>46269</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10102,8 +10092,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10146,7 +10141,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10160,10 +10155,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45938</v>
+        <v>44697</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10176,7 +10171,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10219,7 +10214,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10233,10 +10228,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45943</v>
+        <v>44963</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10249,7 +10244,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10292,7 +10287,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10306,10 +10301,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45943</v>
+        <v>44745</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10322,7 +10317,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10365,7 +10360,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10379,10 +10374,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45950</v>
+        <v>44508</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10395,7 +10390,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10438,7 +10433,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10452,10 +10447,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45923</v>
+        <v>44951</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10468,7 +10463,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10511,7 +10506,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10525,10 +10520,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45923</v>
+        <v>44963</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10541,7 +10536,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10584,7 +10579,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10598,10 +10593,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45993</v>
+        <v>45010</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10609,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10657,7 +10652,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10671,10 +10666,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46019</v>
+        <v>44616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10687,7 +10682,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10730,7 +10725,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10744,10 +10739,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46042</v>
+        <v>46286</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10759,8 +10754,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>12.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10817,10 +10817,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46056</v>
+        <v>44537</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10876,7 +10876,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10886,14 +10886,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46056</v>
+        <v>45621</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10949,7 +10949,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10963,10 +10963,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46086</v>
+        <v>46262</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11022,7 +11022,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11032,14 +11032,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46104</v>
+        <v>46244</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11051,8 +11051,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11095,7 +11100,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11109,10 +11114,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45911</v>
+        <v>46244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11124,8 +11129,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11168,7 +11178,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11182,10 +11192,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45113</v>
+        <v>46244</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11197,8 +11207,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11241,7 +11256,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11255,10 +11270,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45265</v>
+        <v>46288</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11272,11 +11287,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>11.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11319,7 +11334,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11333,10 +11348,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45799</v>
+        <v>44614</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11348,8 +11363,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11392,7 +11412,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11402,14 +11422,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45257</v>
+        <v>46288</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11422,7 +11442,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11465,7 +11485,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11479,10 +11499,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45882</v>
+        <v>46288</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11495,7 +11515,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11538,7 +11558,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11552,10 +11572,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46161</v>
+        <v>45009</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11568,7 +11588,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11611,7 +11631,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11625,10 +11645,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45946</v>
+        <v>46244</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11640,8 +11660,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11684,7 +11709,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11698,10 +11723,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46181</v>
+        <v>46244</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11713,8 +11738,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11757,7 +11787,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11767,14 +11797,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46205</v>
+        <v>45167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11787,7 +11817,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11830,7 +11860,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11844,10 +11874,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46205</v>
+        <v>45146</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11860,7 +11890,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11903,7 +11933,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11917,10 +11947,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46205</v>
+        <v>44606</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11933,7 +11963,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11976,7 +12006,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11990,10 +12020,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46269</v>
+        <v>45091</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12011,7 +12041,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12054,7 +12084,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12068,10 +12098,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46262</v>
+        <v>45582</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12084,7 +12114,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12127,7 +12157,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12141,10 +12171,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12156,13 +12186,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12205,7 +12230,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12219,10 +12244,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46244</v>
+        <v>44980</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12234,13 +12259,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12283,7 +12303,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12297,10 +12317,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46244</v>
+        <v>45699</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12312,13 +12332,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12361,7 +12376,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12375,10 +12390,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46244</v>
+        <v>44560</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12390,13 +12405,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>8.5</v>
+        <v>0.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12439,7 +12449,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12453,10 +12463,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46244</v>
+        <v>45485</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12468,13 +12478,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12517,7 +12522,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12531,10 +12536,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46286</v>
+        <v>45266</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12546,13 +12551,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>12.7</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12595,7 +12595,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12609,10 +12609,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46288</v>
+        <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12624,13 +12624,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>11.7</v>
+        <v>6.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12673,7 +12668,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12683,14 +12678,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46288</v>
+        <v>45470</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12702,8 +12697,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12746,7 +12746,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12760,10 +12760,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46288</v>
+        <v>45538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12833,10 +12833,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46252</v>
+        <v>45771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26270-2024</t>
+          <t>A 33003-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1373,14 +1373,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45468</v>
+        <v>46244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1392,14 +1392,19 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1408,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1417,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1433,35 +1438,35 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
@@ -1485,7 +1490,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1583,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 34275-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1607,13 +1612,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1653,42 +1653,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 34277-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1705,7 +1705,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1762,38 +1762,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34277-2026</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,14 +1803,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46253</v>
+        <v>45468</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,23 +1823,23 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1863,35 +1863,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45186</v>
+        <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4067,14 +4067,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45300</v>
+        <v>45069</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4086,8 +4086,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4135,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4149,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45215</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44810</v>
+        <v>45582</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4233,7 +4238,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4276,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4290,10 +4295,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45209</v>
+        <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4306,7 +4311,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4349,7 +4354,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4363,10 +4368,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44782</v>
+        <v>45538</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4379,7 +4384,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4422,7 +4427,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45468</v>
+        <v>45198</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4452,7 +4457,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4495,7 +4500,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4509,10 +4514,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46019</v>
+        <v>45573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4525,7 +4530,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4568,7 +4573,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4582,10 +4587,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44853</v>
+        <v>45167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4598,7 +4603,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4641,7 +4646,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4651,14 +4656,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45351</v>
+        <v>45167</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4671,7 +4676,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4714,7 +4719,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4724,14 +4729,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45643</v>
+        <v>45300</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4744,7 +4749,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4787,7 +4792,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4801,10 +4806,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46042</v>
+        <v>46019</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4817,7 +4822,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4860,7 +4865,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44939</v>
+        <v>44935</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4890,7 +4895,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4933,7 +4938,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4943,14 +4948,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44945</v>
+        <v>45186</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4963,7 +4968,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5006,7 +5011,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5020,10 +5025,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46056</v>
+        <v>44981</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5036,7 +5041,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5089,14 +5094,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46056</v>
+        <v>45142</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5109,7 +5114,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5152,7 +5157,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5166,10 +5171,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45797</v>
+        <v>46042</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44922</v>
+        <v>45351</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5255,7 +5260,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5298,7 +5303,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5312,10 +5317,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44939</v>
+        <v>45797</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5328,7 +5333,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5371,7 +5376,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5385,10 +5390,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44935</v>
+        <v>45643</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5444,7 +5449,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5458,10 +5463,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45923</v>
+        <v>44945</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5517,7 +5522,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45923</v>
+        <v>45805</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5547,7 +5552,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5590,7 +5595,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45390</v>
+        <v>44782</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5620,7 +5625,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5680,7 +5685,7 @@
         <v>45805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5736,7 +5741,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5750,10 +5755,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45805</v>
+        <v>45923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5766,7 +5771,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5809,7 +5814,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5819,14 +5824,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45197</v>
+        <v>45923</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5839,7 +5844,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5882,7 +5887,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44615</v>
+        <v>46056</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5912,7 +5917,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5955,7 +5960,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5965,14 +5970,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45685</v>
+        <v>46056</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5985,7 +5990,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6028,7 +6033,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6042,10 +6047,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46086</v>
+        <v>45685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6058,7 +6063,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6101,7 +6106,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6115,10 +6120,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45938</v>
+        <v>45215</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6174,7 +6179,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6188,10 +6193,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45198</v>
+        <v>45643</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6204,7 +6209,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6247,7 +6252,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6261,10 +6266,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45943</v>
+        <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6277,7 +6282,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6320,7 +6325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6337,7 +6342,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6350,7 +6355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6393,7 +6398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6407,10 +6412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45950</v>
+        <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6423,7 +6428,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6466,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6480,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45069</v>
+        <v>45615</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6495,13 +6500,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6544,7 +6544,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6554,14 +6554,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46104</v>
+        <v>45950</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6617,7 +6617,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45699</v>
+        <v>45000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45573</v>
+        <v>46086</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6763,7 +6763,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45265</v>
+        <v>45369</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6865,13 +6865,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6914,7 +6909,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6928,10 +6923,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44981</v>
+        <v>44508</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6944,7 +6939,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6987,7 +6982,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7001,10 +6996,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45112</v>
+        <v>45009</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7016,13 +7011,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7065,7 +7055,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7075,14 +7065,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45167</v>
+        <v>46104</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7095,7 +7085,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7138,7 +7128,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7152,10 +7142,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45602</v>
+        <v>45010</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7168,7 +7158,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7211,7 +7201,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7225,10 +7215,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45142</v>
+        <v>45621</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7241,7 +7231,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7301,7 +7291,7 @@
         <v>45596</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7374,7 +7364,7 @@
         <v>45993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7430,7 +7420,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7444,10 +7434,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45113</v>
+        <v>45826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7460,7 +7450,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7503,7 +7493,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7517,10 +7507,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45911</v>
+        <v>45254</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7533,7 +7523,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7576,7 +7566,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7590,10 +7580,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45826</v>
+        <v>45390</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7606,7 +7596,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7649,7 +7639,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7663,10 +7653,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45257</v>
+        <v>45911</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7679,7 +7669,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7722,7 +7712,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7736,10 +7726,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45198</v>
+        <v>44560</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7752,7 +7742,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>8.800000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7795,7 +7785,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7809,10 +7799,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45799</v>
+        <v>44963</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7825,7 +7815,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7868,7 +7858,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7882,10 +7872,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45254</v>
+        <v>45237</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7898,7 +7888,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7941,7 +7931,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7951,14 +7941,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45484</v>
+        <v>44894</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8014,7 +8004,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8028,10 +8018,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45854</v>
+        <v>45113</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8043,13 +8033,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8092,7 +8077,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8106,10 +8091,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45735</v>
+        <v>45854</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8121,8 +8106,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8165,7 +8155,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8179,10 +8169,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45028</v>
+        <v>45265</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8194,8 +8184,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8238,7 +8233,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8252,10 +8247,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45167</v>
+        <v>45799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8268,7 +8263,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8311,7 +8306,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8325,10 +8320,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45167</v>
+        <v>45735</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8341,7 +8336,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8384,7 +8379,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45369</v>
+        <v>45257</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8414,7 +8409,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8457,7 +8452,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8471,10 +8466,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45882</v>
+        <v>45485</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8487,7 +8482,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8530,7 +8525,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8544,10 +8539,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44957</v>
+        <v>45112</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8559,8 +8554,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46161</v>
+        <v>45882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45161</v>
+        <v>45146</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8749,7 +8749,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45946</v>
+        <v>44616</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45000</v>
+        <v>44614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8851,8 +8851,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8895,7 +8900,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8909,10 +8914,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45615</v>
+        <v>46161</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8925,7 +8930,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8968,7 +8973,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8982,10 +8987,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45557</v>
+        <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8998,7 +9003,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11.5</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9041,7 +9046,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9055,10 +9060,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45349</v>
+        <v>45946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9071,7 +9076,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9114,7 +9119,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9128,10 +9133,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46181</v>
+        <v>45557</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9144,7 +9149,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9187,7 +9192,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9201,10 +9206,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45229</v>
+        <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9217,7 +9222,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9260,7 +9265,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9274,10 +9279,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45665</v>
+        <v>45615</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9290,7 +9295,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9333,7 +9338,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9347,10 +9352,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46205</v>
+        <v>45198</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9363,7 +9368,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9406,7 +9411,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9420,10 +9425,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45642</v>
+        <v>45229</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9436,7 +9441,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9496,7 +9501,7 @@
         <v>46205</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9552,7 +9557,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9566,10 +9571,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45615</v>
+        <v>46205</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9582,7 +9587,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9625,7 +9630,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9642,7 +9647,7 @@
         <v>46205</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9655,7 +9660,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9698,7 +9703,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9712,10 +9717,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45198</v>
+        <v>44957</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9728,7 +9733,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9771,7 +9776,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9785,10 +9790,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45390</v>
+        <v>45349</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9844,7 +9849,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9858,10 +9863,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45643</v>
+        <v>44963</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9874,7 +9879,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9917,7 +9922,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9931,10 +9936,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45237</v>
+        <v>45699</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9947,7 +9952,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9990,7 +9995,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10004,10 +10009,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44894</v>
+        <v>45468</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10020,7 +10025,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10063,7 +10068,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10077,10 +10082,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46269</v>
+        <v>44853</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10092,13 +10097,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10141,7 +10141,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44697</v>
+        <v>44606</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10214,7 +10214,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44963</v>
+        <v>46269</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10243,8 +10243,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10287,7 +10292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10301,10 +10306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44745</v>
+        <v>45665</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10317,7 +10322,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10360,7 +10365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10374,10 +10379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44508</v>
+        <v>44745</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10390,7 +10395,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10433,7 +10438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10447,10 +10452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44951</v>
+        <v>45699</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10463,7 +10468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10506,7 +10511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10520,10 +10525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44963</v>
+        <v>45091</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10535,8 +10540,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10579,7 +10589,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10593,10 +10603,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45010</v>
+        <v>46262</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10609,7 +10619,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10652,7 +10662,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10666,10 +10676,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44616</v>
+        <v>44939</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10682,7 +10692,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10725,7 +10735,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10739,10 +10749,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46286</v>
+        <v>44939</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10754,13 +10764,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>12.7</v>
+        <v>11.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10803,7 +10808,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10817,10 +10822,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44537</v>
+        <v>46244</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10832,8 +10837,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10876,7 +10886,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10890,10 +10900,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45621</v>
+        <v>44615</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10906,7 +10916,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10949,7 +10959,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10963,10 +10973,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10978,8 +10988,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11022,7 +11037,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11039,7 +11054,7 @@
         <v>46244</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11057,7 +11072,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11100,7 +11115,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11114,10 +11129,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46244</v>
+        <v>46286</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11150,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11178,7 +11193,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11192,10 +11207,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46244</v>
+        <v>46288</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11228,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.8</v>
+        <v>11.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11256,7 +11271,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11266,14 +11281,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
         <v>46288</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11285,13 +11300,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>11.7</v>
+        <v>3.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11334,7 +11344,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11348,10 +11358,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44614</v>
+        <v>46288</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11363,13 +11373,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11412,7 +11417,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11422,14 +11427,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46288</v>
+        <v>44697</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11442,7 +11447,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11485,7 +11490,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11499,10 +11504,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46288</v>
+        <v>45161</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11515,7 +11520,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11558,7 +11563,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11572,10 +11577,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45009</v>
+        <v>45602</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11588,7 +11593,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11631,7 +11636,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11645,10 +11650,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46244</v>
+        <v>44537</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11660,13 +11665,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11709,7 +11709,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11723,10 +11723,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46244</v>
+        <v>45167</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11738,13 +11738,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11787,7 +11782,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11797,14 +11792,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45167</v>
+        <v>46252</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11817,7 +11812,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11860,7 +11855,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11874,10 +11869,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45146</v>
+        <v>45028</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11890,7 +11885,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11933,7 +11928,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11943,14 +11938,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44606</v>
+        <v>45167</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11963,7 +11958,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12006,7 +12001,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12020,10 +12015,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45091</v>
+        <v>45266</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12035,13 +12030,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>9.4</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12084,7 +12074,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12098,10 +12088,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45582</v>
+        <v>46244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12113,8 +12103,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12157,7 +12152,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12171,10 +12166,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12186,8 +12181,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12244,10 +12244,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44980</v>
+        <v>45209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12303,7 +12303,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45699</v>
+        <v>45390</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12386,14 +12386,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44560</v>
+        <v>45197</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12459,14 +12459,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45485</v>
+        <v>45484</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12522,7 +12522,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12536,10 +12536,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45266</v>
+        <v>44951</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12595,7 +12595,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12609,10 +12609,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45553</v>
+        <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12668,7 +12668,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45470</v>
+        <v>45553</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12697,13 +12697,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12746,7 +12741,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12760,10 +12755,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45538</v>
+        <v>45771</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12776,7 +12771,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12819,7 +12814,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12833,10 +12828,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45771</v>
+        <v>45470</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12848,8 +12843,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>0.4</v>
+        <v>7.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>46244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45468</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>45069</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45582</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45538</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45198</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45167</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45300</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>46019</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>44935</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45186</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44981</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>45142</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46042</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45351</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45797</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45643</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>44945</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45805</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44782</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45923</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>46056</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>46056</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>45685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45215</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>45643</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45615</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45950</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>46086</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45642</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45369</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>44508</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>45009</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>46104</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45010</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>45621</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>45596</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>45826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>45254</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>45390</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45911</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>44560</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44963</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45237</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44894</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45113</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>45854</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>45265</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45735</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45257</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45485</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45112</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45146</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44616</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>46161</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45557</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45615</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45198</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45229</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>46205</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>46205</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>46205</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44957</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45349</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44963</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45699</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45468</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44853</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44606</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>46269</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45665</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44745</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45699</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45091</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>46262</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44939</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44939</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>46244</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>44615</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>46244</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>46244</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>46286</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>46288</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>46288</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>46288</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44697</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>45161</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>45602</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44537</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45167</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>46252</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>45028</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>45167</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>45266</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>46244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>46244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45390</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>45197</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45484</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44951</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45553</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45771</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45470</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>46244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45468</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44474</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44797</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44488</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44781</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44784</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44641</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44854</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44781</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44714</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44615</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44616</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>45069</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45582</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45538</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45198</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45167</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45300</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>46019</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>44935</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45186</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44981</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>45142</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46042</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45351</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45797</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45643</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>44945</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45805</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44782</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>45923</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45923</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>46056</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>46056</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>45685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45215</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>45643</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45615</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45950</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>46086</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45642</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45369</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>44508</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>45009</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>46104</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45010</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>45621</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>45596</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>45826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>45254</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>45390</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45911</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>44560</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44963</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45237</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44894</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45113</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>45854</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>45265</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45735</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45257</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45485</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45112</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45146</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44616</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>46161</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45557</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46181</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>45615</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45198</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45229</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>46205</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>46205</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>46205</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44957</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45349</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44963</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45699</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45468</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44853</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44606</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>46269</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45665</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44745</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45699</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45091</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>46262</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44939</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44939</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>46244</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>44615</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>46244</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>46244</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>46286</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>46288</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>46288</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>46288</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44697</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>45161</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>45602</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44537</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45167</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>46252</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>45028</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>45167</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>45266</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>46244</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>46244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45209</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45390</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>45197</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45484</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44951</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45553</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45771</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45470</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 10014-2025</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1264,14 +1264,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45719</v>
+        <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1284,22 +1284,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1317,53 +1317,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
-        <v/>
-      </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 32951-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1380,7 +1376,7 @@
         <v>46244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1398,7 +1394,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1442,144 +1438,144 @@
         </is>
       </c>
       <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 33003-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 32951-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HJO</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brun nållav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1600,7 +1596,7 @@
         <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1705,7 +1701,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1793,7 +1789,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 26270-2024</t>
+          <t>A 10014-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,14 +1799,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45468</v>
+        <v>45719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,10 +1819,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1835,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1856,42 +1852,46 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
         <v/>
       </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+        <v/>
+      </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
         <v/>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55091-2021</t>
+          <t>A 46998-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44474</v>
+        <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46998-2022</t>
+          <t>A 35216-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44852</v>
+        <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35216-2022</t>
+          <t>A 28512-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44797</v>
+        <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28512-2022</t>
+          <t>A 58495-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44748</v>
+        <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2962,7 +2962,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58495-2021</t>
+          <t>A 32158-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44488</v>
+        <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32158-2022</t>
+          <t>A 63257-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44781</v>
+        <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63257-2021</t>
+          <t>A 7786-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3118,14 +3118,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44508</v>
+        <v>44608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7786-2022</t>
+          <t>A 32814-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44608</v>
+        <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32814-2022</t>
+          <t>A 12726-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44784</v>
+        <v>44641</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12726-2022</t>
+          <t>A 47656-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44641</v>
+        <v>44854</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47656-2022</t>
+          <t>A 7231-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44854</v>
+        <v>44606</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7231-2022</t>
+          <t>A 32219-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44606</v>
+        <v>44781</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32219-2022</t>
+          <t>A 22586-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44781</v>
+        <v>44714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22586-2022</t>
+          <t>A 56175-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44714</v>
+        <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56175-2021</t>
+          <t>A 12544-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44477</v>
+        <v>44638</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3765,7 +3765,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12544-2022</t>
+          <t>A 9184-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44638</v>
+        <v>44615</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3838,7 +3838,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9184-2022</t>
+          <t>A 9210-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9210-2022</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44616</v>
+        <v>45186</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44922</v>
+        <v>45300</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45069</v>
+        <v>44810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4084,11 +4084,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>HJO</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4135,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4149,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>45215</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4165,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45582</v>
+        <v>45209</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4238,7 +4233,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4276,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4295,10 +4290,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45198</v>
+        <v>44782</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4311,7 +4306,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4354,7 +4349,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4368,10 +4363,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45538</v>
+        <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4384,7 +4379,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4427,7 +4422,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4441,10 +4436,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45198</v>
+        <v>44853</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4457,7 +4452,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4500,7 +4495,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4514,10 +4509,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45573</v>
+        <v>44939</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4530,7 +4525,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>11.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4573,7 +4568,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4587,10 +4582,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45167</v>
+        <v>44945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4646,7 +4641,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4656,14 +4651,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45167</v>
+        <v>44922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4676,7 +4671,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4719,7 +4714,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4729,14 +4724,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45300</v>
+        <v>45805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4749,7 +4744,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4792,7 +4787,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 63802-2025</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4806,10 +4801,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46019</v>
+        <v>45805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4822,7 +4817,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4865,7 +4860,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4879,10 +4874,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44935</v>
+        <v>45685</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4895,7 +4890,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4938,7 +4933,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4948,14 +4943,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45186</v>
+        <v>46042</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4968,7 +4963,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5011,7 +5006,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5025,10 +5020,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44981</v>
+        <v>44939</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5041,7 +5036,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5098,10 +5093,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45142</v>
+        <v>44935</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5114,7 +5109,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5157,7 +5152,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5171,10 +5166,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46042</v>
+        <v>45390</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5230,7 +5225,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5240,14 +5235,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45351</v>
+        <v>45826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5260,7 +5255,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5303,7 +5298,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5317,10 +5312,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45797</v>
+        <v>45254</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5333,7 +5328,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5376,7 +5371,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5386,14 +5381,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45643</v>
+        <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5406,7 +5401,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5449,7 +5444,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5463,10 +5458,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44945</v>
+        <v>44615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5479,7 +5474,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5522,7 +5517,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5536,10 +5531,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45805</v>
+        <v>45198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5552,7 +5547,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5595,7 +5590,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44782</v>
+        <v>46056</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5625,7 +5620,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5668,7 +5663,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5678,14 +5673,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45805</v>
+        <v>46056</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5698,7 +5693,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5741,7 +5736,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5755,10 +5750,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45923</v>
+        <v>45854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5770,8 +5765,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45923</v>
+        <v>45069</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5843,8 +5843,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5887,7 +5892,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5901,10 +5906,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46056</v>
+        <v>45735</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5917,7 +5922,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5960,7 +5965,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5970,14 +5975,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46056</v>
+        <v>45699</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5990,7 +5995,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6033,7 +6038,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6047,10 +6052,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45685</v>
+        <v>45923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6063,7 +6068,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6106,7 +6111,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6120,10 +6125,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45215</v>
+        <v>45923</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6136,7 +6141,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6179,7 +6184,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6193,10 +6198,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45643</v>
+        <v>45573</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6209,7 +6214,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6252,7 +6257,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6266,10 +6271,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45938</v>
+        <v>45643</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6282,7 +6287,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45943</v>
+        <v>45938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6415,7 +6420,7 @@
         <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45615</v>
+        <v>45943</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45950</v>
+        <v>44981</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6631,10 +6636,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45000</v>
+        <v>45112</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6646,8 +6651,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6690,7 +6700,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6704,10 +6714,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46086</v>
+        <v>45167</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6720,7 +6730,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6763,7 +6773,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6777,10 +6787,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45642</v>
+        <v>45950</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6793,7 +6803,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6836,7 +6846,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6850,10 +6860,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45369</v>
+        <v>45602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6866,7 +6876,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6909,7 +6919,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6923,10 +6933,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44508</v>
+        <v>45142</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6939,7 +6949,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6982,7 +6992,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6996,10 +7006,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45009</v>
+        <v>45596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7012,7 +7022,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7055,7 +7065,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7065,14 +7075,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46104</v>
+        <v>46086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7085,7 +7095,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7128,7 +7138,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7142,10 +7152,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45010</v>
+        <v>45198</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7158,7 +7168,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7201,7 +7211,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7211,14 +7221,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45621</v>
+        <v>45484</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7231,7 +7241,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7274,7 +7284,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7284,14 +7294,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45596</v>
+        <v>46104</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7304,7 +7314,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7364,7 +7374,7 @@
         <v>45993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7420,7 +7430,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7434,10 +7444,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45826</v>
+        <v>45265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7449,8 +7459,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7493,7 +7508,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7507,10 +7522,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45254</v>
+        <v>45028</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7523,7 +7538,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7566,7 +7581,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7580,10 +7595,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45390</v>
+        <v>45167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7596,7 +7611,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7639,7 +7654,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7653,10 +7668,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45911</v>
+        <v>45167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7669,7 +7684,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7712,7 +7727,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 63802-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7726,10 +7741,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44560</v>
+        <v>46019</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7742,7 +7757,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7785,7 +7800,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7799,10 +7814,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44963</v>
+        <v>45369</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7815,7 +7830,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7858,7 +7873,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7872,10 +7887,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45237</v>
+        <v>45113</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7888,7 +7903,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7931,7 +7946,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7945,10 +7960,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44894</v>
+        <v>45911</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7961,7 +7976,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8004,7 +8019,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8018,10 +8033,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45113</v>
+        <v>45257</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8034,7 +8049,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8077,7 +8092,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8091,10 +8106,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45854</v>
+        <v>44957</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8106,13 +8121,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8155,7 +8165,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8169,10 +8179,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45265</v>
+        <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8184,13 +8194,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8233,7 +8238,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8247,10 +8252,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45799</v>
+        <v>45161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8263,7 +8268,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8306,7 +8311,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8320,10 +8325,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45735</v>
+        <v>45000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8336,7 +8341,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8379,7 +8384,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8393,10 +8398,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45257</v>
+        <v>45615</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8409,7 +8414,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8452,7 +8457,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8466,10 +8471,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45485</v>
+        <v>45557</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8482,7 +8487,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8525,7 +8530,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8539,10 +8544,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45112</v>
+        <v>45349</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8554,13 +8559,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8620,7 +8620,7 @@
         <v>45882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45146</v>
+        <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8749,7 +8749,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44616</v>
+        <v>45946</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44614</v>
+        <v>45229</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8851,13 +8851,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8900,7 +8895,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8914,10 +8909,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46161</v>
+        <v>45665</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8930,7 +8925,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8973,7 +8968,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8987,10 +8982,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44980</v>
+        <v>46181</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9003,7 +8998,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9046,7 +9041,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9060,10 +9055,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45946</v>
+        <v>45642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9076,7 +9071,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9119,7 +9114,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9133,10 +9128,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45557</v>
+        <v>45615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9149,7 +9144,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9192,7 +9187,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9206,10 +9201,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46181</v>
+        <v>45198</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9222,7 +9217,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9265,7 +9260,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9279,10 +9274,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45615</v>
+        <v>45390</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9295,7 +9290,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9338,7 +9333,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9352,10 +9347,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45198</v>
+        <v>45643</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9368,7 +9363,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9411,7 +9406,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9425,10 +9420,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9441,7 +9436,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9484,7 +9479,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9498,10 +9493,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46205</v>
+        <v>44894</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9514,7 +9509,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9557,7 +9552,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9574,7 +9569,7 @@
         <v>46205</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9587,7 +9582,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9630,7 +9625,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9647,7 +9642,7 @@
         <v>46205</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9660,7 +9655,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9703,7 +9698,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9717,10 +9712,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44957</v>
+        <v>46205</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9733,7 +9728,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9776,7 +9771,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9790,10 +9785,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45349</v>
+        <v>44697</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9806,7 +9801,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9849,7 +9844,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9866,7 +9861,7 @@
         <v>44963</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9879,7 +9874,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9922,7 +9917,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45699</v>
+        <v>44745</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9952,7 +9947,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9995,7 +9990,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10009,10 +10004,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45468</v>
+        <v>44508</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10025,7 +10020,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10068,7 +10063,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10082,10 +10077,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44853</v>
+        <v>44951</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10098,7 +10093,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10141,7 +10136,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10155,10 +10150,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44606</v>
+        <v>44963</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10171,7 +10166,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10214,7 +10209,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10228,10 +10223,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46269</v>
+        <v>45010</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10243,13 +10238,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10292,7 +10282,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10306,10 +10296,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45665</v>
+        <v>44616</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10322,7 +10312,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10365,7 +10355,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10379,10 +10369,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44745</v>
+        <v>44537</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10395,7 +10385,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10438,7 +10428,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10452,10 +10442,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45699</v>
+        <v>46269</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10467,8 +10457,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10511,7 +10506,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10525,10 +10520,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45091</v>
+        <v>45621</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10540,13 +10535,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>9.4</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10589,7 +10579,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10603,10 +10593,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46262</v>
+        <v>44614</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10618,8 +10608,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10662,7 +10657,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10676,10 +10671,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44939</v>
+        <v>45009</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10692,7 +10687,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10735,7 +10730,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10745,14 +10740,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44939</v>
+        <v>45167</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10765,7 +10760,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>11.6</v>
+        <v>5.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10808,7 +10803,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10822,10 +10817,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46244</v>
+        <v>45146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10837,13 +10832,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10886,7 +10876,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10900,10 +10890,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44615</v>
+        <v>44606</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10906,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10959,7 +10949,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10973,10 +10963,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46244</v>
+        <v>45091</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10984,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11037,7 +11027,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11051,10 +11041,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46244</v>
+        <v>45582</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11066,13 +11056,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11132,7 +11117,7 @@
         <v>46286</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11193,7 +11178,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11207,10 +11192,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46288</v>
+        <v>46262</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11222,13 +11207,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>11.7</v>
+        <v>4.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11271,7 +11251,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11281,14 +11261,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46288</v>
+        <v>44980</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11301,7 +11281,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11344,7 +11324,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11358,10 +11338,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46288</v>
+        <v>46244</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11373,8 +11353,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11417,7 +11402,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11431,10 +11416,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44697</v>
+        <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11446,8 +11431,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11490,7 +11480,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11504,10 +11494,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45161</v>
+        <v>46244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11519,8 +11509,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11563,7 +11558,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11573,14 +11568,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45602</v>
+        <v>46288</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11593,7 +11588,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11636,7 +11631,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11650,10 +11645,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44537</v>
+        <v>46288</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11666,7 +11661,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11709,7 +11704,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11723,10 +11718,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45167</v>
+        <v>45699</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11739,7 +11734,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11782,7 +11777,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11796,10 +11791,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46252</v>
+        <v>44560</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11812,7 +11807,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11855,7 +11850,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11869,10 +11864,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45028</v>
+        <v>45485</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11885,7 +11880,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11928,7 +11923,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11938,14 +11933,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45167</v>
+        <v>45266</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11958,7 +11953,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12001,7 +11996,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12015,10 +12010,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45266</v>
+        <v>45553</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12031,7 +12026,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12074,7 +12069,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12088,10 +12083,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12103,13 +12098,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12152,7 +12142,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12166,10 +12156,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46244</v>
+        <v>45470</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12183,11 +12173,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12230,7 +12220,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12244,10 +12234,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45209</v>
+        <v>45538</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12260,7 +12250,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12303,7 +12293,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12317,10 +12307,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45390</v>
+        <v>46244</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12332,8 +12322,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12376,7 +12371,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12386,14 +12381,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45197</v>
+        <v>45771</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12406,7 +12401,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12449,7 +12444,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12459,14 +12454,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45484</v>
+        <v>46244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12478,8 +12473,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12522,7 +12522,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12532,14 +12532,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44951</v>
+        <v>45351</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12595,7 +12595,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 41239-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12609,10 +12609,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44810</v>
+        <v>46300</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12668,7 +12668,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45553</v>
+        <v>45643</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12741,7 +12741,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12755,10 +12755,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45771</v>
+        <v>46288</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12770,8 +12770,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>0.4</v>
+        <v>11.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12814,7 +12819,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12828,10 +12833,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45470</v>
+        <v>45797</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12843,13 +12848,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26270-2024</t>
+          <t>A 33003-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1264,14 +1264,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45468</v>
+        <v>46244</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,14 +1283,19 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1299,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1308,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1324,35 +1329,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
@@ -1376,7 +1381,7 @@
         <v>46244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 34275-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1483,10 +1488,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,13 +1503,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1544,42 +1544,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34275-2026</t>
+          <t>A 34277-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1596,7 +1596,7 @@
         <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1653,38 +1653,38 @@
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34275-2026 artfynd.xlsx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34275-2026 karta.png", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34275-2026 georefererad karta.tif", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34275-2026 FSC-klagomål.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34275-2026 FSC-klagomål mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34275-2026 tillsynsbegäran.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34275-2026 tillsynsbegäran mail.docx", "A 34275-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34277-2026</t>
+          <t>A 26270-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1694,14 +1694,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46253</v>
+        <v>45468</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
@@ -1738,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1754,35 +1754,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 34277-2026 artfynd.xlsx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 34277-2026 karta.png", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 34277-2026 georefererad karta.tif", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 34277-2026 FSC-klagomål.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 34277-2026 FSC-klagomål mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 34277-2026 tillsynsbegäran.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 34277-2026 tillsynsbegäran mail.docx", "A 34277-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
         <v/>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
         <v>45719</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44799</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>44729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>44846</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44515</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44797</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44488</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44781</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44641</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44854</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44606</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44781</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44714</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44638</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44615</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44684-2023</t>
+          <t>A 62233-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45186</v>
+        <v>44922</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 724-2024</t>
+          <t>A 60413-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3994,14 +3994,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45300</v>
+        <v>45643</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37789-2022</t>
+          <t>A 22050-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44810</v>
+        <v>45069</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4084,6 +4084,11 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>HJO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4130,7 +4135,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50152-2023</t>
+          <t>A 46339-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4149,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45215</v>
+        <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49025-2023</t>
+          <t>A 46762-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45209</v>
+        <v>45198</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4233,7 +4238,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4276,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32518-2022</t>
+          <t>A 46790-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4290,10 +4295,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44782</v>
+        <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4306,7 +4311,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4349,7 +4354,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26248-2024</t>
+          <t>A 39537-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4363,10 +4368,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45468</v>
+        <v>45167</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4379,7 +4384,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4422,7 +4427,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47300-2022</t>
+          <t>A 39540-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44853</v>
+        <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4452,7 +4457,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4495,7 +4500,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2070-2023</t>
+          <t>A 44310-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4509,10 +4514,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44939</v>
+        <v>45573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4525,7 +4530,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>11.6</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4568,7 +4573,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2866-2023</t>
+          <t>A 724-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4578,14 +4583,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44945</v>
+        <v>45300</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4598,7 +4603,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4641,7 +4646,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62233-2022</t>
+          <t>A 1108-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4651,14 +4656,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44922</v>
+        <v>44935</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4671,7 +4676,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4714,7 +4719,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26229-2025</t>
+          <t>A 9473-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4728,10 +4733,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45805</v>
+        <v>44981</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4744,7 +4749,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4787,7 +4792,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26238-2025</t>
+          <t>A 34859-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4801,10 +4806,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45805</v>
+        <v>45142</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4817,7 +4822,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4860,7 +4865,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4243-2025</t>
+          <t>A 2866-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45685</v>
+        <v>44945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4890,7 +4895,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4933,7 +4938,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3569-2026</t>
+          <t>A 44684-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4943,14 +4948,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46042</v>
+        <v>45186</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4963,7 +4968,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5006,7 +5011,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2060-2023</t>
+          <t>A 32518-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5020,10 +5025,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44939</v>
+        <v>44782</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5036,7 +5041,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1108-2023</t>
+          <t>A 26238-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5093,10 +5098,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44935</v>
+        <v>45805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5109,7 +5114,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5152,7 +5157,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13694-2024</t>
+          <t>A 26229-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5166,10 +5171,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45390</v>
+        <v>45805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29960-2025</t>
+          <t>A 3569-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45826</v>
+        <v>46042</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5255,7 +5260,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5298,7 +5303,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59452-2023</t>
+          <t>A 4243-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5312,10 +5317,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45254</v>
+        <v>45685</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5328,7 +5333,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5371,7 +5376,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 46520-2023</t>
+          <t>A 50152-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5381,14 +5386,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45197</v>
+        <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5444,7 +5449,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9177-2022</t>
+          <t>A 60318-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5458,10 +5463,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44615</v>
+        <v>45643</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5474,7 +5479,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5517,7 +5522,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46762-2023</t>
+          <t>A 6686-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45198</v>
+        <v>46056</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5547,7 +5552,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5590,7 +5595,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6686-2026</t>
+          <t>A 6705-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5600,14 +5605,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
         <v>46056</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5620,7 +5625,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5663,7 +5668,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6705-2026</t>
+          <t>A 53846-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5673,14 +5678,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46056</v>
+        <v>45615</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5693,7 +5698,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5736,7 +5741,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35319-2025</t>
+          <t>A 12554-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5750,10 +5755,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45854</v>
+        <v>45000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5765,13 +5770,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22050-2023</t>
+          <t>A 59988-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45069</v>
+        <v>45642</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5843,13 +5843,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5892,7 +5887,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13177-2025</t>
+          <t>A 45736-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5906,10 +5901,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45735</v>
+        <v>45923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5922,7 +5917,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5965,7 +5960,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6369-2025</t>
+          <t>A 45742-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5979,10 +5974,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45699</v>
+        <v>45923</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5995,7 +5990,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6038,7 +6033,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45742-2025</t>
+          <t>A 10670-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6052,10 +6047,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45923</v>
+        <v>45369</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6068,7 +6063,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6111,7 +6106,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45736-2025</t>
+          <t>A 12165-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6125,10 +6120,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45923</v>
+        <v>46086</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6141,7 +6136,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6184,7 +6179,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44310-2024</t>
+          <t>A 29960-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6198,10 +6193,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45573</v>
+        <v>45826</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6257,7 +6252,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60318-2024</t>
+          <t>A 63239-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6271,10 +6266,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45643</v>
+        <v>44508</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49278-2025</t>
+          <t>A 59452-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45938</v>
+        <v>45254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50093-2025</t>
+          <t>A 14196-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45943</v>
+        <v>45009</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50091-2025</t>
+          <t>A 49278-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45943</v>
+        <v>45938</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9473-2023</t>
+          <t>A 15019-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6559,14 +6554,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44981</v>
+        <v>46104</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30636-2023</t>
+          <t>A 50093-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6636,10 +6631,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45112</v>
+        <v>45943</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6651,13 +6646,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6700,7 +6690,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39542-2023</t>
+          <t>A 50091-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6714,10 +6704,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45167</v>
+        <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6730,7 +6720,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6773,7 +6763,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51362-2025</t>
+          <t>A 14460-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6787,10 +6777,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45950</v>
+        <v>45010</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6803,7 +6793,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6846,7 +6836,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50711-2024</t>
+          <t>A 55003-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6860,10 +6850,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45602</v>
+        <v>45621</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6876,7 +6866,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6919,7 +6909,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34859-2023</t>
+          <t>A 51362-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6933,10 +6923,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45142</v>
+        <v>45950</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6949,7 +6939,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6992,7 +6982,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49564-2024</t>
+          <t>A 35319-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7006,10 +6996,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45596</v>
+        <v>45854</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7021,8 +7011,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7065,7 +7060,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12165-2026</t>
+          <t>A 13177-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7079,10 +7074,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46086</v>
+        <v>45735</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7095,7 +7090,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7138,7 +7133,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46787-2023</t>
+          <t>A 49564-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7152,10 +7147,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45198</v>
+        <v>45596</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7168,7 +7163,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.800000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7211,7 +7206,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 29596-2024</t>
+          <t>A 43370-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7221,14 +7216,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45484</v>
+        <v>45911</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7241,7 +7236,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7284,7 +7279,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15019-2026</t>
+          <t>A 13703-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7294,14 +7289,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46104</v>
+        <v>45390</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7314,7 +7309,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7357,7 +7352,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60071-2025</t>
+          <t>A 30970-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7371,10 +7366,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45993</v>
+        <v>45113</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7387,7 +7382,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7430,7 +7425,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61700-2023</t>
+          <t>A 60071-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7444,10 +7439,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45265</v>
+        <v>45993</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7459,13 +7454,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7508,7 +7498,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16352-2023</t>
+          <t>A 61700-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7522,10 +7512,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45028</v>
+        <v>45265</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7537,8 +7527,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7581,7 +7576,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 39537-2023</t>
+          <t>A 25053-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7595,10 +7590,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45167</v>
+        <v>45799</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7611,7 +7606,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7654,7 +7649,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 39540-2023</t>
+          <t>A 59986-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7668,10 +7663,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45167</v>
+        <v>45257</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7684,7 +7679,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7744,7 +7739,7 @@
         <v>46019</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7800,7 +7795,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10670-2024</t>
+          <t>A 138-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7814,10 +7809,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45369</v>
+        <v>44560</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7830,7 +7825,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7873,7 +7868,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30970-2023</t>
+          <t>A 38052-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7887,10 +7882,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45113</v>
+        <v>45882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7903,7 +7898,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7946,7 +7941,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43370-2025</t>
+          <t>A 23193-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7960,10 +7955,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45911</v>
+        <v>46161</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7976,7 +7971,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8019,7 +8014,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59986-2023</t>
+          <t>A 50932-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8033,10 +8028,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45257</v>
+        <v>45946</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8049,7 +8044,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8092,7 +8087,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4783-2023</t>
+          <t>A 5773-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8106,10 +8101,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44957</v>
+        <v>44963</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8122,7 +8117,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8165,7 +8160,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25053-2025</t>
+          <t>A 25991-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8179,10 +8174,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45799</v>
+        <v>46181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8195,7 +8190,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8238,7 +8233,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38186-2023</t>
+          <t>A 55119-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8252,10 +8247,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45161</v>
+        <v>45237</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8268,7 +8263,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8311,7 +8306,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 12554-2023</t>
+          <t>A 58597-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8325,10 +8320,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45000</v>
+        <v>44894</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8341,7 +8336,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8384,7 +8379,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 53839-2024</t>
+          <t>A 29798-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45615</v>
+        <v>45485</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8414,7 +8409,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8457,7 +8452,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40629-2024</t>
+          <t>A 30636-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8471,10 +8466,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45557</v>
+        <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8486,8 +8481,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>11.5</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8530,7 +8530,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 7722-2024</t>
+          <t>A 29905-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8544,10 +8544,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45349</v>
+        <v>46205</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38052-2025</t>
+          <t>A 29953-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45882</v>
+        <v>46205</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23193-2026</t>
+          <t>A 29891-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46161</v>
+        <v>46205</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8749,7 +8749,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 50932-2025</t>
+          <t>A 35486-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45946</v>
+        <v>45146</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54902-2023</t>
+          <t>A 9297-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45229</v>
+        <v>44616</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1094-2025</t>
+          <t>A 8814-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45665</v>
+        <v>44614</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8924,8 +8924,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8968,7 +8973,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25991-2026</t>
+          <t>A 9338-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8982,10 +8987,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46181</v>
+        <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8998,7 +9003,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9041,7 +9046,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59988-2024</t>
+          <t>A 40629-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9055,10 +9060,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45642</v>
+        <v>45557</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9071,7 +9076,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9114,7 +9119,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 53846-2024</t>
+          <t>A 53839-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9131,7 +9136,7 @@
         <v>45615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9144,7 +9149,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9187,7 +9192,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46790-2023</t>
+          <t>A 36436-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9201,10 +9206,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45198</v>
+        <v>46269</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9216,8 +9221,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9260,7 +9270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 13703-2024</t>
+          <t>A 46787-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9274,10 +9284,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45390</v>
+        <v>45198</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9290,7 +9300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9333,7 +9343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60413-2024</t>
+          <t>A 54902-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9347,10 +9357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45643</v>
+        <v>45229</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9363,7 +9373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9406,7 +9416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55119-2023</t>
+          <t>A 4783-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9420,10 +9430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45237</v>
+        <v>44957</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9436,7 +9446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9479,7 +9489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58597-2022</t>
+          <t>A 7722-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9493,10 +9503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44894</v>
+        <v>45349</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9509,7 +9519,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9552,7 +9562,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29891-2026</t>
+          <t>A 35592-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9566,10 +9576,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46205</v>
+        <v>46262</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9582,7 +9592,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9625,7 +9635,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 29905-2026</t>
+          <t>A 5770-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9639,10 +9649,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46205</v>
+        <v>44963</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9655,7 +9665,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9698,7 +9708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 29953-2026</t>
+          <t>A 32919-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9712,10 +9722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9727,8 +9737,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9771,7 +9786,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20024-2022</t>
+          <t>A 6369-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9785,10 +9800,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44697</v>
+        <v>45699</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9801,7 +9816,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9844,7 +9859,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 5773-2023</t>
+          <t>A 26248-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9858,10 +9873,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44963</v>
+        <v>45468</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9874,7 +9889,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9917,7 +9932,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27989-2022</t>
+          <t>A 32914-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9931,10 +9946,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44745</v>
+        <v>46244</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9946,8 +9961,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9990,7 +10010,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 63239-2021</t>
+          <t>A 32921-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10004,10 +10024,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44508</v>
+        <v>46244</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10019,8 +10039,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10063,7 +10088,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4272-2023</t>
+          <t>A 47300-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10077,10 +10102,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44951</v>
+        <v>44853</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10093,7 +10118,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10136,7 +10161,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5770-2023</t>
+          <t>A 38892-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10150,10 +10175,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44963</v>
+        <v>46286</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10165,8 +10190,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.7</v>
+        <v>12.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10209,7 +10239,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 14460-2023</t>
+          <t>A 7392-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10223,10 +10253,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45010</v>
+        <v>44606</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10239,7 +10269,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10282,7 +10312,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9297-2022</t>
+          <t>A 39246-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10292,14 +10322,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44616</v>
+        <v>46288</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10312,7 +10342,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10355,7 +10385,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 70743-2021</t>
+          <t>A 1094-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10369,10 +10399,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44537</v>
+        <v>45665</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10385,7 +10415,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10428,7 +10458,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36436-2026</t>
+          <t>A 39248-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10442,10 +10472,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46269</v>
+        <v>46288</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10457,13 +10487,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10506,7 +10531,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 55003-2024</t>
+          <t>A 27989-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10520,10 +10545,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45621</v>
+        <v>44745</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10536,7 +10561,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10579,7 +10604,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8814-2022</t>
+          <t>A 6497-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10593,10 +10618,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44614</v>
+        <v>45699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10608,13 +10633,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10657,7 +10677,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 14196-2023</t>
+          <t>A 26230-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10671,10 +10691,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45009</v>
+        <v>45091</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10686,8 +10706,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>3.5</v>
+        <v>9.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10730,7 +10755,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 39538-2023</t>
+          <t>A 2060-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10740,14 +10765,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45167</v>
+        <v>44939</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10760,7 +10785,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10803,7 +10828,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35486-2023</t>
+          <t>A 2070-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10817,10 +10842,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45146</v>
+        <v>44939</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10833,7 +10858,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.9</v>
+        <v>11.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10876,7 +10901,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7392-2022</t>
+          <t>A 33950-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10890,10 +10915,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44606</v>
+        <v>46252</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10906,7 +10931,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10949,7 +10974,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 26230-2023</t>
+          <t>A 9177-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10963,10 +10988,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45091</v>
+        <v>44615</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10978,13 +11003,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>9.4</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11027,7 +11047,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46339-2024</t>
+          <t>A 20024-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11041,10 +11061,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45582</v>
+        <v>44697</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11057,7 +11077,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11100,7 +11120,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 38892-2026</t>
+          <t>A 32961-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11114,10 +11134,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46286</v>
+        <v>46244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11135,7 +11155,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>12.7</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11178,7 +11198,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 35592-2026</t>
+          <t>A 38186-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11192,10 +11212,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46262</v>
+        <v>45161</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11208,7 +11228,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11251,7 +11271,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 9338-2023</t>
+          <t>A 50711-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11265,10 +11285,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44980</v>
+        <v>45602</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11281,7 +11301,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11324,7 +11344,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32914-2026</t>
+          <t>A 70743-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11338,10 +11358,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46244</v>
+        <v>44537</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11353,13 +11373,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11402,7 +11417,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32921-2026</t>
+          <t>A 32973-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11419,7 +11434,7 @@
         <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11437,7 +11452,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11480,7 +11495,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32919-2026</t>
+          <t>A 39542-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11494,10 +11509,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46244</v>
+        <v>45167</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11509,13 +11524,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11558,7 +11568,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39246-2026</t>
+          <t>A 39330-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11568,14 +11578,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
         <v>46288</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11587,8 +11597,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>3.2</v>
+        <v>11.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11631,7 +11646,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39248-2026</t>
+          <t>A 41239-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11645,10 +11660,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46288</v>
+        <v>46300</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11661,7 +11676,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11704,7 +11719,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6497-2025</t>
+          <t>A 16352-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11718,10 +11733,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45699</v>
+        <v>45028</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11734,7 +11749,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11777,7 +11792,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 138-2022</t>
+          <t>A 39538-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11787,14 +11802,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44560</v>
+        <v>45167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11807,7 +11822,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11850,7 +11865,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29798-2024</t>
+          <t>A 61925-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11864,10 +11879,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45485</v>
+        <v>45266</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11880,7 +11895,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11923,7 +11938,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 61925-2023</t>
+          <t>A 49025-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11937,10 +11952,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45266</v>
+        <v>45209</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11953,7 +11968,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11996,7 +12011,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 39907-2024</t>
+          <t>A 13694-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12010,10 +12025,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45553</v>
+        <v>45390</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12026,7 +12041,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12069,7 +12084,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33950-2026</t>
+          <t>A 46520-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12079,14 +12094,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46252</v>
+        <v>45197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12099,7 +12114,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12142,7 +12157,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26792-2024</t>
+          <t>A 29596-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12152,14 +12167,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45470</v>
+        <v>45484</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12171,13 +12186,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12220,7 +12230,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 36738-2024</t>
+          <t>A 4272-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12234,10 +12244,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45538</v>
+        <v>44951</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12250,7 +12260,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12293,7 +12303,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32961-2026</t>
+          <t>A 37789-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12307,10 +12317,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46244</v>
+        <v>44810</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12322,13 +12332,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12371,7 +12376,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 19810-2025</t>
+          <t>A 39907-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12385,10 +12390,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45771</v>
+        <v>45553</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12401,7 +12406,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12444,7 +12449,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 32973-2026</t>
+          <t>A 19810-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12458,10 +12463,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46244</v>
+        <v>45771</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12473,13 +12478,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12522,7 +12522,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 8145-2024</t>
+          <t>A 26792-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12532,14 +12532,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45351</v>
+        <v>45470</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12551,8 +12551,13 @@
           <t>HJO</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12595,7 +12600,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 41239-2026</t>
+          <t>A 36738-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12609,10 +12614,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46300</v>
+        <v>45538</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12625,7 +12630,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12668,7 +12673,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60414-2024</t>
+          <t>A 8145-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12678,14 +12683,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45643</v>
+        <v>45351</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12698,7 +12703,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12741,7 +12746,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39330-2026</t>
+          <t>A 24388-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12755,10 +12760,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46288</v>
+        <v>45797</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12770,13 +12775,8 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>11.7</v>
+        <v>1.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24388-2025</t>
+          <t>A 60414-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12833,10 +12833,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45797</v>
+        <v>45643</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12909,7 +12909,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>

--- a/Översikt HJO.xlsx
+++ b/Översikt HJO.xlsx
@@ -601,7 +601,7 @@
         <v>45015</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>46269</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>46269</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 33003-2026</t>
+          <t>A 10014-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46244</v>
+        <v>45719</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1283,26 +1283,21 @@
           <t>HJO</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1313,588 +1308,593 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 10014-2025 artfynd.xlsx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 10014-2025 karta.png", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 10014-2025 georefererad karta.tif", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/knärot/A 10014-2025 karta knärot.png", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 10014-2025 FSC-klagomål.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 10014-2025 FSC-klagomål mail.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 10014-2025 tillsynsbegäran.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 10014-2025 tillsynsbegäran mail.docx", "A 10014-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 26270-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45468</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 26270-2024 artfynd.xlsx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 26270-2024 karta.png", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 26270-2024 georefererad karta.tif", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 26270-2024 FSC-klagomål.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 26270-2024 FSC-klagomål mail.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 26270-2024 tillsynsbegäran.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 26270-2024 tillsynsbegäran mail.docx", "A 26270-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 32951-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Brun nållav</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 32951-2026 artfynd.xlsx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 32951-2026 karta.png", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 32951-2026 georefererad karta.tif", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 32951-2026 FSC-klagomål.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 32951-2026 FSC-klagomål mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 32951-2026 tillsynsbegäran.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 32951-2026 tillsynsbegäran mail.docx", "A 32951-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 33003-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HJO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/artfynd/A 33003-2026 artfynd.xlsx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor/A 33003-2026 karta.png", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/kartor_geotiff/A 33003-2026 georefererad karta.tif", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomål/A 33003-2026 FSC-klagomål.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/klagomålsmail/A 33003-2026 FSC-klagomål mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsyn/A 33003-2026 tillsynsbegäran.docx", "A 33003-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1497/tillsynsmail/A 33003-2026 tillsynsbegäran mail.docx", "A 33003-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        